--- a/Vanguard EU/Vanguard-ETFs-KostenBepaling.xlsx
+++ b/Vanguard EU/Vanguard-ETFs-KostenBepaling.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/Vanguard EU/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="739" documentId="13_ncr:1_{383DE9F1-B669-4070-96E2-664D98CFDC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D82275AD-C0A6-447E-8ECC-29D2998131D9}"/>
+  <xr:revisionPtr revIDLastSave="1016" documentId="13_ncr:1_{383DE9F1-B669-4070-96E2-664D98CFDC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77B05692-6954-4C54-93F9-2EF556FA7325}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VWRL" sheetId="13" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="97">
   <si>
     <t>Dividend income</t>
   </si>
@@ -310,13 +310,31 @@
     <t>2021: capital gains tax reservation high, taking on only real paid taxes as specifiek on page 637</t>
   </si>
   <si>
-    <t>2014-2021</t>
-  </si>
-  <si>
     <t>2015-2021</t>
   </si>
   <si>
     <t>2016-2021</t>
+  </si>
+  <si>
+    <t>KID % transaction costs</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>The current securities lending income split</t>
+  </si>
+  <si>
+    <t>2014-2024</t>
+  </si>
+  <si>
+    <t>2015-2024</t>
+  </si>
+  <si>
+    <t>2021: capital gains tax reservation high, taking on only real paid taxes as specified on page 637</t>
+  </si>
+  <si>
+    <t>2024: weird jump in dividend leakage. Tracking diff also jumps.</t>
   </si>
 </sst>
 </file>
@@ -765,769 +783,982 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD89FDB9-F393-4A65-BDCD-E968CF6BDA63}">
-  <dimension ref="B2:O39"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="38.42578125" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="16.28515625" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" customWidth="1"/>
+    <col min="1" max="1" width="38.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="16.28515625" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>35</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C4" s="1">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B3" s="1">
         <v>2013</v>
       </c>
-      <c r="D4" s="1">
+      <c r="C3" s="1">
         <v>2014</v>
       </c>
-      <c r="E4" s="1">
+      <c r="D3" s="1">
         <v>2015</v>
       </c>
-      <c r="F4" s="1">
+      <c r="E3" s="1">
         <v>2016</v>
       </c>
-      <c r="G4" s="1">
+      <c r="F3" s="1">
         <v>2017</v>
       </c>
-      <c r="H4" s="1">
+      <c r="G3" s="1">
         <v>2018</v>
       </c>
-      <c r="I4" s="1">
+      <c r="H3" s="1">
         <v>2019</v>
       </c>
-      <c r="J4" s="1">
+      <c r="I3" s="1">
         <v>2020</v>
       </c>
-      <c r="K4" s="1">
+      <c r="J3" s="1">
         <v>2021</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="K3" s="1">
+        <v>2022</v>
+      </c>
+      <c r="L3" s="1">
+        <v>2023</v>
+      </c>
+      <c r="M3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O4" s="30" t="s">
+      <c r="Q3" s="30" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="5">
+      <c r="B4" s="5">
         <v>114950407</v>
       </c>
+      <c r="C4" s="19">
+        <v>474931514</v>
+      </c>
+      <c r="D4" s="19">
+        <v>876937458</v>
+      </c>
+      <c r="E4" s="20">
+        <v>937471365</v>
+      </c>
+      <c r="F4" s="20">
+        <v>1295979632</v>
+      </c>
+      <c r="G4" s="20">
+        <v>2102651548</v>
+      </c>
+      <c r="H4" s="20">
+        <v>2704960870</v>
+      </c>
+      <c r="I4" s="20">
+        <v>5594999708</v>
+      </c>
+      <c r="J4" s="20">
+        <v>11438295558</v>
+      </c>
+      <c r="K4" s="20">
+        <v>12728930487</v>
+      </c>
+      <c r="L4" s="20">
+        <v>18223363484</v>
+      </c>
+      <c r="M4" s="20">
+        <v>27231939274</v>
+      </c>
+      <c r="N4" s="1"/>
+      <c r="Q4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="19">
+        <v>615977</v>
+      </c>
       <c r="D5" s="19">
-        <v>474931514</v>
-      </c>
-      <c r="E5" s="19">
-        <v>876937458</v>
+        <v>1698292</v>
+      </c>
+      <c r="E5" s="20">
+        <v>2296151</v>
       </c>
       <c r="F5" s="20">
-        <v>937471365</v>
+        <v>2711104</v>
       </c>
       <c r="G5" s="20">
-        <v>1295979632</v>
+        <v>4167659</v>
       </c>
       <c r="H5" s="20">
-        <v>2102651548</v>
+        <v>5770056</v>
       </c>
       <c r="I5" s="20">
-        <v>2704960870</v>
+        <v>9632698</v>
       </c>
       <c r="J5" s="20">
-        <v>5594999708</v>
+        <v>18625547</v>
       </c>
       <c r="K5" s="20">
-        <v>11438295558</v>
-      </c>
-      <c r="L5" s="1"/>
-      <c r="O5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="19">
-        <v>615977</v>
-      </c>
-      <c r="E6" s="19">
-        <v>1698292</v>
-      </c>
-      <c r="F6" s="20">
-        <v>2296151</v>
-      </c>
-      <c r="G6" s="20">
-        <v>2711104</v>
-      </c>
-      <c r="H6" s="20">
-        <v>4167659</v>
-      </c>
-      <c r="I6" s="20">
-        <v>5770056</v>
-      </c>
-      <c r="J6" s="20">
-        <v>9632698</v>
-      </c>
-      <c r="K6" s="20">
-        <v>18625547</v>
-      </c>
-      <c r="O6" t="s">
+        <v>28531762</v>
+      </c>
+      <c r="L5" s="20">
+        <v>32899328</v>
+      </c>
+      <c r="M5" s="20">
+        <v>47677363</v>
+      </c>
+      <c r="Q5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="14">
+      <c r="C6" s="14">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="E7" s="14">
+      <c r="D6" s="14">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="F7" s="14">
+      <c r="E6" s="14">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="G7" s="14">
+      <c r="F6" s="14">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="H7" s="14">
+      <c r="G6" s="14">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="I7" s="14">
+      <c r="H6" s="14">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="J7" s="14">
+      <c r="I6" s="14">
         <f>((114/366)*0.25%)+((252/366)*0.22%)</f>
         <v>2.29344262295082E-3</v>
       </c>
-      <c r="K7" s="14">
+      <c r="J6" s="14">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="L7" s="3">
-        <f>AVERAGE(D7:K7)</f>
-        <v>2.4366803278688528E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+      <c r="K6" s="14">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="L6" s="14">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="M6" s="14">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="N6" s="3">
+        <f>AVERAGE(C6:M6)</f>
+        <v>2.3721311475409842E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="19">
-        <f>(C5+D5)/2</f>
+      <c r="B7" s="5"/>
+      <c r="C7" s="19">
+        <f>(B4+C4)/2</f>
         <v>294940960.5</v>
       </c>
-      <c r="E8" s="19">
-        <f t="shared" ref="E8:K8" si="0">(D5+E5)/2</f>
+      <c r="D7" s="19">
+        <f t="shared" ref="D7:M7" si="0">(C4+D4)/2</f>
         <v>675934486</v>
       </c>
-      <c r="F8" s="19">
+      <c r="E7" s="19">
         <f t="shared" si="0"/>
         <v>907204411.5</v>
       </c>
-      <c r="G8" s="19">
+      <c r="F7" s="19">
         <f t="shared" si="0"/>
         <v>1116725498.5</v>
       </c>
-      <c r="H8" s="19">
+      <c r="G7" s="19">
         <f t="shared" si="0"/>
         <v>1699315590</v>
       </c>
-      <c r="I8" s="19">
+      <c r="H7" s="19">
         <f t="shared" si="0"/>
         <v>2403806209</v>
       </c>
-      <c r="J8" s="19">
+      <c r="I7" s="19">
         <f t="shared" si="0"/>
         <v>4149980289</v>
       </c>
-      <c r="K8" s="19">
+      <c r="J7" s="19">
         <f t="shared" si="0"/>
         <v>8516647633</v>
       </c>
-      <c r="L8" s="3"/>
-      <c r="O8" t="s">
+      <c r="K7" s="19">
+        <f t="shared" si="0"/>
+        <v>12083613022.5</v>
+      </c>
+      <c r="L7" s="19">
+        <f t="shared" si="0"/>
+        <v>15476146985.5</v>
+      </c>
+      <c r="M7" s="19">
+        <f t="shared" si="0"/>
+        <v>22727651379</v>
+      </c>
+      <c r="N7" s="3"/>
+      <c r="Q7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="20">
-        <f>D6/D7</f>
+      <c r="B8" s="5"/>
+      <c r="C8" s="20">
+        <f>C5/C6</f>
         <v>246390800</v>
       </c>
-      <c r="E9" s="20">
-        <f t="shared" ref="E9:K9" si="1">E6/E7</f>
+      <c r="D8" s="20">
+        <f t="shared" ref="D8:M8" si="1">D5/D6</f>
         <v>679316800</v>
       </c>
-      <c r="F9" s="20">
+      <c r="E8" s="20">
         <f t="shared" si="1"/>
         <v>918460400</v>
       </c>
-      <c r="G9" s="20">
+      <c r="F8" s="20">
         <f t="shared" si="1"/>
         <v>1084441600</v>
       </c>
-      <c r="H9" s="20">
+      <c r="G8" s="20">
         <f t="shared" si="1"/>
         <v>1667063600</v>
       </c>
-      <c r="I9" s="20">
+      <c r="H8" s="20">
         <f t="shared" si="1"/>
         <v>2308022400</v>
       </c>
-      <c r="J9" s="20">
+      <c r="I8" s="20">
         <f t="shared" si="1"/>
         <v>4200104203.0021439</v>
       </c>
-      <c r="K9" s="20">
+      <c r="J8" s="20">
         <f t="shared" si="1"/>
         <v>8466157727.272727</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C10" s="5"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="3"/>
-      <c r="O10" t="s">
+      <c r="K8" s="20">
+        <f t="shared" si="1"/>
+        <v>12968982727.272726</v>
+      </c>
+      <c r="L8" s="20">
+        <f t="shared" si="1"/>
+        <v>14954240000</v>
+      </c>
+      <c r="M8" s="20">
+        <f t="shared" si="1"/>
+        <v>21671528636.363636</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B9" s="5"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="3"/>
+      <c r="Q9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5">
+        <v>7496554</v>
+      </c>
+      <c r="D10" s="5">
+        <v>17837465</v>
+      </c>
+      <c r="E10" s="5">
+        <v>25181502</v>
+      </c>
+      <c r="F10" s="5">
+        <v>28329734</v>
+      </c>
+      <c r="G10" s="5">
+        <v>43044701</v>
+      </c>
+      <c r="H10" s="5">
+        <v>64119281</v>
+      </c>
+      <c r="I10" s="5">
+        <v>100819368</v>
+      </c>
+      <c r="J10" s="5">
+        <v>174261332</v>
+      </c>
+      <c r="K10" s="5">
+        <v>290519219</v>
+      </c>
+      <c r="L10" s="5">
+        <v>362329280</v>
+      </c>
+      <c r="M10" s="5">
+        <v>465915642</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5">
+        <v>734078</v>
+      </c>
       <c r="D11" s="5">
-        <v>7496554</v>
+        <v>1970630</v>
       </c>
       <c r="E11" s="5">
-        <v>17837465</v>
+        <v>3037267</v>
       </c>
       <c r="F11" s="5">
-        <v>25181502</v>
+        <v>3337917</v>
       </c>
       <c r="G11" s="5">
-        <v>28329734</v>
+        <v>5268891</v>
       </c>
       <c r="H11" s="5">
-        <v>43044701</v>
+        <v>7444601</v>
       </c>
       <c r="I11" s="5">
-        <v>64119281</v>
+        <v>12482600</v>
       </c>
       <c r="J11" s="5">
-        <v>100819368</v>
-      </c>
-      <c r="K11" s="5">
-        <v>174261332</v>
-      </c>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5">
-        <v>734078</v>
-      </c>
-      <c r="E12" s="5">
-        <v>1970630</v>
-      </c>
-      <c r="F12" s="5">
-        <v>3037267</v>
-      </c>
-      <c r="G12" s="5">
-        <v>3337917</v>
-      </c>
-      <c r="H12" s="5">
-        <v>5268891</v>
-      </c>
-      <c r="I12" s="5">
-        <v>7444601</v>
-      </c>
-      <c r="J12" s="5">
-        <v>12482600</v>
-      </c>
-      <c r="K12" s="5">
         <f>20634618+171202</f>
         <v>20805820</v>
       </c>
-      <c r="L12" s="3"/>
-      <c r="O12" t="s">
+      <c r="K11" s="5">
+        <f>31505719+127120</f>
+        <v>31632839</v>
+      </c>
+      <c r="L11" s="5">
+        <f>41917155+333018</f>
+        <v>42250173</v>
+      </c>
+      <c r="M11" s="5">
+        <f>55892990+1229091</f>
+        <v>57122081</v>
+      </c>
+      <c r="N11" s="3"/>
+      <c r="Q11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="16">
-        <f>D12/D11</f>
+      <c r="C12" s="16">
+        <f>C11/C10</f>
         <v>9.7922058588519476E-2</v>
       </c>
-      <c r="E13" s="16">
-        <f t="shared" ref="E13:J13" si="2">E12/E11</f>
+      <c r="D12" s="16">
+        <f t="shared" ref="D12:I12" si="2">D11/D10</f>
         <v>0.11047702125834585</v>
       </c>
-      <c r="F13" s="16">
+      <c r="E12" s="16">
         <f t="shared" si="2"/>
         <v>0.12061500541151199</v>
       </c>
-      <c r="G13" s="16">
+      <c r="F12" s="16">
         <f t="shared" si="2"/>
         <v>0.11782380307559541</v>
       </c>
-      <c r="H13" s="16">
+      <c r="G12" s="16">
         <f t="shared" si="2"/>
         <v>0.12240510161750223</v>
       </c>
-      <c r="I13" s="16">
+      <c r="H12" s="16">
         <f t="shared" si="2"/>
         <v>0.11610549719046288</v>
       </c>
-      <c r="J13" s="16">
+      <c r="I12" s="16">
         <f t="shared" si="2"/>
         <v>0.12381152795958808</v>
       </c>
-      <c r="K13" s="16">
-        <f t="shared" ref="K13" si="3">K12/K11</f>
+      <c r="J12" s="16">
+        <f t="shared" ref="J12:M12" si="3">J11/J10</f>
         <v>0.11939435881277437</v>
       </c>
-      <c r="L13" s="3">
-        <f>AVERAGE(D13:K13)</f>
-        <v>0.11606929673928755</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
+      <c r="K12" s="16">
+        <f t="shared" si="3"/>
+        <v>0.10888380847533533</v>
+      </c>
+      <c r="L12" s="16">
+        <f t="shared" si="3"/>
+        <v>0.11660711770243906</v>
+      </c>
+      <c r="M12" s="16">
+        <f t="shared" si="3"/>
+        <v>0.12260176703833438</v>
+      </c>
+      <c r="N12" s="3">
+        <f>AVERAGE(C12:M12)</f>
+        <v>0.11605882428458264</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="15">
-        <f t="shared" ref="D14:K14" si="4">D12/D9</f>
+      <c r="C13" s="15">
+        <f t="shared" ref="C13:M13" si="4">C11/C8</f>
         <v>2.9793239033275593E-3</v>
       </c>
-      <c r="E14" s="15">
+      <c r="D13" s="15">
         <f t="shared" si="4"/>
         <v>2.9008998452562927E-3</v>
       </c>
-      <c r="F14" s="15">
+      <c r="E13" s="15">
         <f t="shared" si="4"/>
         <v>3.3069112179469032E-3</v>
       </c>
-      <c r="G14" s="15">
+      <c r="F13" s="15">
         <f t="shared" si="4"/>
         <v>3.0780053070631006E-3</v>
       </c>
-      <c r="H14" s="15">
+      <c r="G13" s="15">
         <f t="shared" si="4"/>
         <v>3.1605818758204548E-3</v>
       </c>
-      <c r="I14" s="15">
+      <c r="H13" s="15">
         <f t="shared" si="4"/>
         <v>3.2255323865140995E-3</v>
       </c>
-      <c r="J14" s="15">
+      <c r="I13" s="15">
         <f t="shared" si="4"/>
         <v>2.9719738836664353E-3</v>
       </c>
-      <c r="K14" s="15">
+      <c r="J13" s="15">
         <f t="shared" si="4"/>
         <v>2.4575280393107383E-3</v>
       </c>
-      <c r="L14" s="3">
-        <f>AVERAGE(D14:K14)</f>
-        <v>3.0100945573631977E-3</v>
-      </c>
-      <c r="O14" t="s">
+      <c r="K13" s="15">
+        <f t="shared" si="4"/>
+        <v>2.4391148993882679E-3</v>
+      </c>
+      <c r="L13" s="15">
+        <f t="shared" si="4"/>
+        <v>2.8252972401138408E-3</v>
+      </c>
+      <c r="M13" s="15">
+        <f t="shared" si="4"/>
+        <v>2.6358122658755269E-3</v>
+      </c>
+      <c r="N13" s="3">
+        <f>AVERAGE(C13:M13)</f>
+        <v>2.9073618967530193E-3</v>
+      </c>
+      <c r="Q13" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20">
+      <c r="B15" s="5"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20">
         <v>984905</v>
       </c>
-      <c r="H16" s="20">
+      <c r="G15" s="20">
         <v>3201782</v>
       </c>
-      <c r="I16" s="20">
+      <c r="H15" s="20">
         <v>7704750</v>
       </c>
-      <c r="J16" s="20">
+      <c r="I15" s="20">
         <v>46764163</v>
       </c>
-      <c r="K16" s="20">
+      <c r="J15" s="20">
         <v>54994816</v>
       </c>
-      <c r="L16" s="3"/>
-      <c r="O16" t="s">
+      <c r="K15" s="20">
+        <v>122625203</v>
+      </c>
+      <c r="L15" s="20">
+        <v>144720872</v>
+      </c>
+      <c r="M15" s="20">
+        <v>186032405</v>
+      </c>
+      <c r="N15" s="3"/>
+      <c r="Q15" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="15">
+        <f t="shared" ref="F16:M16" si="5">F15/F4</f>
+        <v>7.5996950544667203E-4</v>
+      </c>
+      <c r="G16" s="15">
+        <f t="shared" si="5"/>
+        <v>1.5227354256797665E-3</v>
+      </c>
+      <c r="H16" s="15">
+        <f t="shared" si="5"/>
+        <v>2.8483776181205903E-3</v>
+      </c>
+      <c r="I16" s="15">
+        <f t="shared" si="5"/>
+        <v>8.3582065130645752E-3</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" si="5"/>
+        <v>4.8079554966156089E-3</v>
+      </c>
+      <c r="K16" s="15">
+        <f t="shared" si="5"/>
+        <v>9.6335825798747644E-3</v>
+      </c>
+      <c r="L16" s="15">
+        <f t="shared" si="5"/>
+        <v>7.9415016951763055E-3</v>
+      </c>
+      <c r="M16" s="15">
+        <f t="shared" si="5"/>
+        <v>6.8314049590150394E-3</v>
+      </c>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C17" s="13"/>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="15">
-        <f>G16/G5</f>
-        <v>7.5996950544667203E-4</v>
-      </c>
-      <c r="H17" s="15">
-        <f>H16/H5</f>
-        <v>1.5227354256797665E-3</v>
-      </c>
-      <c r="I17" s="15">
-        <f>I16/I5</f>
-        <v>2.8483776181205903E-3</v>
-      </c>
-      <c r="J17" s="15">
-        <f>J16/J5</f>
-        <v>8.3582065130645752E-3</v>
-      </c>
-      <c r="K17" s="15">
-        <f>K16/K5</f>
-        <v>4.8079554966156089E-3</v>
-      </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20">
+      <c r="B18" s="5"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20">
         <v>44238</v>
       </c>
-      <c r="H19" s="20">
+      <c r="G18" s="20">
         <v>121589</v>
       </c>
-      <c r="I19" s="20">
+      <c r="H18" s="20">
         <v>263359</v>
       </c>
-      <c r="J19" s="20">
+      <c r="I18" s="20">
         <v>543754</v>
       </c>
-      <c r="K19" s="20">
+      <c r="J18" s="20">
         <v>1048130</v>
       </c>
-      <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
+      <c r="K18" s="20">
+        <v>1772784</v>
+      </c>
+      <c r="L18" s="20">
+        <v>3148829</v>
+      </c>
+      <c r="M18" s="20">
+        <v>3848294</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="17">
-        <f t="shared" ref="D20:K20" si="5">D19/D9</f>
+      <c r="C19" s="17">
+        <f t="shared" ref="C19:M19" si="6">C18/C8</f>
         <v>0</v>
       </c>
-      <c r="E20" s="17">
-        <f t="shared" si="5"/>
+      <c r="D19" s="17">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F20" s="17">
-        <f t="shared" si="5"/>
+      <c r="E19" s="17">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G20" s="17">
-        <f t="shared" si="5"/>
+      <c r="F19" s="17">
+        <f t="shared" si="6"/>
         <v>4.0793344703854958E-5</v>
       </c>
-      <c r="H20" s="17">
-        <f t="shared" si="5"/>
+      <c r="G19" s="17">
+        <f t="shared" si="6"/>
         <v>7.2936029555201135E-5</v>
       </c>
-      <c r="I20" s="17">
-        <f t="shared" si="5"/>
+      <c r="H19" s="17">
+        <f t="shared" si="6"/>
         <v>1.1410591162373468E-4</v>
       </c>
-      <c r="J20" s="17">
-        <f t="shared" si="5"/>
+      <c r="I19" s="17">
+        <f t="shared" si="6"/>
         <v>1.294620261114799E-4</v>
       </c>
-      <c r="K20" s="17">
-        <f t="shared" si="5"/>
+      <c r="J19" s="17">
+        <f t="shared" si="6"/>
         <v>1.2380232376531009E-4</v>
       </c>
-      <c r="L20" s="2">
-        <f>AVERAGE(D20:K20)</f>
-        <v>6.0137454469947593E-5</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
+      <c r="K19" s="17">
+        <f t="shared" si="6"/>
+        <v>1.3669414458174718E-4</v>
+      </c>
+      <c r="L19" s="17">
+        <f t="shared" si="6"/>
+        <v>2.1056429480869639E-4</v>
+      </c>
+      <c r="M19" s="17">
+        <f t="shared" si="6"/>
+        <v>1.7757372193592168E-4</v>
+      </c>
+      <c r="N19" s="2">
+        <f>AVERAGE(C19:M19)</f>
+        <v>9.1448345189631473E-5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5">
         <v>282714</v>
       </c>
-      <c r="E22" s="19">
+      <c r="D21" s="19">
         <v>332383</v>
       </c>
-      <c r="F22" s="20">
+      <c r="E21" s="20">
         <v>250041</v>
       </c>
-      <c r="G22" s="20">
+      <c r="F21" s="20">
         <v>214668</v>
       </c>
-      <c r="H22" s="20">
+      <c r="G21" s="20">
         <v>556031</v>
       </c>
-      <c r="I22" s="20">
+      <c r="H21" s="20">
         <v>394506</v>
       </c>
-      <c r="J22" s="20">
+      <c r="I21" s="20">
         <v>1569681</v>
       </c>
-      <c r="K22" s="20">
+      <c r="J21" s="20">
         <v>2299311</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
+      <c r="K21" s="20">
+        <v>2236422</v>
+      </c>
+      <c r="L21" s="20">
+        <v>2122555</v>
+      </c>
+      <c r="M21" s="20">
+        <v>2914559</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="15">
-        <f t="shared" ref="D23:K23" si="6">D22/D9</f>
+      <c r="C22" s="15">
+        <f t="shared" ref="C22:M22" si="7">C21/C8</f>
         <v>1.1474210887744186E-3</v>
       </c>
-      <c r="E23" s="15">
-        <f t="shared" si="6"/>
+      <c r="D22" s="15">
+        <f t="shared" si="7"/>
         <v>4.8929012207559125E-4</v>
       </c>
-      <c r="F23" s="15">
-        <f t="shared" si="6"/>
+      <c r="E22" s="15">
+        <f t="shared" si="7"/>
         <v>2.7223928217264459E-4</v>
       </c>
-      <c r="G23" s="15">
-        <f t="shared" si="6"/>
+      <c r="F22" s="15">
+        <f t="shared" si="7"/>
         <v>1.979525684001794E-4</v>
       </c>
-      <c r="H23" s="15">
-        <f t="shared" si="6"/>
+      <c r="G22" s="15">
+        <f t="shared" si="7"/>
         <v>3.335391643126273E-4</v>
       </c>
-      <c r="I23" s="18">
-        <f t="shared" si="6"/>
+      <c r="H22" s="18">
+        <f t="shared" si="7"/>
         <v>1.7092815043736145E-4</v>
       </c>
-      <c r="J23" s="18">
-        <f t="shared" si="6"/>
+      <c r="I22" s="18">
+        <f t="shared" si="7"/>
         <v>3.7372429923953455E-4</v>
       </c>
-      <c r="K23" s="18">
-        <f t="shared" si="6"/>
+      <c r="J22" s="18">
+        <f t="shared" si="7"/>
         <v>2.7158849079707569E-4</v>
       </c>
-      <c r="L23" s="3">
-        <f>AVERAGE(D23:K23)</f>
-        <v>4.0708539577617904E-4</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K22" s="18">
+        <f t="shared" si="7"/>
+        <v>1.7244390304391297E-4</v>
+      </c>
+      <c r="L22" s="18">
+        <f t="shared" si="7"/>
+        <v>1.4193666812890526E-4</v>
+      </c>
+      <c r="M22" s="18">
+        <f t="shared" si="7"/>
+        <v>1.3448792878918242E-4</v>
+      </c>
+      <c r="N22" s="2">
+        <f>AVERAGE(C22:M22)</f>
+        <v>3.3686833328831208E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
+      <c r="H24" s="18"/>
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="L25" s="18"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
+      <c r="L24" s="18"/>
+      <c r="M24" s="18">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N25" s="18"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="3">
-        <f>L7+L14-L20+L23</f>
-        <v>5.7937228265382817E-3</v>
-      </c>
-      <c r="D26" t="s">
-        <v>88</v>
-      </c>
+      <c r="B26" s="3">
+        <f>N6+N13-N19+N22</f>
+        <v>5.5249130323926851E-3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="8"/>
       <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+      <c r="G26" s="18"/>
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
       <c r="K26" s="18"/>
       <c r="L26" s="18"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="3">
-        <f>AVERAGE(GTD!D5:J5)/100</f>
-        <v>5.7857142857142855E-3</v>
-      </c>
-      <c r="D27" t="s">
-        <v>88</v>
-      </c>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
+      <c r="B27" s="3">
+        <f>AVERAGE(GTD!D5:N5)/100</f>
+        <v>5.5272727272727253E-3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="3">
-        <f>C27-C26</f>
-        <v>-8.0085408239961506E-6</v>
-      </c>
-      <c r="I28" s="3"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
+      <c r="B28" s="3">
+        <f>B27-B26</f>
+        <v>2.3596948800401821E-6</v>
+      </c>
+      <c r="H28" s="3"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="11">
-        <f>0.22%+L14-K20+AVERAGE(I23:K23)</f>
-        <v>5.3583725470892117E-3</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
+      <c r="B30" s="11">
+        <f>0.22%+N13-AVERAGE(K19:M19)+AVERAGE(K22:M22)</f>
+        <v>5.0820406762982313E-3</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="11">
-        <f>C30-L14</f>
-        <v>2.348277989726014E-3</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B32" s="1"/>
-      <c r="C32" s="11"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
+      <c r="B31" s="11">
+        <f>B30-N13</f>
+        <v>2.174678779545212E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="11"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="11">
-        <f>C30-C26</f>
-        <v>-4.3535027944906993E-4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B34" s="1" t="s">
+      <c r="B33" s="11">
+        <f>B30-B26</f>
+        <v>-4.4287235609445381E-4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="11">
-        <f>C27+C33</f>
-        <v>5.3503640062652156E-3</v>
-      </c>
+      <c r="B34" s="11">
+        <f>B27+B33</f>
+        <v>5.0844003711782715E-3</v>
+      </c>
+      <c r="D34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
+      <c r="G34" s="7"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
+      <c r="G39" s="7"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="O4" r:id="rId1" display="https://www.ie.vanguard/product-documentation/mifid-priips" xr:uid="{5F97709C-78A2-4F08-A418-EFDAFE8E468D}"/>
+    <hyperlink ref="Q3" r:id="rId1" display="https://www.ie.vanguard/product-documentation/mifid-priips" xr:uid="{5F97709C-78A2-4F08-A418-EFDAFE8E468D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
@@ -1536,676 +1767,886 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF345284-CA73-4DF5-92DD-8F9EBDED894B}">
-  <dimension ref="B2:M35"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="38.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="16.28515625" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" customWidth="1"/>
+    <col min="1" max="1" width="38.42578125" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="16.28515625" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>47</v>
       </c>
-      <c r="M3" t="s">
+      <c r="O2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C4" s="1">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B3" s="1">
         <v>2015</v>
       </c>
-      <c r="D4" s="1">
+      <c r="C3" s="1">
         <v>2016</v>
       </c>
-      <c r="E4" s="1">
+      <c r="D3" s="1">
         <v>2017</v>
       </c>
-      <c r="F4" s="1">
+      <c r="E3" s="1">
         <v>2018</v>
       </c>
-      <c r="G4" s="1">
+      <c r="F3" s="1">
         <v>2019</v>
       </c>
-      <c r="H4" s="1">
+      <c r="G3" s="1">
         <v>2020</v>
       </c>
-      <c r="I4" s="1">
+      <c r="H3" s="1">
         <v>2021</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="I3" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J3" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="30" t="s">
+      <c r="O3" s="30" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="19">
+      <c r="B4" s="19">
         <v>36748312</v>
       </c>
+      <c r="C4" s="20">
+        <v>62180178</v>
+      </c>
+      <c r="D4" s="20">
+        <v>110225318</v>
+      </c>
+      <c r="E4" s="20">
+        <v>192982164</v>
+      </c>
+      <c r="F4" s="20">
+        <v>350661628</v>
+      </c>
+      <c r="G4" s="20">
+        <v>564482029</v>
+      </c>
+      <c r="H4" s="20">
+        <v>1366292883</v>
+      </c>
+      <c r="I4" s="20">
+        <v>1966352880</v>
+      </c>
+      <c r="J4" s="20">
+        <v>3121340084</v>
+      </c>
+      <c r="K4" s="20">
+        <v>5631475076</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="O4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="19">
+        <v>40773</v>
+      </c>
+      <c r="C5" s="20">
+        <v>85228</v>
+      </c>
       <c r="D5" s="20">
-        <v>62180178</v>
+        <v>145838</v>
       </c>
       <c r="E5" s="20">
-        <v>110225318</v>
+        <v>276479</v>
       </c>
       <c r="F5" s="20">
-        <v>192982164</v>
+        <v>484895</v>
       </c>
       <c r="G5" s="20">
-        <v>350661628</v>
+        <v>570934</v>
       </c>
       <c r="H5" s="20">
-        <v>564482029</v>
+        <v>1141318</v>
       </c>
       <c r="I5" s="20">
-        <v>1366292883</v>
-      </c>
-      <c r="J5" s="1"/>
-      <c r="M5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="19">
-        <v>40773</v>
-      </c>
-      <c r="D6" s="20">
-        <v>85228</v>
-      </c>
-      <c r="E6" s="20">
-        <v>145838</v>
-      </c>
-      <c r="F6" s="20">
-        <v>276479</v>
-      </c>
-      <c r="G6" s="20">
-        <v>484895</v>
-      </c>
-      <c r="H6" s="20">
-        <v>570934</v>
-      </c>
-      <c r="I6" s="20">
-        <v>1141318</v>
-      </c>
-      <c r="M6" t="s">
+        <v>2177326</v>
+      </c>
+      <c r="J5" s="20">
+        <v>2934105</v>
+      </c>
+      <c r="K5" s="20">
+        <v>4899038</v>
+      </c>
+      <c r="O5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="14">
+      <c r="B6" s="14">
         <v>1.8E-3</v>
       </c>
-      <c r="D7" s="14">
+      <c r="C6" s="14">
         <v>1.8E-3</v>
       </c>
-      <c r="E7" s="14">
+      <c r="D6" s="14">
         <v>1.8E-3</v>
       </c>
-      <c r="F7" s="14">
+      <c r="E6" s="14">
         <v>1.8E-3</v>
       </c>
-      <c r="G7" s="14">
+      <c r="F6" s="14">
         <v>1.8E-3</v>
       </c>
-      <c r="H7" s="14">
+      <c r="G6" s="14">
         <f>((114/366)*0.18%)+((252/366)*0.12%)</f>
         <v>1.3868852459016394E-3</v>
       </c>
-      <c r="I7" s="14">
+      <c r="H6" s="14">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="J7" s="3">
-        <f>AVERAGE(C7:I7)</f>
-        <v>1.655269320843091E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+      <c r="I6" s="14">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="J6" s="14">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="K6" s="14">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="L6" s="3">
+        <f>AVERAGE(B6:K6)</f>
+        <v>1.5186885245901637E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19">
-        <f t="shared" ref="D8:I8" si="0">(C5+D5)/2</f>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19">
+        <f t="shared" ref="C7:H7" si="0">(B4+C4)/2</f>
         <v>49464245</v>
       </c>
-      <c r="E8" s="19">
+      <c r="D7" s="19">
         <f t="shared" si="0"/>
         <v>86202748</v>
       </c>
-      <c r="F8" s="19">
+      <c r="E7" s="19">
         <f t="shared" si="0"/>
         <v>151603741</v>
       </c>
-      <c r="G8" s="19">
+      <c r="F7" s="19">
         <f t="shared" si="0"/>
         <v>271821896</v>
       </c>
-      <c r="H8" s="19">
+      <c r="G7" s="19">
         <f t="shared" si="0"/>
         <v>457571828.5</v>
       </c>
-      <c r="I8" s="19">
+      <c r="H7" s="19">
         <f t="shared" si="0"/>
         <v>965387456</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="M8" t="s">
+      <c r="I7" s="19">
+        <f t="shared" ref="I7" si="1">(H4+I4)/2</f>
+        <v>1666322881.5</v>
+      </c>
+      <c r="J7" s="19">
+        <f t="shared" ref="J7" si="2">(I4+J4)/2</f>
+        <v>2543846482</v>
+      </c>
+      <c r="K7" s="19">
+        <f t="shared" ref="K7" si="3">(J4+K4)/2</f>
+        <v>4376407580</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="O7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="20">
-        <f t="shared" ref="C9:H9" si="1">C6/C7</f>
+      <c r="B8" s="20">
+        <f t="shared" ref="B8:G8" si="4">B5/B6</f>
         <v>22651666.666666668</v>
       </c>
-      <c r="D9" s="20">
-        <f t="shared" si="1"/>
+      <c r="C8" s="20">
+        <f t="shared" si="4"/>
         <v>47348888.888888888</v>
       </c>
-      <c r="E9" s="20">
-        <f t="shared" si="1"/>
+      <c r="D8" s="20">
+        <f t="shared" si="4"/>
         <v>81021111.111111119</v>
       </c>
-      <c r="F9" s="20">
-        <f t="shared" si="1"/>
+      <c r="E8" s="20">
+        <f t="shared" si="4"/>
         <v>153599444.44444445</v>
       </c>
-      <c r="G9" s="20">
-        <f t="shared" si="1"/>
+      <c r="F8" s="20">
+        <f t="shared" si="4"/>
         <v>269386111.1111111</v>
       </c>
-      <c r="H9" s="20">
-        <f t="shared" si="1"/>
+      <c r="G8" s="20">
+        <f t="shared" si="4"/>
         <v>411666359.33806145</v>
       </c>
-      <c r="I9" s="20">
-        <f t="shared" ref="I9" si="2">I6/I7</f>
+      <c r="H8" s="20">
+        <f t="shared" ref="H8:K8" si="5">H5/H6</f>
         <v>951098333.33333337</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+      <c r="I8" s="20">
+        <f t="shared" si="5"/>
+        <v>1814438333.3333335</v>
+      </c>
+      <c r="J8" s="20">
+        <f t="shared" si="5"/>
+        <v>2445087500</v>
+      </c>
+      <c r="K8" s="20">
+        <f t="shared" si="5"/>
+        <v>4082531666.666667</v>
+      </c>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>0</v>
       </c>
+      <c r="B10" s="5">
+        <v>572890</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1316266</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2129637</v>
+      </c>
+      <c r="E10" s="5">
+        <v>3930173</v>
+      </c>
+      <c r="F10" s="5">
+        <v>7446153</v>
+      </c>
+      <c r="G10" s="5">
+        <v>9716656</v>
+      </c>
+      <c r="H10" s="5">
+        <v>19286055</v>
+      </c>
+      <c r="I10" s="5">
+        <v>39205089</v>
+      </c>
+      <c r="J10" s="5">
+        <v>56258998</v>
+      </c>
+      <c r="K10" s="5">
+        <v>85525055</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="5">
+        <v>66149</v>
+      </c>
       <c r="C11" s="5">
-        <v>572890</v>
+        <v>156844</v>
       </c>
       <c r="D11" s="5">
-        <v>1316266</v>
+        <v>255100</v>
       </c>
       <c r="E11" s="5">
-        <v>2129637</v>
+        <v>487837</v>
       </c>
       <c r="F11" s="5">
-        <v>3930173</v>
+        <v>877262</v>
       </c>
       <c r="G11" s="5">
-        <v>7446153</v>
+        <v>1250078</v>
       </c>
       <c r="H11" s="5">
-        <v>9716656</v>
+        <v>2280126</v>
       </c>
       <c r="I11" s="5">
-        <v>19286055</v>
-      </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5">
-        <v>66149</v>
-      </c>
-      <c r="D12" s="5">
-        <v>156844</v>
-      </c>
-      <c r="E12" s="5">
-        <v>255100</v>
-      </c>
-      <c r="F12" s="5">
-        <v>487837</v>
-      </c>
-      <c r="G12" s="5">
-        <v>877262</v>
-      </c>
-      <c r="H12" s="5">
-        <v>1250078</v>
-      </c>
-      <c r="I12" s="5">
-        <v>2280126</v>
-      </c>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+        <v>4336238</v>
+      </c>
+      <c r="J11" s="5">
+        <v>6656706</v>
+      </c>
+      <c r="K11" s="5">
+        <v>10185280</v>
+      </c>
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="16">
-        <f t="shared" ref="C13:H13" si="3">C12/C11</f>
+      <c r="B12" s="16">
+        <f t="shared" ref="B12:G12" si="6">B11/B10</f>
         <v>0.11546544711899318</v>
       </c>
-      <c r="D13" s="16">
-        <f t="shared" si="3"/>
+      <c r="C12" s="16">
+        <f t="shared" si="6"/>
         <v>0.11915828563527434</v>
       </c>
-      <c r="E13" s="16">
-        <f t="shared" si="3"/>
+      <c r="D12" s="16">
+        <f t="shared" si="6"/>
         <v>0.1197856723939338</v>
       </c>
-      <c r="F13" s="16">
-        <f t="shared" si="3"/>
+      <c r="E12" s="16">
+        <f t="shared" si="6"/>
         <v>0.12412608808823429</v>
       </c>
-      <c r="G13" s="16">
-        <f t="shared" si="3"/>
+      <c r="F12" s="16">
+        <f t="shared" si="6"/>
         <v>0.11781412495821668</v>
       </c>
-      <c r="H13" s="16">
-        <f t="shared" si="3"/>
+      <c r="G12" s="16">
+        <f t="shared" si="6"/>
         <v>0.12865310864149149</v>
       </c>
-      <c r="I13" s="16">
-        <f t="shared" ref="I13" si="4">I12/I11</f>
+      <c r="H12" s="16">
+        <f t="shared" ref="H12:K12" si="7">H11/H10</f>
         <v>0.1182266668844406</v>
       </c>
-      <c r="J13" s="3">
-        <f>AVERAGE(C13:I13)</f>
-        <v>0.12046134196008348</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
+      <c r="I12" s="16">
+        <f t="shared" si="7"/>
+        <v>0.11060395756275417</v>
+      </c>
+      <c r="J12" s="16">
+        <f t="shared" si="7"/>
+        <v>0.11832251260500587</v>
+      </c>
+      <c r="K12" s="16">
+        <f t="shared" si="7"/>
+        <v>0.11909118327956644</v>
+      </c>
+      <c r="L12" s="3">
+        <f>AVERAGE(B12:K12)</f>
+        <v>0.11912470471679108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="15">
-        <f t="shared" ref="C14:H14" si="5">C12/C9</f>
+      <c r="B13" s="15">
+        <f t="shared" ref="B13:G13" si="8">B11/B8</f>
         <v>2.9202707674196157E-3</v>
       </c>
-      <c r="D14" s="15">
-        <f t="shared" si="5"/>
+      <c r="C13" s="15">
+        <f t="shared" si="8"/>
         <v>3.3125170131881542E-3</v>
       </c>
-      <c r="E14" s="15">
-        <f t="shared" si="5"/>
+      <c r="D13" s="15">
+        <f t="shared" si="8"/>
         <v>3.1485621031555559E-3</v>
       </c>
-      <c r="F14" s="15">
-        <f t="shared" si="5"/>
+      <c r="E13" s="15">
+        <f t="shared" si="8"/>
         <v>3.1760336228067953E-3</v>
       </c>
-      <c r="G14" s="15">
-        <f t="shared" si="5"/>
+      <c r="F13" s="15">
+        <f t="shared" si="8"/>
         <v>3.2565227523484465E-3</v>
       </c>
-      <c r="H14" s="15">
-        <f t="shared" si="5"/>
+      <c r="G13" s="15">
+        <f t="shared" si="8"/>
         <v>3.0366289876346997E-3</v>
       </c>
-      <c r="I14" s="15">
-        <f t="shared" ref="I14" si="6">I12/I9</f>
+      <c r="H13" s="15">
+        <f t="shared" ref="H13:K13" si="9">H11/H8</f>
         <v>2.3973609458538287E-3</v>
       </c>
-      <c r="J14" s="3">
-        <f>AVERAGE(C14:I14)</f>
-        <v>3.0354137417724419E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+      <c r="I13" s="15">
+        <f t="shared" si="9"/>
+        <v>2.3898514048883812E-3</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="9"/>
+        <v>2.7224817107772215E-3</v>
+      </c>
+      <c r="K13" s="15">
+        <f t="shared" si="9"/>
+        <v>2.4948440897988541E-3</v>
+      </c>
+      <c r="L13" s="3">
+        <f>AVERAGE(B13:K13)</f>
+        <v>2.8855073397871548E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20">
         <v>30075</v>
       </c>
-      <c r="F16" s="20">
+      <c r="E15" s="20">
         <v>68141</v>
       </c>
-      <c r="G16" s="20">
+      <c r="F15" s="20">
         <v>814184</v>
       </c>
-      <c r="H16" s="20">
+      <c r="G15" s="20">
         <v>3829531</v>
       </c>
-      <c r="I16" s="20">
+      <c r="H15" s="20">
         <v>4637977</v>
       </c>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I15" s="20">
+        <v>15281532</v>
+      </c>
+      <c r="J15" s="20">
+        <v>22955094</v>
+      </c>
+      <c r="K15" s="20">
+        <v>29429298</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="15">
+        <f>D15/D4</f>
+        <v>2.728501994432894E-4</v>
+      </c>
+      <c r="E16" s="15">
+        <f>E15/E4</f>
+        <v>3.5309480724861185E-4</v>
+      </c>
+      <c r="F16" s="15">
+        <f>F15/F4</f>
+        <v>2.3218508527542681E-3</v>
+      </c>
+      <c r="G16" s="15">
+        <f>G15/G4</f>
+        <v>6.7841504304116647E-3</v>
+      </c>
+      <c r="H16" s="15">
+        <f>H15/H4</f>
+        <v>3.394570123073678E-3</v>
+      </c>
+      <c r="I16" s="15">
+        <f>I15/I4</f>
+        <v>7.7715104727285773E-3</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" ref="J16:K16" si="10">J15/J4</f>
+        <v>7.3542431719208975E-3</v>
+      </c>
+      <c r="K16" s="15">
+        <f t="shared" si="10"/>
+        <v>5.2258595843601673E-3</v>
+      </c>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B17" s="13"/>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
-      <c r="E17" s="15">
-        <f>E16/E5</f>
-        <v>2.728501994432894E-4</v>
-      </c>
-      <c r="F17" s="15">
-        <f>F16/F5</f>
-        <v>3.5309480724861185E-4</v>
-      </c>
-      <c r="G17" s="15">
-        <f>G16/G5</f>
-        <v>2.3218508527542681E-3</v>
-      </c>
-      <c r="H17" s="15">
-        <f>H16/H5</f>
-        <v>6.7841504304116647E-3</v>
-      </c>
-      <c r="I17" s="15">
-        <f>I16/I5</f>
-        <v>3.394570123073678E-3</v>
-      </c>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20">
+      <c r="C18" s="20"/>
+      <c r="D18" s="20">
         <v>2526</v>
       </c>
-      <c r="F19" s="20">
+      <c r="E18" s="20">
         <v>7751</v>
       </c>
-      <c r="G19" s="20">
+      <c r="F18" s="20">
         <v>26354</v>
       </c>
-      <c r="H19" s="20">
+      <c r="G18" s="20">
         <v>49345</v>
       </c>
-      <c r="I19" s="20">
+      <c r="H18" s="20">
         <v>101628</v>
       </c>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
+      <c r="I18" s="20">
+        <v>219754</v>
+      </c>
+      <c r="J18" s="20">
+        <v>501732</v>
+      </c>
+      <c r="K18" s="20">
+        <v>687170</v>
+      </c>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="17">
-        <f t="shared" ref="C20:I20" si="7">C19/C9</f>
+      <c r="B19" s="17">
+        <f t="shared" ref="B19:K19" si="11">B18/B8</f>
         <v>0</v>
       </c>
-      <c r="D20" s="17">
-        <f t="shared" si="7"/>
+      <c r="C19" s="17">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="E20" s="17">
-        <f t="shared" si="7"/>
+      <c r="D19" s="17">
+        <f t="shared" si="11"/>
         <v>3.1177059476953876E-5</v>
       </c>
-      <c r="F20" s="17">
-        <f t="shared" si="7"/>
+      <c r="E19" s="17">
+        <f t="shared" si="11"/>
         <v>5.0462422100774383E-5</v>
       </c>
-      <c r="G20" s="17">
-        <f t="shared" si="7"/>
+      <c r="F19" s="17">
+        <f t="shared" si="11"/>
         <v>9.7829839449777785E-5</v>
       </c>
-      <c r="H20" s="17">
-        <f t="shared" si="7"/>
+      <c r="G19" s="17">
+        <f t="shared" si="11"/>
         <v>1.1986648624712558E-4</v>
       </c>
-      <c r="I20" s="17">
-        <f t="shared" si="7"/>
+      <c r="H19" s="17">
+        <f t="shared" si="11"/>
         <v>1.0685330468808869E-4</v>
       </c>
-      <c r="J20" s="3">
-        <f>AVERAGE(C20:I20)</f>
-        <v>5.8027015994674327E-5</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="3"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
+      <c r="I19" s="17">
+        <f t="shared" si="11"/>
+        <v>1.2111406376445236E-4</v>
+      </c>
+      <c r="J19" s="17">
+        <f t="shared" si="11"/>
+        <v>2.0520001840424934E-4</v>
+      </c>
+      <c r="K19" s="17">
+        <f t="shared" si="11"/>
+        <v>1.6831957621067645E-4</v>
+      </c>
+      <c r="L19" s="2">
+        <f>AVERAGE(B19:K19)</f>
+        <v>9.0082277034209845E-5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="19">
+      <c r="B21" s="19">
         <v>34772</v>
       </c>
-      <c r="D22" s="20">
+      <c r="C21" s="20">
         <v>16732</v>
       </c>
-      <c r="E22" s="20">
+      <c r="D21" s="20">
         <v>21750</v>
       </c>
-      <c r="F22" s="20">
+      <c r="E21" s="20">
         <v>43725</v>
       </c>
-      <c r="G22" s="20">
+      <c r="F21" s="20">
         <v>80913</v>
       </c>
-      <c r="H22" s="20">
+      <c r="G21" s="20">
         <v>117730</v>
       </c>
-      <c r="I22" s="20">
+      <c r="H21" s="20">
         <v>235160</v>
       </c>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
+      <c r="I21" s="20">
+        <v>437491</v>
+      </c>
+      <c r="J21" s="20">
+        <v>335377</v>
+      </c>
+      <c r="K21" s="20">
+        <v>699386</v>
+      </c>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="15">
-        <f t="shared" ref="C23:I23" si="8">C22/C9</f>
+      <c r="B22" s="15">
+        <f t="shared" ref="B22:K22" si="12">B21/B8</f>
         <v>1.5350746817747037E-3</v>
       </c>
-      <c r="D23" s="15">
-        <f t="shared" si="8"/>
+      <c r="C22" s="15">
+        <f t="shared" si="12"/>
         <v>3.533768245177641E-4</v>
       </c>
-      <c r="E23" s="15">
-        <f t="shared" si="8"/>
+      <c r="D22" s="15">
+        <f t="shared" si="12"/>
         <v>2.684485525034627E-4</v>
       </c>
-      <c r="F23" s="15">
-        <f t="shared" si="8"/>
+      <c r="E22" s="15">
+        <f t="shared" si="12"/>
         <v>2.8466899836877304E-4</v>
       </c>
-      <c r="G23" s="18">
-        <f t="shared" si="8"/>
+      <c r="F22" s="18">
+        <f t="shared" si="12"/>
         <v>3.0036069664566558E-4</v>
       </c>
-      <c r="H23" s="18">
-        <f t="shared" si="8"/>
+      <c r="G22" s="18">
+        <f t="shared" si="12"/>
         <v>2.8598401916859041E-4</v>
       </c>
-      <c r="I23" s="18">
-        <f t="shared" si="8"/>
+      <c r="H22" s="18">
+        <f t="shared" si="12"/>
         <v>2.472509852644048E-4</v>
       </c>
-      <c r="J23" s="3">
-        <f>AVERAGE(C23:I23)</f>
-        <v>4.6788067974905208E-4</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I22" s="18">
+        <f t="shared" si="12"/>
+        <v>2.4111648875731054E-4</v>
+      </c>
+      <c r="J22" s="18">
+        <f t="shared" si="12"/>
+        <v>1.3716359843972864E-4</v>
+      </c>
+      <c r="K22" s="18">
+        <f t="shared" si="12"/>
+        <v>1.7131183714027119E-4</v>
+      </c>
+      <c r="L22" s="2">
+        <f>AVERAGE(B22:K22)</f>
+        <v>3.8247566825806749E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
+      <c r="F24" s="18"/>
       <c r="G24" s="18"/>
       <c r="H24" s="18"/>
       <c r="I24" s="18"/>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J25" s="18"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
+      <c r="J24" s="18"/>
+      <c r="K24" s="18">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L25" s="18"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="3">
-        <f>J7+J14-J20+J23</f>
-        <v>5.1005367263699105E-3</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E26" s="8"/>
+      <c r="B26" s="3">
+        <f>L6+L13-L19+L22</f>
+        <v>4.6965892556011758E-3</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="8"/>
+      <c r="E26" s="18"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="3">
-        <f>GTD!O12/100</f>
-        <v>5.1714285714285655E-3</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
+      <c r="B27" s="3">
+        <f>GTD!Q12/100</f>
+        <v>4.5699999999999951E-3</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="3">
-        <f>C27-C26</f>
-        <v>7.0891845058655006E-5</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
+      <c r="B28" s="3">
+        <f>B27-B26</f>
+        <v>-1.2658925560118071E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="11">
-        <f>0.12%+J14-I20+I23</f>
-        <v>4.3758114223487578E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
+      <c r="B30" s="11">
+        <f>0.12%+L13-K19+K22</f>
+        <v>4.0884996007167496E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="11">
-        <f>C30-J14</f>
-        <v>1.3403976805763159E-3</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B32" s="1"/>
-      <c r="C32" s="11"/>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
+      <c r="B31" s="11">
+        <f>B30-L13</f>
+        <v>1.2029922609295947E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="11"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="11">
-        <f>C30-C26</f>
-        <v>-7.2472530402115272E-4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B34" s="1" t="s">
+      <c r="B33" s="11">
+        <f>B30-B26</f>
+        <v>-6.0808965488442623E-4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="11">
-        <f>C27+C33</f>
-        <v>4.4467032674074128E-3</v>
-      </c>
+      <c r="B34" s="11">
+        <f>B27+B33</f>
+        <v>3.9619103451155688E-3</v>
+      </c>
+      <c r="C34" s="8"/>
       <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
+      <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B35" s="8"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
+      <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="M4" r:id="rId1" display="https://www.ie.vanguard/product-documentation/mifid-priips" xr:uid="{800CBD80-C22D-47C1-B2D9-A56B04DD2856}"/>
+    <hyperlink ref="O3" r:id="rId1" display="https://www.ie.vanguard/product-documentation/mifid-priips" xr:uid="{800CBD80-C22D-47C1-B2D9-A56B04DD2856}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
@@ -2214,767 +2655,983 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D805E6BE-6294-49D0-8387-463ECD6DFB0D}">
-  <dimension ref="B2:O40"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="38.42578125" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="16.28515625" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" customWidth="1"/>
+    <col min="1" max="1" width="38.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="16.28515625" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>35</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C4" s="1">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B3" s="1">
         <v>2013</v>
       </c>
-      <c r="D4" s="1">
+      <c r="C3" s="1">
         <v>2014</v>
       </c>
-      <c r="E4" s="1">
+      <c r="D3" s="1">
         <v>2015</v>
       </c>
-      <c r="F4" s="1">
+      <c r="E3" s="1">
         <v>2016</v>
       </c>
-      <c r="G4" s="1">
+      <c r="F3" s="1">
         <v>2017</v>
       </c>
-      <c r="H4" s="1">
+      <c r="G3" s="1">
         <v>2018</v>
       </c>
-      <c r="I4" s="1">
+      <c r="H3" s="1">
         <v>2019</v>
       </c>
-      <c r="J4" s="1">
+      <c r="I3" s="1">
         <v>2020</v>
       </c>
-      <c r="K4" s="1">
+      <c r="J3" s="1">
         <v>2021</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="K3" s="1">
+        <v>2022</v>
+      </c>
+      <c r="L3" s="1">
+        <v>2023</v>
+      </c>
+      <c r="M3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O4" s="30" t="s">
+      <c r="Q3" s="30" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="5">
+      <c r="B4" s="5">
         <v>43898122</v>
       </c>
+      <c r="C4" s="19">
+        <v>252031560</v>
+      </c>
+      <c r="D4" s="19">
+        <v>558122115</v>
+      </c>
+      <c r="E4" s="20">
+        <v>635252624</v>
+      </c>
+      <c r="F4" s="20">
+        <v>1382224416</v>
+      </c>
+      <c r="G4" s="20">
+        <v>1480869360</v>
+      </c>
+      <c r="H4" s="20">
+        <v>1971859507</v>
+      </c>
+      <c r="I4" s="20">
+        <v>1912680136</v>
+      </c>
+      <c r="J4" s="20">
+        <v>2825325240</v>
+      </c>
+      <c r="K4" s="20">
+        <v>2219774482</v>
+      </c>
+      <c r="L4" s="20">
+        <v>2529967642</v>
+      </c>
+      <c r="M4" s="20">
+        <v>2887900203</v>
+      </c>
+      <c r="N4" s="1"/>
+      <c r="Q4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="19">
+        <v>348524</v>
+      </c>
       <c r="D5" s="19">
-        <v>252031560</v>
-      </c>
-      <c r="E5" s="19">
-        <v>558122115</v>
+        <v>1087252</v>
+      </c>
+      <c r="E5" s="20">
+        <v>1277504</v>
       </c>
       <c r="F5" s="20">
-        <v>635252624</v>
+        <v>2493543</v>
       </c>
       <c r="G5" s="20">
-        <v>1382224416</v>
+        <v>3984684</v>
       </c>
       <c r="H5" s="20">
-        <v>1480869360</v>
+        <v>4162039</v>
       </c>
       <c r="I5" s="20">
-        <v>1971859507</v>
+        <v>4590519</v>
       </c>
       <c r="J5" s="20">
-        <v>1912680136</v>
+        <v>5410324</v>
       </c>
       <c r="K5" s="20">
-        <v>2825325240</v>
-      </c>
-      <c r="L5" s="1"/>
-      <c r="O5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="19">
-        <v>348524</v>
-      </c>
-      <c r="E6" s="19">
-        <v>1087252</v>
-      </c>
-      <c r="F6" s="20">
-        <v>1277504</v>
-      </c>
-      <c r="G6" s="20">
-        <v>2493543</v>
-      </c>
-      <c r="H6" s="20">
-        <v>3984684</v>
-      </c>
-      <c r="I6" s="20">
-        <v>4162039</v>
-      </c>
-      <c r="J6" s="20">
-        <v>4590519</v>
-      </c>
-      <c r="K6" s="20">
-        <v>5410324</v>
-      </c>
-      <c r="O6" t="s">
+        <v>5668186</v>
+      </c>
+      <c r="L5" s="20">
+        <v>5112583</v>
+      </c>
+      <c r="M5" s="20">
+        <v>5835147</v>
+      </c>
+      <c r="Q5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="14">
+      <c r="C6" s="14">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="E7" s="14">
+      <c r="D6" s="14">
         <f>((2/12)*0.29%)+((10/12)*0.25%)</f>
         <v>2.5666666666666667E-3</v>
       </c>
-      <c r="F7" s="14">
+      <c r="E6" s="14">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="G7" s="14">
+      <c r="F6" s="14">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="H7" s="14">
+      <c r="G6" s="14">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="I7" s="14">
+      <c r="H6" s="14">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="J7" s="14">
+      <c r="I6" s="14">
         <f>((114/366)*0.25%)+((252/366)*0.22%)</f>
         <v>2.29344262295082E-3</v>
       </c>
-      <c r="K7" s="14">
+      <c r="J6" s="14">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="L7" s="3">
-        <f>AVERAGE(D7:K7)</f>
-        <v>2.4950136612021862E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+      <c r="K6" s="14">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="L6" s="14">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="M6" s="14">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="N6" s="3">
+        <f>AVERAGE(C6:M6)</f>
+        <v>2.4145553899652264E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="19">
-        <f>(C5+D5)/2</f>
+      <c r="B7" s="5"/>
+      <c r="C7" s="19">
+        <f>(B4+C4)/2</f>
         <v>147964841</v>
       </c>
-      <c r="E8" s="19">
-        <f t="shared" ref="E8:K8" si="0">(D5+E5)/2</f>
+      <c r="D7" s="19">
+        <f t="shared" ref="D7:J7" si="0">(C4+D4)/2</f>
         <v>405076837.5</v>
       </c>
-      <c r="F8" s="19">
+      <c r="E7" s="19">
         <f t="shared" si="0"/>
         <v>596687369.5</v>
       </c>
-      <c r="G8" s="19">
+      <c r="F7" s="19">
         <f t="shared" si="0"/>
         <v>1008738520</v>
       </c>
-      <c r="H8" s="19">
+      <c r="G7" s="19">
         <f t="shared" si="0"/>
         <v>1431546888</v>
       </c>
-      <c r="I8" s="19">
+      <c r="H7" s="19">
         <f t="shared" si="0"/>
         <v>1726364433.5</v>
       </c>
-      <c r="J8" s="19">
+      <c r="I7" s="19">
         <f t="shared" si="0"/>
         <v>1942269821.5</v>
       </c>
-      <c r="K8" s="19">
+      <c r="J7" s="19">
         <f t="shared" si="0"/>
         <v>2369002688</v>
       </c>
-      <c r="L8" s="3"/>
-      <c r="O8" s="31" t="s">
+      <c r="K7" s="19">
+        <f t="shared" ref="K7" si="1">(J4+K4)/2</f>
+        <v>2522549861</v>
+      </c>
+      <c r="L7" s="19">
+        <f t="shared" ref="L7" si="2">(K4+L4)/2</f>
+        <v>2374871062</v>
+      </c>
+      <c r="M7" s="19">
+        <f t="shared" ref="M7" si="3">(L4+M4)/2</f>
+        <v>2708933922.5</v>
+      </c>
+      <c r="N7" s="3"/>
+      <c r="Q7" s="31" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="20">
-        <f>D6/E7</f>
+      <c r="B8" s="5"/>
+      <c r="C8" s="20">
+        <f>C5/D6</f>
         <v>135788571.42857143</v>
       </c>
-      <c r="E9" s="20">
-        <f t="shared" ref="E9:J9" si="1">E6/E7</f>
+      <c r="D8" s="20">
+        <f t="shared" ref="D8:I8" si="4">D5/D6</f>
         <v>423604675.32467532</v>
       </c>
-      <c r="F9" s="20">
-        <f t="shared" si="1"/>
+      <c r="E8" s="20">
+        <f t="shared" si="4"/>
         <v>511001600</v>
       </c>
-      <c r="G9" s="20">
-        <f t="shared" si="1"/>
+      <c r="F8" s="20">
+        <f t="shared" si="4"/>
         <v>997417200</v>
       </c>
-      <c r="H9" s="20">
-        <f t="shared" si="1"/>
+      <c r="G8" s="20">
+        <f t="shared" si="4"/>
         <v>1593873600</v>
       </c>
-      <c r="I9" s="20">
-        <f t="shared" si="1"/>
+      <c r="H8" s="20">
+        <f t="shared" si="4"/>
         <v>1664815600</v>
       </c>
-      <c r="J9" s="20">
-        <f t="shared" si="1"/>
+      <c r="I8" s="20">
+        <f t="shared" si="4"/>
         <v>2001584410.2930663</v>
       </c>
-      <c r="K9" s="20">
-        <f t="shared" ref="K9" si="2">K6/K7</f>
+      <c r="J8" s="20">
+        <f t="shared" ref="J8:M8" si="5">J5/J6</f>
         <v>2459238181.8181815</v>
       </c>
-      <c r="L9" s="3"/>
-      <c r="O9" s="31" t="s">
+      <c r="K8" s="20">
+        <f t="shared" si="5"/>
+        <v>2576448181.8181815</v>
+      </c>
+      <c r="L8" s="20">
+        <f t="shared" si="5"/>
+        <v>2323901363.6363635</v>
+      </c>
+      <c r="M8" s="20">
+        <f t="shared" si="5"/>
+        <v>2652339545.4545455</v>
+      </c>
+      <c r="N8" s="3"/>
+      <c r="Q8" s="31" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C10" s="5"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B9" s="5"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5">
+        <v>3325881</v>
+      </c>
+      <c r="D10" s="5">
+        <v>13386831</v>
+      </c>
+      <c r="E10" s="5">
+        <v>17405209</v>
+      </c>
+      <c r="F10" s="5">
+        <v>29020960</v>
+      </c>
+      <c r="G10" s="5">
+        <v>44723633</v>
+      </c>
+      <c r="H10" s="5">
+        <v>55691122</v>
+      </c>
+      <c r="I10" s="5">
+        <v>57139164</v>
+      </c>
+      <c r="J10" s="5">
+        <v>57452248</v>
+      </c>
+      <c r="K10" s="5">
+        <v>84998689</v>
+      </c>
+      <c r="L10" s="5">
+        <v>84796868</v>
+      </c>
+      <c r="M10" s="5">
+        <v>81019956</v>
+      </c>
+      <c r="N10" s="3"/>
+      <c r="Q10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5">
+        <v>298586</v>
+      </c>
       <c r="D11" s="5">
-        <v>3325881</v>
+        <v>1274164</v>
       </c>
       <c r="E11" s="5">
-        <v>13386831</v>
+        <v>1706810</v>
       </c>
       <c r="F11" s="5">
-        <v>17405209</v>
+        <v>3013440</v>
       </c>
       <c r="G11" s="5">
-        <v>29020960</v>
+        <v>4856073</v>
       </c>
       <c r="H11" s="5">
-        <v>44723633</v>
+        <v>5576288</v>
       </c>
       <c r="I11" s="5">
-        <v>55691122</v>
+        <v>6005283</v>
       </c>
       <c r="J11" s="5">
-        <v>57139164</v>
-      </c>
-      <c r="K11" s="5">
-        <v>57452248</v>
-      </c>
-      <c r="L11" s="3"/>
-      <c r="O11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5">
-        <v>298586</v>
-      </c>
-      <c r="E12" s="5">
-        <v>1274164</v>
-      </c>
-      <c r="F12" s="5">
-        <v>1706810</v>
-      </c>
-      <c r="G12" s="5">
-        <v>3013440</v>
-      </c>
-      <c r="H12" s="5">
-        <v>4856073</v>
-      </c>
-      <c r="I12" s="5">
-        <v>5576288</v>
-      </c>
-      <c r="J12" s="5">
-        <v>6005283</v>
-      </c>
-      <c r="K12" s="5">
         <f>6241303+431841</f>
         <v>6673144</v>
       </c>
-      <c r="L12" s="3"/>
-      <c r="O12" t="s">
+      <c r="K11" s="5">
+        <v>8726820</v>
+      </c>
+      <c r="L11" s="5">
+        <f>9165498+269259</f>
+        <v>9434757</v>
+      </c>
+      <c r="M11" s="5">
+        <f>9985172+2197734</f>
+        <v>12182906</v>
+      </c>
+      <c r="N11" s="3"/>
+      <c r="Q11" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="16">
-        <f>D12/D11</f>
+      <c r="C12" s="16">
+        <f>C11/C10</f>
         <v>8.9776513350898604E-2</v>
       </c>
-      <c r="E13" s="16">
-        <f t="shared" ref="E13:K13" si="3">E12/E11</f>
+      <c r="D12" s="16">
+        <f t="shared" ref="D12:M12" si="6">D11/D10</f>
         <v>9.5180405280383379E-2</v>
       </c>
-      <c r="F13" s="16">
-        <f t="shared" si="3"/>
+      <c r="E12" s="16">
+        <f t="shared" si="6"/>
         <v>9.8063171778057942E-2</v>
       </c>
-      <c r="G13" s="16">
-        <f t="shared" si="3"/>
+      <c r="F12" s="16">
+        <f t="shared" si="6"/>
         <v>0.10383667528572453</v>
       </c>
-      <c r="H13" s="16">
-        <f t="shared" si="3"/>
+      <c r="G12" s="16">
+        <f t="shared" si="6"/>
         <v>0.10857957357802306</v>
       </c>
-      <c r="I13" s="16">
-        <f t="shared" si="3"/>
+      <c r="H12" s="16">
+        <f t="shared" si="6"/>
         <v>0.10012884998079227</v>
       </c>
-      <c r="J13" s="16">
-        <f t="shared" si="3"/>
+      <c r="I12" s="16">
+        <f t="shared" si="6"/>
         <v>0.10509924506420849</v>
       </c>
-      <c r="K13" s="16">
-        <f t="shared" si="3"/>
+      <c r="J12" s="16">
+        <f t="shared" si="6"/>
         <v>0.11615113824614835</v>
       </c>
-      <c r="L13" s="3">
-        <f>AVERAGE(D13:K13)</f>
-        <v>0.10210194657052958</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
+      <c r="K12" s="16">
+        <f t="shared" si="6"/>
+        <v>0.10267005412283477</v>
+      </c>
+      <c r="L12" s="16">
+        <f t="shared" si="6"/>
+        <v>0.11126303627157551</v>
+      </c>
+      <c r="M12" s="16">
+        <f t="shared" si="6"/>
+        <v>0.1503692003979859</v>
+      </c>
+      <c r="N12" s="3">
+        <f>AVERAGE(C12:M12)</f>
+        <v>0.10737435121423934</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="15">
-        <f t="shared" ref="D14:K14" si="4">D12/D9</f>
+      <c r="C13" s="15">
+        <f t="shared" ref="C13:M13" si="7">C11/C8</f>
         <v>2.1989037579430207E-3</v>
       </c>
-      <c r="E14" s="15">
-        <f t="shared" si="4"/>
+      <c r="D13" s="15">
+        <f t="shared" si="7"/>
         <v>3.0079082555531439E-3</v>
       </c>
-      <c r="F14" s="15">
-        <f t="shared" si="4"/>
+      <c r="E13" s="15">
+        <f t="shared" si="7"/>
         <v>3.3401265279795599E-3</v>
       </c>
-      <c r="G14" s="15">
-        <f t="shared" si="4"/>
+      <c r="F13" s="15">
+        <f t="shared" si="7"/>
         <v>3.0212432671102925E-3</v>
       </c>
-      <c r="H14" s="15">
-        <f t="shared" si="4"/>
+      <c r="G13" s="15">
+        <f t="shared" si="7"/>
         <v>3.0467114832694385E-3</v>
       </c>
-      <c r="I14" s="15">
-        <f t="shared" si="4"/>
+      <c r="H13" s="15">
+        <f t="shared" si="7"/>
         <v>3.3494928807731019E-3</v>
       </c>
-      <c r="J14" s="15">
-        <f t="shared" si="4"/>
+      <c r="I13" s="15">
+        <f t="shared" si="7"/>
         <v>3.0002646748835955E-3</v>
       </c>
-      <c r="K14" s="15">
-        <f t="shared" si="4"/>
+      <c r="J13" s="15">
+        <f t="shared" si="7"/>
         <v>2.7135004853683442E-3</v>
       </c>
-      <c r="L14" s="3">
-        <f>AVERAGE(D14:K14)</f>
-        <v>2.9597689166100619E-3</v>
-      </c>
-      <c r="O14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+      <c r="K13" s="15">
+        <f t="shared" si="7"/>
+        <v>3.387151374355041E-3</v>
+      </c>
+      <c r="L13" s="15">
+        <f t="shared" si="7"/>
+        <v>4.0598784215336945E-3</v>
+      </c>
+      <c r="M13" s="15">
+        <f t="shared" si="7"/>
+        <v>4.5932678645456571E-3</v>
+      </c>
+      <c r="N13" s="3">
+        <f>AVERAGE(C13:M13)</f>
+        <v>3.2471317266649898E-3</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20">
+      <c r="B15" s="5"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20">
         <v>4397504</v>
       </c>
-      <c r="H16" s="20">
+      <c r="G15" s="20">
         <v>4131498</v>
       </c>
-      <c r="I16" s="20">
+      <c r="H15" s="20">
         <v>5461085</v>
       </c>
-      <c r="J16" s="20">
+      <c r="I15" s="20">
         <v>9560909</v>
       </c>
-      <c r="K16" s="20">
+      <c r="J15" s="20">
         <v>11232569</v>
       </c>
-      <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K15" s="20">
+        <v>13959222</v>
+      </c>
+      <c r="L15" s="20">
+        <v>22579958</v>
+      </c>
+      <c r="M15" s="20">
+        <v>42404847</v>
+      </c>
+      <c r="N15" s="3"/>
+      <c r="Q15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="15">
+        <f>F15/F4</f>
+        <v>3.1814689055528881E-3</v>
+      </c>
+      <c r="G16" s="15">
+        <f>G15/G4</f>
+        <v>2.7899138922018079E-3</v>
+      </c>
+      <c r="H16" s="15">
+        <f>H15/H4</f>
+        <v>2.7695101910726544E-3</v>
+      </c>
+      <c r="I16" s="15">
+        <f>I15/I4</f>
+        <v>4.9986972834855647E-3</v>
+      </c>
+      <c r="J16" s="15">
+        <f>J15/J4</f>
+        <v>3.9756729034141217E-3</v>
+      </c>
+      <c r="K16" s="15">
+        <f t="shared" ref="K16:M16" si="8">K15/K4</f>
+        <v>6.2885766609150524E-3</v>
+      </c>
+      <c r="L16" s="15">
+        <f t="shared" si="8"/>
+        <v>8.9249987332446681E-3</v>
+      </c>
+      <c r="M16" s="15">
+        <f t="shared" si="8"/>
+        <v>1.4683626170997572E-2</v>
+      </c>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C17" s="13"/>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="15">
-        <f>G16/G5</f>
-        <v>3.1814689055528881E-3</v>
-      </c>
-      <c r="H17" s="15">
-        <f>H16/H5</f>
-        <v>2.7899138922018079E-3</v>
-      </c>
-      <c r="I17" s="15">
-        <f>I16/I5</f>
-        <v>2.7695101910726544E-3</v>
-      </c>
-      <c r="J17" s="15">
-        <f>J16/J5</f>
-        <v>4.9986972834855647E-3</v>
-      </c>
-      <c r="K17" s="15">
-        <f>K16/K5</f>
-        <v>3.9756729034141217E-3</v>
-      </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20">
+      <c r="B18" s="5"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20">
         <v>46231</v>
       </c>
-      <c r="H19" s="20">
+      <c r="G18" s="20">
         <v>161281</v>
       </c>
-      <c r="I19" s="20">
+      <c r="H18" s="20">
         <v>215630</v>
       </c>
-      <c r="J19" s="20">
+      <c r="I18" s="20">
         <v>205976</v>
       </c>
-      <c r="K19" s="20">
+      <c r="J18" s="20">
         <v>241334</v>
       </c>
-      <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
+      <c r="K18" s="20">
+        <v>632998</v>
+      </c>
+      <c r="L18" s="20">
+        <v>375855</v>
+      </c>
+      <c r="M18" s="20">
+        <v>589129</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="17">
-        <f t="shared" ref="D20:K20" si="5">D19/D9</f>
+      <c r="C19" s="17">
+        <f t="shared" ref="C19:M19" si="9">C18/C8</f>
         <v>0</v>
       </c>
-      <c r="E20" s="17">
-        <f t="shared" si="5"/>
+      <c r="D19" s="17">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F20" s="17">
-        <f t="shared" si="5"/>
+      <c r="E19" s="17">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="G20" s="17">
-        <f t="shared" si="5"/>
+      <c r="F19" s="17">
+        <f t="shared" si="9"/>
         <v>4.6350714625735352E-5</v>
       </c>
-      <c r="H20" s="17">
-        <f t="shared" si="5"/>
+      <c r="G19" s="17">
+        <f t="shared" si="9"/>
         <v>1.0118807413586624E-4</v>
       </c>
-      <c r="I20" s="17">
-        <f t="shared" si="5"/>
+      <c r="H19" s="17">
+        <f t="shared" si="9"/>
         <v>1.2952185214987173E-4</v>
       </c>
-      <c r="J20" s="17">
-        <f t="shared" si="5"/>
+      <c r="I19" s="17">
+        <f t="shared" si="9"/>
         <v>1.0290647695934121E-4</v>
       </c>
-      <c r="K20" s="17">
-        <f t="shared" si="5"/>
+      <c r="J19" s="17">
+        <f t="shared" si="9"/>
         <v>9.8133642273549616E-5</v>
       </c>
-      <c r="L20" s="3">
-        <f>AVERAGE(D20:K20)</f>
-        <v>5.9762595018045511E-5</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
+      <c r="K19" s="17">
+        <f t="shared" si="9"/>
+        <v>2.4568629187539013E-4</v>
+      </c>
+      <c r="L19" s="17">
+        <f t="shared" si="9"/>
+        <v>1.6173448920046873E-4</v>
+      </c>
+      <c r="M19" s="17">
+        <f t="shared" si="9"/>
+        <v>2.2211673501970044E-4</v>
+      </c>
+      <c r="N19" s="2">
+        <f>AVERAGE(C19:M19)</f>
+        <v>1.0069438874908396E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5">
         <v>248141</v>
       </c>
-      <c r="E22" s="19">
+      <c r="D21" s="19">
         <v>437315</v>
       </c>
-      <c r="F22" s="20">
+      <c r="E21" s="20">
         <v>522563</v>
       </c>
-      <c r="G22" s="20">
+      <c r="F21" s="20">
         <v>913162</v>
       </c>
-      <c r="H22" s="20">
+      <c r="G21" s="20">
         <v>588927</v>
       </c>
-      <c r="I22" s="20">
+      <c r="H21" s="20">
         <v>821909</v>
       </c>
-      <c r="J22" s="20">
+      <c r="I21" s="20">
         <v>1066867</v>
       </c>
-      <c r="K22" s="20">
+      <c r="J21" s="20">
         <v>839604</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
+      <c r="K21" s="20">
+        <v>730734</v>
+      </c>
+      <c r="L21" s="20">
+        <v>782250</v>
+      </c>
+      <c r="M21" s="20">
+        <v>733911</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="15">
-        <f t="shared" ref="D23:K23" si="6">D22/D9</f>
+      <c r="C22" s="15">
+        <f t="shared" ref="C22:M22" si="10">C21/C8</f>
         <v>1.8274071034802002E-3</v>
       </c>
-      <c r="E23" s="15">
-        <f t="shared" si="6"/>
+      <c r="D22" s="15">
+        <f t="shared" si="10"/>
         <v>1.0323658483344553E-3</v>
       </c>
-      <c r="F23" s="15">
-        <f t="shared" si="6"/>
+      <c r="E22" s="15">
+        <f t="shared" si="10"/>
         <v>1.0226249780822603E-3</v>
       </c>
-      <c r="G23" s="15">
-        <f t="shared" si="6"/>
+      <c r="F22" s="15">
+        <f t="shared" si="10"/>
         <v>9.155266221597141E-4</v>
       </c>
-      <c r="H23" s="15">
-        <f t="shared" si="6"/>
+      <c r="G22" s="15">
+        <f t="shared" si="10"/>
         <v>3.6949416816992265E-4</v>
       </c>
-      <c r="I23" s="18">
-        <f t="shared" si="6"/>
+      <c r="H22" s="18">
+        <f t="shared" si="10"/>
         <v>4.9369371598872568E-4</v>
       </c>
-      <c r="J23" s="18">
-        <f t="shared" si="6"/>
+      <c r="I22" s="18">
+        <f t="shared" si="10"/>
         <v>5.3301124574795845E-4</v>
       </c>
-      <c r="K23" s="18">
-        <f t="shared" si="6"/>
+      <c r="J22" s="18">
+        <f t="shared" si="10"/>
         <v>3.414081670524723E-4</v>
       </c>
-      <c r="L23" s="3">
-        <f>AVERAGE(D23:K23)</f>
-        <v>8.1694148112696364E-4</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K22" s="18">
+        <f t="shared" si="10"/>
+        <v>2.8362068570085742E-4</v>
+      </c>
+      <c r="L22" s="18">
+        <f t="shared" si="10"/>
+        <v>3.3661067213969925E-4</v>
+      </c>
+      <c r="M22" s="18">
+        <f t="shared" si="10"/>
+        <v>2.7670326043199942E-4</v>
+      </c>
+      <c r="N22" s="2">
+        <f>AVERAGE(C22:M22)</f>
+        <v>6.756787697534786E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
+      <c r="H24" s="18"/>
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
       <c r="K24" s="18"/>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="L25" s="18"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
+      <c r="L24" s="18"/>
+      <c r="M24" s="18">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N25" s="18"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="3">
-        <f>L7+L14-L20+L23</f>
-        <v>6.2119614639211656E-3</v>
-      </c>
-      <c r="D26" t="s">
-        <v>88</v>
-      </c>
+      <c r="B26" s="3">
+        <f>N6+N13-N19+N22</f>
+        <v>6.2366714976346107E-3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="8"/>
       <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+      <c r="G26" s="18"/>
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
       <c r="K26" s="18"/>
       <c r="L26" s="18"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="3">
-        <f>AVERAGE(GTD!D19:J19)/100</f>
-        <v>6.3571428571428589E-3</v>
-      </c>
-      <c r="D27" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
+      <c r="B27" s="3">
+        <f>AVERAGE(GTD!D19:N19)/100</f>
+        <v>7.0818181818181839E-3</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="3">
-        <f>C27-C26</f>
-        <v>1.4518139322169336E-4</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
+      <c r="B28" s="3">
+        <f>B27-B26</f>
+        <v>8.4514668418357326E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="11">
-        <f>0.22%+L14-K20+AVERAGE(J23:K23)</f>
-        <v>5.4988449807367281E-3</v>
-      </c>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
+      <c r="B30" s="11">
+        <f>0.22%+N13-J19+AVERAGE(I22:J22)</f>
+        <v>5.7862077907916551E-3</v>
+      </c>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="11">
-        <f>C30-L14</f>
-        <v>2.5390760641266661E-3</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B32" s="1"/>
-      <c r="C32" s="11"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
+      <c r="B31" s="11">
+        <f>B30-N13</f>
+        <v>2.5390760641266653E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="11"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="11">
-        <f>C30-C26</f>
-        <v>-7.1311648318443752E-4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B34" s="1" t="s">
+      <c r="B33" s="11">
+        <f>B30-B26</f>
+        <v>-4.504637068429556E-4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="11">
-        <f>C27+C33</f>
-        <v>5.6440263739584214E-3</v>
-      </c>
+      <c r="B34" s="11">
+        <f>B27+B33</f>
+        <v>6.6313544749752283E-3</v>
+      </c>
+      <c r="D34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
+      <c r="G34" s="7"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
+      <c r="G40" s="7"/>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="O4" r:id="rId1" display="https://www.ie.vanguard/product-documentation/mifid-priips" xr:uid="{ED597E86-B6BB-480D-8B9C-8BC707A084BF}"/>
+    <hyperlink ref="Q3" r:id="rId1" display="https://www.ie.vanguard/product-documentation/mifid-priips" xr:uid="{ED597E86-B6BB-480D-8B9C-8BC707A084BF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -3575,7 +4232,7 @@
         <v>4.541101386275375E-3</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="18"/>
@@ -3593,7 +4250,7 @@
         <v>3.7799999999999995E-3</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
@@ -4241,7 +4898,7 @@
         <v>3.766799557477012E-3</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="18"/>
@@ -4259,7 +4916,7 @@
         <v>3.5500000000000015E-3</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
@@ -4904,7 +5561,7 @@
         <v>5.1141855558525795E-3</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="18"/>
@@ -4922,7 +5579,7 @@
         <v>5.416666666666666E-3</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
@@ -4983,13 +5640,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D55271D4-8CAB-4791-86A4-56A1D92A09CA}">
-  <dimension ref="B1:P41"/>
+  <dimension ref="B1:R41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="67.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C1" s="25">
         <v>2013</v>
       </c>
@@ -5023,14 +5680,20 @@
       <c r="M1" s="25">
         <v>2023</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="N1" s="25">
+        <v>2024</v>
+      </c>
+      <c r="O1" s="25">
+        <v>2025</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B2" s="21" t="s">
         <v>9</v>
       </c>
@@ -5061,13 +5724,21 @@
       <c r="K2" s="23">
         <v>18.329999999999998</v>
       </c>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
+      <c r="L2" s="23">
+        <v>-18.079999999999998</v>
+      </c>
+      <c r="M2" s="23">
+        <v>22.03</v>
+      </c>
+      <c r="N2" s="23">
+        <v>17.190000000000001</v>
+      </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
         <v>10</v>
       </c>
@@ -5098,13 +5769,21 @@
       <c r="K3" s="23">
         <v>18.899999999999999</v>
       </c>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
+      <c r="L3" s="23">
+        <v>-17.7</v>
+      </c>
+      <c r="M3" s="23">
+        <v>22.6</v>
+      </c>
+      <c r="N3" s="23">
+        <v>17.7</v>
+      </c>
       <c r="O3" s="23"/>
       <c r="P3" s="23"/>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
         <v>85</v>
       </c>
@@ -5135,13 +5814,21 @@
       <c r="K4" s="23">
         <v>18.399999999999999</v>
       </c>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
+      <c r="L4" s="23">
+        <v>-18.07</v>
+      </c>
+      <c r="M4" s="23">
+        <v>22</v>
+      </c>
+      <c r="N4" s="23">
+        <v>17.2</v>
+      </c>
       <c r="O4" s="23"/>
       <c r="P4" s="23"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>11</v>
       </c>
@@ -5178,19 +5865,30 @@
         <v>0.61000000000000121</v>
       </c>
       <c r="K5" s="22">
-        <f t="shared" ref="K5" si="1">K3-K2</f>
+        <f t="shared" ref="K5:N5" si="1">K3-K2</f>
         <v>0.57000000000000028</v>
       </c>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="26">
-        <f>AVERAGE(C5:K5)</f>
-        <v>0.56666666666666676</v>
-      </c>
-      <c r="P5" s="26"/>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="L5" s="22">
+        <f t="shared" si="1"/>
+        <v>0.37999999999999901</v>
+      </c>
+      <c r="M5" s="22">
+        <f t="shared" si="1"/>
+        <v>0.57000000000000028</v>
+      </c>
+      <c r="N5" s="22">
+        <f t="shared" si="1"/>
+        <v>0.50999999999999801</v>
+      </c>
+      <c r="O5" s="22"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="26">
+        <f>AVERAGE(C5:N5)</f>
+        <v>0.54666666666666652</v>
+      </c>
+      <c r="R5" s="26"/>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>12</v>
       </c>
@@ -5227,27 +5925,38 @@
         <v>-2.000000000000135E-2</v>
       </c>
       <c r="K6" s="22">
-        <f t="shared" ref="K6" si="3">K2-K4</f>
+        <f t="shared" ref="K6:N6" si="3">K2-K4</f>
         <v>-7.0000000000000284E-2</v>
       </c>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="26">
-        <f>AVERAGE(C6:K6)</f>
-        <v>2.2222222222223228E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="O7" s="27"/>
-      <c r="P7" s="27"/>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="L6" s="22">
+        <f t="shared" si="3"/>
+        <v>-9.9999999999980105E-3</v>
+      </c>
+      <c r="M6" s="22">
+        <f t="shared" si="3"/>
+        <v>3.0000000000001137E-2</v>
+      </c>
+      <c r="N6" s="22">
+        <f t="shared" si="3"/>
+        <v>-9.9999999999980105E-3</v>
+      </c>
+      <c r="O6" s="22"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="26"/>
+      <c r="R6" s="26">
+        <f>AVERAGE(C6:N6)</f>
+        <v>2.5000000000005018E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="21" t="s">
         <v>56</v>
       </c>
@@ -5280,11 +5989,15 @@
       <c r="M9" s="22">
         <v>23.84</v>
       </c>
-      <c r="N9" s="23"/>
-      <c r="O9" s="32"/>
-      <c r="P9" s="32"/>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="N9" s="22">
+        <v>17.86</v>
+      </c>
+      <c r="O9" s="22"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="32"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="21" t="s">
         <v>57</v>
       </c>
@@ -5317,11 +6030,15 @@
       <c r="M10" s="22">
         <v>24.2</v>
       </c>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="32"/>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="N10" s="22">
+        <v>18.2</v>
+      </c>
+      <c r="O10" s="22"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="32"/>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="21" t="s">
         <v>58</v>
       </c>
@@ -5354,11 +6071,15 @@
       <c r="M11" s="22">
         <v>23.61</v>
       </c>
-      <c r="N11" s="23"/>
-      <c r="O11" s="32"/>
-      <c r="P11" s="32"/>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="N11" s="22">
+        <v>17.73</v>
+      </c>
+      <c r="O11" s="22"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="32"/>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
         <v>11</v>
       </c>
@@ -5389,7 +6110,7 @@
         <v>0.48999999999999844</v>
       </c>
       <c r="K12" s="22">
-        <f t="shared" ref="K12:M12" si="5">K10-K9</f>
+        <f t="shared" ref="K12:N12" si="5">K10-K9</f>
         <v>0.41000000000000014</v>
       </c>
       <c r="L12" s="22">
@@ -5400,14 +6121,19 @@
         <f t="shared" si="5"/>
         <v>0.35999999999999943</v>
       </c>
-      <c r="N12" s="23"/>
-      <c r="O12" s="32">
-        <f>AVERAGE(E12:K12)</f>
-        <v>0.51714285714285657</v>
-      </c>
-      <c r="P12" s="32"/>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="N12" s="22">
+        <f t="shared" si="5"/>
+        <v>0.33999999999999986</v>
+      </c>
+      <c r="O12" s="22"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="32">
+        <f>AVERAGE(E12:N12)</f>
+        <v>0.45699999999999952</v>
+      </c>
+      <c r="R12" s="32"/>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="21" t="s">
         <v>12</v>
       </c>
@@ -5438,7 +6164,7 @@
         <v>0.10000000000000142</v>
       </c>
       <c r="K13" s="22">
-        <f t="shared" ref="K13:M13" si="7">K9-K11</f>
+        <f t="shared" ref="K13:N13" si="7">K9-K11</f>
         <v>0.11999999999999744</v>
       </c>
       <c r="L13" s="22">
@@ -5449,17 +6175,22 @@
         <f t="shared" si="7"/>
         <v>0.23000000000000043</v>
       </c>
-      <c r="N13" s="23"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="32">
-        <f>AVERAGE(E13:K13)</f>
-        <v>9.1428571428571637E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="N13" s="22">
+        <f t="shared" si="7"/>
+        <v>0.12999999999999901</v>
+      </c>
+      <c r="O13" s="22"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32">
+        <f>AVERAGE(E13:N13)</f>
+        <v>0.10999999999999988</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="21"/>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="33" t="s">
         <v>59</v>
       </c>
@@ -5490,12 +6221,20 @@
       <c r="K16" s="34">
         <v>-0.66</v>
       </c>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
+      <c r="L16" s="34">
+        <v>-17.5</v>
+      </c>
+      <c r="M16" s="34">
+        <v>7.86</v>
+      </c>
+      <c r="N16" s="34">
+        <v>12.06</v>
+      </c>
       <c r="O16" s="34"/>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P16" s="34"/>
+      <c r="Q16" s="34"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="33" t="s">
         <v>60</v>
       </c>
@@ -5526,12 +6265,20 @@
       <c r="K17" s="34">
         <v>0.1</v>
       </c>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
+      <c r="L17" s="34">
+        <v>-16.899999999999999</v>
+      </c>
+      <c r="M17" s="34">
+        <v>9.1</v>
+      </c>
+      <c r="N17" s="34">
+        <v>12.8</v>
+      </c>
       <c r="O17" s="34"/>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P17" s="34"/>
+      <c r="Q17" s="34"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="33" t="s">
         <v>61</v>
       </c>
@@ -5562,11 +6309,19 @@
       <c r="K18" s="34">
         <v>-0.24</v>
       </c>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="35"/>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="L18" s="34">
+        <v>-17.27</v>
+      </c>
+      <c r="M18" s="34">
+        <v>8.64</v>
+      </c>
+      <c r="N18" s="34">
+        <v>12.35</v>
+      </c>
+      <c r="O18" s="34"/>
+      <c r="P18" s="35"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="33" t="s">
         <v>11</v>
       </c>
@@ -5575,7 +6330,7 @@
         <v>0.45999999999999996</v>
       </c>
       <c r="D19" s="34">
-        <f t="shared" ref="D19:K19" si="8">D17-D16</f>
+        <f t="shared" ref="D19:N19" si="8">D17-D16</f>
         <v>0.51</v>
       </c>
       <c r="E19" s="34">
@@ -5606,15 +6361,26 @@
         <f t="shared" si="8"/>
         <v>0.76</v>
       </c>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="O19" s="35">
-        <f>AVERAGE(C19:K19)</f>
-        <v>0.63000000000000012</v>
-      </c>
-      <c r="P19" s="34"/>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="L19" s="34">
+        <f t="shared" si="8"/>
+        <v>0.60000000000000142</v>
+      </c>
+      <c r="M19" s="34">
+        <f t="shared" si="8"/>
+        <v>1.2399999999999993</v>
+      </c>
+      <c r="N19" s="34">
+        <f t="shared" si="8"/>
+        <v>0.74000000000000021</v>
+      </c>
+      <c r="O19" s="34"/>
+      <c r="Q19" s="35">
+        <f>AVERAGE(C19:N19)</f>
+        <v>0.68750000000000011</v>
+      </c>
+      <c r="R19" s="34"/>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="33" t="s">
         <v>12</v>
       </c>
@@ -5623,7 +6389,7 @@
         <v>-0.16999999999999993</v>
       </c>
       <c r="D20" s="34">
-        <f t="shared" ref="D20:K20" si="9">D16-D18</f>
+        <f t="shared" ref="D20:N20" si="9">D16-D18</f>
         <v>-3.0000000000000027E-2</v>
       </c>
       <c r="E20" s="34">
@@ -5654,15 +6420,26 @@
         <f t="shared" si="9"/>
         <v>-0.42000000000000004</v>
       </c>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
+      <c r="L20" s="34">
+        <f t="shared" si="9"/>
+        <v>-0.23000000000000043</v>
+      </c>
+      <c r="M20" s="34">
+        <f t="shared" si="9"/>
+        <v>-0.78000000000000025</v>
+      </c>
+      <c r="N20" s="34">
+        <f t="shared" si="9"/>
+        <v>-0.28999999999999915</v>
+      </c>
       <c r="O20" s="34"/>
-      <c r="P20" s="35">
-        <f>AVERAGE(C20:K20)</f>
-        <v>-0.24999999999999989</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q20" s="34"/>
+      <c r="R20" s="35">
+        <f>AVERAGE(C20:N20)</f>
+        <v>-0.29583333333333323</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="33" t="s">
         <v>70</v>
       </c>
@@ -5691,7 +6468,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B24" s="33" t="s">
         <v>71</v>
       </c>
@@ -5720,7 +6497,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="33" t="s">
         <v>72</v>
       </c>
@@ -5749,7 +6526,7 @@
         <v>24.86</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B26" s="33" t="s">
         <v>11</v>
       </c>
@@ -5787,13 +6564,15 @@
       </c>
       <c r="L26" s="34"/>
       <c r="M26" s="34"/>
-      <c r="O26" s="35">
+      <c r="N26" s="34"/>
+      <c r="O26" s="34"/>
+      <c r="Q26" s="35">
         <f>AVERAGE(D26:K26)</f>
         <v>0.3500000000000002</v>
       </c>
-      <c r="P26" s="34"/>
-    </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="R26" s="34"/>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="33" t="s">
         <v>12</v>
       </c>
@@ -5831,13 +6610,15 @@
       </c>
       <c r="L27" s="34"/>
       <c r="M27" s="34"/>
+      <c r="N27" s="34"/>
       <c r="O27" s="34"/>
-      <c r="P27" s="35">
+      <c r="Q27" s="34"/>
+      <c r="R27" s="35">
         <f>AVERAGE(D27:K27)</f>
         <v>0.2724999999999998</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>73</v>
       </c>
@@ -5866,7 +6647,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="33" t="s">
         <v>74</v>
       </c>
@@ -5895,7 +6676,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="33" t="s">
         <v>77</v>
       </c>
@@ -5924,7 +6705,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="33" t="s">
         <v>11</v>
       </c>
@@ -5963,13 +6744,15 @@
       </c>
       <c r="L33" s="34"/>
       <c r="M33" s="34"/>
-      <c r="O33" s="35">
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
+      <c r="Q33" s="35">
         <f>AVERAGE(D33:K33)</f>
         <v>0.38</v>
       </c>
-      <c r="P33" s="34"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="R33" s="34"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="33" t="s">
         <v>12</v>
       </c>
@@ -6008,13 +6791,15 @@
       </c>
       <c r="L34" s="34"/>
       <c r="M34" s="34"/>
+      <c r="N34" s="34"/>
       <c r="O34" s="34"/>
-      <c r="P34" s="35">
+      <c r="Q34" s="34"/>
+      <c r="R34" s="35">
         <f>AVERAGE(D34:K34)</f>
         <v>-0.15499999999999917</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="33" t="s">
         <v>75</v>
       </c>
@@ -6043,7 +6828,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="33" t="s">
         <v>86</v>
       </c>
@@ -6072,7 +6857,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="33" t="s">
         <v>76</v>
       </c>
@@ -6101,7 +6886,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="33" t="s">
         <v>11</v>
       </c>
@@ -6139,13 +6924,15 @@
       </c>
       <c r="L40" s="34"/>
       <c r="M40" s="34"/>
-      <c r="O40" s="35">
+      <c r="N40" s="34"/>
+      <c r="O40" s="34"/>
+      <c r="Q40" s="35">
         <f>AVERAGE(D40:K40)</f>
         <v>0.53625</v>
       </c>
-      <c r="P40" s="34"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="R40" s="34"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="33" t="s">
         <v>12</v>
       </c>
@@ -6183,8 +6970,10 @@
       </c>
       <c r="L41" s="34"/>
       <c r="M41" s="34"/>
+      <c r="N41" s="34"/>
       <c r="O41" s="34"/>
-      <c r="P41" s="35">
+      <c r="Q41" s="34"/>
+      <c r="R41" s="35">
         <f>AVERAGE(D41:K41)</f>
         <v>-0.19000000000000017</v>
       </c>
@@ -6289,8 +7078,8 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="J4" s="29">
-        <f>VWRL!L13</f>
-        <v>0.11606929673928755</v>
+        <f>VWRL!N12</f>
+        <v>0.11605882428458264</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -6609,13 +7398,13 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B41DF3-38FC-48D2-A2F4-45E9F93EAE67}">
-  <dimension ref="B1:G10"/>
+  <dimension ref="B1:J13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C1" s="1">
         <v>2017</v>
       </c>
@@ -6631,8 +7420,17 @@
       <c r="G1" s="1">
         <v>2021</v>
       </c>
-    </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>54</v>
       </c>
@@ -6641,7 +7439,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>52</v>
       </c>
@@ -6660,8 +7458,17 @@
       <c r="G3" s="6">
         <v>0.08</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="I3" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J3" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>53</v>
       </c>
@@ -6682,16 +7489,26 @@
         <v>0.92</v>
       </c>
       <c r="G4" s="6">
-        <f t="shared" ref="G4" si="1">100%-G3</f>
+        <f t="shared" ref="G4:H4" si="1">100%-G3</f>
         <v>0.92</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="6">
+        <f t="shared" si="1"/>
+        <v>0.92</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>52</v>
       </c>
@@ -6710,8 +7527,17 @@
       <c r="G7" s="6">
         <v>0.08</v>
       </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="I7" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>53</v>
       </c>
@@ -6724,7 +7550,7 @@
         <v>0.95</v>
       </c>
       <c r="E8" s="6">
-        <f t="shared" ref="E8:G8" si="3">100%-E7</f>
+        <f t="shared" ref="E8:H8" si="3">100%-E7</f>
         <v>0.92999999999999994</v>
       </c>
       <c r="F8" s="6">
@@ -6735,10 +7561,29 @@
         <f t="shared" si="3"/>
         <v>0.92</v>
       </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H8" s="6">
+        <v>0.94</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="31" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Vanguard EU/Vanguard-ETFs-KostenBepaling.xlsx
+++ b/Vanguard EU/Vanguard-ETFs-KostenBepaling.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/Vanguard EU/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1016" documentId="13_ncr:1_{383DE9F1-B669-4070-96E2-664D98CFDC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77B05692-6954-4C54-93F9-2EF556FA7325}"/>
+  <xr:revisionPtr revIDLastSave="1058" documentId="13_ncr:1_{383DE9F1-B669-4070-96E2-664D98CFDC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9314512-4F6F-4C48-B176-310634A020E5}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VWRL" sheetId="13" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="99">
   <si>
     <t>Dividend income</t>
   </si>
@@ -160,15 +160,6 @@
     <t>Estimated future costs</t>
   </si>
   <si>
-    <t>Estimated future costs (ex leakage)</t>
-  </si>
-  <si>
-    <t>Difference future and current costs</t>
-  </si>
-  <si>
-    <t>GTD estimation future</t>
-  </si>
-  <si>
     <t>Bookyear differs from calender year!</t>
   </si>
   <si>
@@ -335,6 +326,21 @@
   </si>
   <si>
     <t>2024: weird jump in dividend leakage. Tracking diff also jumps.</t>
+  </si>
+  <si>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>ITK</t>
+  </si>
+  <si>
+    <t>Lending</t>
+  </si>
+  <si>
+    <t>Dividendlekkage</t>
+  </si>
+  <si>
+    <t>Total costs</t>
   </si>
 </sst>
 </file>
@@ -783,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD89FDB9-F393-4A65-BDCD-E968CF6BDA63}">
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" customWidth="1"/>
@@ -819,7 +825,7 @@
         <v>35</v>
       </c>
       <c r="Q2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -863,7 +869,7 @@
         <v>31</v>
       </c>
       <c r="Q3" s="30" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -908,7 +914,7 @@
       </c>
       <c r="N4" s="1"/>
       <c r="Q4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -950,7 +956,7 @@
         <v>47677363</v>
       </c>
       <c r="Q5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -1047,7 +1053,7 @@
       </c>
       <c r="N7" s="3"/>
       <c r="Q7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -1116,7 +1122,7 @@
       <c r="M9" s="20"/>
       <c r="N9" s="3"/>
       <c r="Q9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -1203,7 +1209,7 @@
       </c>
       <c r="N11" s="3"/>
       <c r="Q11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -1312,7 +1318,7 @@
         <v>2.9073618967530193E-3</v>
       </c>
       <c r="Q13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -1363,7 +1369,7 @@
       </c>
       <c r="N15" s="3"/>
       <c r="Q15" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -1626,7 +1632,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -1647,14 +1653,14 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B26" s="3">
         <f>N6+N13-N19+N22</f>
         <v>5.5249130323926851E-3</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
@@ -1676,7 +1682,7 @@
         <v>5.5272727272727253E-3</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H27" s="2"/>
     </row>
@@ -1690,46 +1696,49 @@
       </c>
       <c r="H28" s="3"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="11">
-        <f>0.22%+N13-AVERAGE(K19:M19)+AVERAGE(K22:M22)</f>
-        <v>5.0820406762982313E-3</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="H30" s="2"/>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B29" s="3"/>
+      <c r="H29" s="3"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="11">
-        <f>B30-N13</f>
-        <v>2.174678779545212E-3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="11"/>
+      <c r="A32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="3">
+        <v>2.2000000000000001E-3</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="11">
-        <f>B30-B26</f>
-        <v>-4.4287235609445381E-4</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="B33" s="2">
+        <f>AVERAGE(L22:M22)</f>
+        <v>1.3821229845904385E-4</v>
+      </c>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="11">
-        <f>B27+B33</f>
-        <v>5.0844003711782715E-3</v>
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="3">
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -1743,18 +1752,23 @@
       <c r="M34" s="7"/>
       <c r="N34" s="7"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="7"/>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="2">
+        <f>-AVERAGE(L19:M19)</f>
+        <v>-1.9406900837230903E-4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" s="3">
+        <f>SUM(B32:B35)</f>
+        <v>5.1441432900867353E-3</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1780,7 +1794,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -1796,10 +1810,10 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -1837,7 +1851,7 @@
         <v>31</v>
       </c>
       <c r="O3" s="30" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -1876,7 +1890,7 @@
       </c>
       <c r="L4" s="1"/>
       <c r="O4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -1914,7 +1928,7 @@
         <v>4899038</v>
       </c>
       <c r="O5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -2000,7 +2014,7 @@
       </c>
       <c r="L7" s="3"/>
       <c r="O7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -2281,35 +2295,35 @@
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
       <c r="D16" s="15">
-        <f>D15/D4</f>
+        <f t="shared" ref="D16:I16" si="10">D15/D4</f>
         <v>2.728501994432894E-4</v>
       </c>
       <c r="E16" s="15">
-        <f>E15/E4</f>
+        <f t="shared" si="10"/>
         <v>3.5309480724861185E-4</v>
       </c>
       <c r="F16" s="15">
-        <f>F15/F4</f>
+        <f t="shared" si="10"/>
         <v>2.3218508527542681E-3</v>
       </c>
       <c r="G16" s="15">
-        <f>G15/G4</f>
+        <f t="shared" si="10"/>
         <v>6.7841504304116647E-3</v>
       </c>
       <c r="H16" s="15">
-        <f>H15/H4</f>
+        <f t="shared" si="10"/>
         <v>3.394570123073678E-3</v>
       </c>
       <c r="I16" s="15">
-        <f>I15/I4</f>
+        <f t="shared" si="10"/>
         <v>7.7715104727285773E-3</v>
       </c>
       <c r="J16" s="15">
-        <f t="shared" ref="J16:K16" si="10">J15/J4</f>
+        <f t="shared" ref="J16:K16" si="11">J15/J4</f>
         <v>7.3542431719208975E-3</v>
       </c>
       <c r="K16" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.2258595843601673E-3</v>
       </c>
       <c r="L16" s="3"/>
@@ -2363,43 +2377,43 @@
         <v>4</v>
       </c>
       <c r="B19" s="17">
-        <f t="shared" ref="B19:K19" si="11">B18/B8</f>
+        <f t="shared" ref="B19:K19" si="12">B18/B8</f>
         <v>0</v>
       </c>
       <c r="C19" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D19" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.1177059476953876E-5</v>
       </c>
       <c r="E19" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.0462422100774383E-5</v>
       </c>
       <c r="F19" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>9.7829839449777785E-5</v>
       </c>
       <c r="G19" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.1986648624712558E-4</v>
       </c>
       <c r="H19" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.0685330468808869E-4</v>
       </c>
       <c r="I19" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.2111406376445236E-4</v>
       </c>
       <c r="J19" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.0520001840424934E-4</v>
       </c>
       <c r="K19" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.6831957621067645E-4</v>
       </c>
       <c r="L19" s="2">
@@ -2461,43 +2475,43 @@
         <v>34</v>
       </c>
       <c r="B22" s="15">
-        <f t="shared" ref="B22:K22" si="12">B21/B8</f>
+        <f t="shared" ref="B22:K22" si="13">B21/B8</f>
         <v>1.5350746817747037E-3</v>
       </c>
       <c r="C22" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.533768245177641E-4</v>
       </c>
       <c r="D22" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.684485525034627E-4</v>
       </c>
       <c r="E22" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.8466899836877304E-4</v>
       </c>
       <c r="F22" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.0036069664566558E-4</v>
       </c>
       <c r="G22" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.8598401916859041E-4</v>
       </c>
       <c r="H22" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.472509852644048E-4</v>
       </c>
       <c r="I22" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.4111648875731054E-4</v>
       </c>
       <c r="J22" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.3716359843972864E-4</v>
       </c>
       <c r="K22" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.7131183714027119E-4</v>
       </c>
       <c r="L22" s="2">
@@ -2520,7 +2534,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -2541,14 +2555,14 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B26" s="3">
         <f>L6+L13-L19+L22</f>
         <v>4.6965892556011758E-3</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="18"/>
@@ -2569,7 +2583,7 @@
         <v>4.5699999999999951E-3</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -2581,68 +2595,58 @@
         <v>-1.2658925560118071E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="11">
-        <f>0.12%+L13-K19+K22</f>
-        <v>4.0884996007167496E-3</v>
-      </c>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B29" s="3"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="11">
-        <f>B30-L13</f>
-        <v>1.2029922609295947E-3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="11"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="3">
+        <v>1.1999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="11">
-        <f>B30-B26</f>
-        <v>-6.0808965488442623E-4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="11">
-        <f>B27+B33</f>
-        <v>3.9619103451155688E-3</v>
-      </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
+        <v>97</v>
+      </c>
+      <c r="B33" s="3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="2">
+        <f>AVERAGE(J22:K22)</f>
+        <v>1.542377177899999E-4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="2">
+        <f>-AVERAGE(J19:K19)</f>
+        <v>-1.8675979730746288E-4</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2655,7 +2659,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D805E6BE-6294-49D0-8387-463ECD6DFB0D}">
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" customWidth="1"/>
@@ -2670,7 +2674,7 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="10"/>
@@ -2691,7 +2695,7 @@
         <v>35</v>
       </c>
       <c r="Q2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -2735,7 +2739,7 @@
         <v>31</v>
       </c>
       <c r="Q3" s="30" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -2780,7 +2784,7 @@
       </c>
       <c r="N4" s="1"/>
       <c r="Q4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -2822,7 +2826,7 @@
         <v>5835147</v>
       </c>
       <c r="Q5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -2920,7 +2924,7 @@
       </c>
       <c r="N7" s="3"/>
       <c r="Q7" s="31" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -2974,7 +2978,7 @@
       </c>
       <c r="N8" s="3"/>
       <c r="Q8" s="31" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -3032,7 +3036,7 @@
       </c>
       <c r="N10" s="3"/>
       <c r="Q10" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -3078,7 +3082,7 @@
       </c>
       <c r="N11" s="3"/>
       <c r="Q11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -3187,7 +3191,7 @@
         <v>3.2471317266649898E-3</v>
       </c>
       <c r="Q13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -3238,7 +3242,7 @@
       </c>
       <c r="N15" s="3"/>
       <c r="Q15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -3501,7 +3505,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -3523,14 +3527,14 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B26" s="3">
         <f>N6+N13-N19+N22</f>
         <v>6.2366714976346107E-3</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
@@ -3552,7 +3556,7 @@
         <v>7.0818181818181839E-3</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -3564,70 +3568,66 @@
         <v>8.4514668418357326E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="11">
-        <f>0.22%+N13-J19+AVERAGE(I22:J22)</f>
-        <v>5.7862077907916551E-3</v>
-      </c>
-      <c r="D30" s="2"/>
-    </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="11">
-        <f>B30-N13</f>
-        <v>2.5390760641266653E-3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="11"/>
+      <c r="A32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="3">
+        <v>2.2000000000000001E-3</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="11">
-        <f>B30-B26</f>
-        <v>-4.504637068429556E-4</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="B33" s="3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="11">
-        <f>B27+B33</f>
-        <v>6.6313544749752283E-3</v>
-      </c>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-      <c r="N40" s="7"/>
+      <c r="A34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="2">
+        <f>AVERAGE(L22:M22)</f>
+        <v>3.0665696628584934E-4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="2">
+        <f>-AVERAGE(L19:M19)</f>
+        <v>-1.9192561211008459E-4</v>
+      </c>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3666,10 +3666,10 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
@@ -3754,7 +3754,7 @@
         <v>2223741</v>
       </c>
       <c r="M6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="J8" s="3"/>
       <c r="M8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="J9" s="3"/>
       <c r="M9" s="30" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
@@ -3869,7 +3869,7 @@
       <c r="I10" s="15"/>
       <c r="J10" s="3"/>
       <c r="M10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="J11" s="3"/>
       <c r="M11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
@@ -4225,14 +4225,14 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C27" s="3">
         <f>J7+J14-J20+J23</f>
         <v>4.541101386275375E-3</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="18"/>
@@ -4250,7 +4250,7 @@
         <v>3.7799999999999995E-3</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
@@ -4340,10 +4340,10 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="J5" s="1"/>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
@@ -4429,7 +4429,7 @@
         <v>1281554</v>
       </c>
       <c r="M6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
@@ -4463,7 +4463,7 @@
         <v>2.0311475409836065E-3</v>
       </c>
       <c r="M7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
@@ -4891,14 +4891,14 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C27" s="3">
         <f>J7+J14-J20+J23</f>
         <v>3.766799557477012E-3</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="18"/>
@@ -4916,7 +4916,7 @@
         <v>3.5500000000000015E-3</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
@@ -5003,10 +5003,10 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="J5" s="1"/>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
@@ -5092,7 +5092,7 @@
         <v>3098267</v>
       </c>
       <c r="M6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
@@ -5126,7 +5126,7 @@
         <v>1.8035128805620607E-3</v>
       </c>
       <c r="M7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
@@ -5554,14 +5554,14 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C27" s="3">
         <f>J7+J14-J20+J23</f>
         <v>5.1141855558525795E-3</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="18"/>
@@ -5579,7 +5579,7 @@
         <v>5.416666666666666E-3</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
@@ -5785,7 +5785,7 @@
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C4" s="24">
         <v>22.69</v>
@@ -5958,7 +5958,7 @@
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="21" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
@@ -5999,7 +5999,7 @@
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="21" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
@@ -6040,7 +6040,7 @@
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
@@ -6192,7 +6192,7 @@
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="33" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C16" s="34">
         <v>-3.96</v>
@@ -6236,7 +6236,7 @@
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="33" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C17" s="34">
         <v>-3.5</v>
@@ -6280,7 +6280,7 @@
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="33" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C18" s="34">
         <v>-3.79</v>
@@ -6441,7 +6441,7 @@
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="33" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D23">
         <v>7.16</v>
@@ -6470,7 +6470,7 @@
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B24" s="33" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D24">
         <v>7.4</v>
@@ -6499,7 +6499,7 @@
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="33" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D25">
         <v>6.83</v>
@@ -6620,7 +6620,7 @@
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D30">
         <v>-3.76</v>
@@ -6649,7 +6649,7 @@
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D31">
         <v>-3.2</v>
@@ -6678,7 +6678,7 @@
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="33" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D32">
         <v>-3.36</v>
@@ -6801,7 +6801,7 @@
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D37">
         <v>-3.91</v>
@@ -6830,7 +6830,7 @@
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="33" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D38">
         <v>-3.3</v>
@@ -6859,7 +6859,7 @@
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D39">
         <v>-3.59</v>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
@@ -7432,7 +7432,7 @@
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7441,7 +7441,7 @@
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C3" s="6">
         <v>0.05</v>
@@ -7470,7 +7470,7 @@
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C4" s="6">
         <f>100%-C3</f>
@@ -7505,12 +7505,12 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C7" s="6">
         <v>0.05</v>
@@ -7539,7 +7539,7 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C8" s="6">
         <f>100%-C7</f>
@@ -7550,7 +7550,7 @@
         <v>0.95</v>
       </c>
       <c r="E8" s="6">
-        <f t="shared" ref="E8:H8" si="3">100%-E7</f>
+        <f t="shared" ref="E8:G8" si="3">100%-E7</f>
         <v>0.92999999999999994</v>
       </c>
       <c r="F8" s="6">
@@ -7573,17 +7573,17 @@
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="31" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Vanguard EU/Vanguard-ETFs-KostenBepaling.xlsx
+++ b/Vanguard EU/Vanguard-ETFs-KostenBepaling.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/Vanguard EU/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1058" documentId="13_ncr:1_{383DE9F1-B669-4070-96E2-664D98CFDC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9314512-4F6F-4C48-B176-310634A020E5}"/>
+  <xr:revisionPtr revIDLastSave="1062" documentId="13_ncr:1_{383DE9F1-B669-4070-96E2-664D98CFDC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FC59109-6488-474F-BD54-616E5D75D707}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -331,9 +331,6 @@
     <t>TER</t>
   </si>
   <si>
-    <t>ITK</t>
-  </si>
-  <si>
     <t>Lending</t>
   </si>
   <si>
@@ -341,6 +338,9 @@
   </si>
   <si>
     <t>Total costs</t>
+  </si>
+  <si>
+    <t>Transaction costs</t>
   </si>
 </sst>
 </file>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B33" s="2">
         <f>AVERAGE(L22:M22)</f>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B35" s="2">
         <f>-AVERAGE(L19:M19)</f>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B36" s="3">
         <f>SUM(B32:B35)</f>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B33" s="3">
         <v>3.0000000000000001E-3</v>
@@ -2632,7 +2632,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B34" s="2">
         <f>AVERAGE(J22:K22)</f>
@@ -2641,7 +2641,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B35" s="2">
         <f>-AVERAGE(J19:K19)</f>
@@ -3583,7 +3583,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B33" s="3">
         <v>3.0000000000000001E-3</v>
@@ -3602,7 +3602,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B34" s="2">
         <f>AVERAGE(L22:M22)</f>
@@ -3611,7 +3611,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B35" s="2">
         <f>-AVERAGE(L19:M19)</f>

--- a/Vanguard EU/Vanguard-ETFs-KostenBepaling.xlsx
+++ b/Vanguard EU/Vanguard-ETFs-KostenBepaling.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/Vanguard EU/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1064" documentId="13_ncr:1_{383DE9F1-B669-4070-96E2-664D98CFDC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69D06FD4-6E3E-49EB-8414-AE0464945B0B}"/>
+  <xr:revisionPtr revIDLastSave="1083" documentId="13_ncr:1_{383DE9F1-B669-4070-96E2-664D98CFDC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CF0B47E-CC8E-43EB-98C3-B18ED53E9BF1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VWRL" sheetId="13" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="LeakgePerFund" sheetId="15" r:id="rId8"/>
     <sheet name="Lending" sheetId="18" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="99">
   <si>
     <t>Dividend income</t>
   </si>
@@ -332,9 +332,6 @@
   </si>
   <si>
     <t>Lending</t>
-  </si>
-  <si>
-    <t>Dividendlekkage</t>
   </si>
   <si>
     <t>Total costs</t>
@@ -523,6 +520,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1709,16 +1710,16 @@
         <v>94</v>
       </c>
       <c r="B32" s="3">
-        <v>2.2000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B33" s="2">
-        <f>AVERAGE(L22:M22)</f>
-        <v>1.3821229845904385E-4</v>
+        <f>AVERAGE(K22:M22)</f>
+        <v>1.4962283332066686E-4</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -1737,7 +1738,8 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>3.0000000000000001E-3</v>
+        <f>N13</f>
+        <v>2.9073618967530193E-3</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -1756,17 +1758,17 @@
         <v>95</v>
       </c>
       <c r="B35" s="2">
-        <f>-AVERAGE(L19:M19)</f>
-        <v>-1.9406900837230903E-4</v>
+        <f>-AVERAGE(K19:M19)</f>
+        <v>-1.749440537754551E-4</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B36" s="3">
         <f>SUM(B32:B35)</f>
-        <v>5.1441432900867353E-3</v>
+        <v>4.7820406762982314E-3</v>
       </c>
     </row>
   </sheetData>
@@ -2612,10 +2614,11 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>3.0000000000000001E-3</v>
+        <f>L13</f>
+        <v>2.8855073397871548E-3</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -2631,11 +2634,11 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B34" s="2">
-        <f>AVERAGE(J22:K22)</f>
-        <v>1.542377177899999E-4</v>
+        <f>AVERAGE(I22:K22)</f>
+        <v>1.8319730811243678E-4</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -2643,8 +2646,8 @@
         <v>95</v>
       </c>
       <c r="B35" s="2">
-        <f>-AVERAGE(J19:K19)</f>
-        <v>-1.8675979730746288E-4</v>
+        <f>-AVERAGE(I19:K19)</f>
+        <v>-1.6487788612645936E-4</v>
       </c>
     </row>
   </sheetData>
@@ -3582,10 +3585,11 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>3.0000000000000001E-3</v>
+        <f>N13</f>
+        <v>3.2471317266649898E-3</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -3601,11 +3605,11 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B34" s="2">
-        <f>AVERAGE(L22:M22)</f>
-        <v>3.0665696628584934E-4</v>
+        <f>AVERAGE(K22:M22)</f>
+        <v>2.9897820609085199E-4</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -3613,8 +3617,8 @@
         <v>95</v>
       </c>
       <c r="B35" s="2">
-        <f>-AVERAGE(L19:M19)</f>
-        <v>-1.9192561211008459E-4</v>
+        <f>-AVERAGE(K19:M19)</f>
+        <v>-2.0984583869851977E-4</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
@@ -4262,13 +4266,8 @@
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="11">
-        <f>I7+J14-I20+I23</f>
-        <v>3.6330311819945745E-3</v>
-      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="11"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
@@ -4928,13 +4927,8 @@
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="11">
-        <f>I7+J14-I20+I23</f>
-        <v>3.1635915771624466E-3</v>
-      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="11"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
@@ -5591,13 +5585,8 @@
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="11">
-        <f>I7+J14-I20+I23</f>
-        <v>4.7166622249069203E-3</v>
-      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="11"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
@@ -6438,7 +6427,7 @@
         <v>-0.29583333333333323</v>
       </c>
       <c r="T20" s="31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">

--- a/Vanguard EU/Vanguard-ETFs-KostenBepaling.xlsx
+++ b/Vanguard EU/Vanguard-ETFs-KostenBepaling.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/Vanguard EU/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1083" documentId="13_ncr:1_{383DE9F1-B669-4070-96E2-664D98CFDC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CF0B47E-CC8E-43EB-98C3-B18ED53E9BF1}"/>
+  <xr:revisionPtr revIDLastSave="1186" documentId="13_ncr:1_{383DE9F1-B669-4070-96E2-664D98CFDC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84BF6C09-70EC-4502-98DB-2A0E0EFD36F1}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VWRL" sheetId="13" r:id="rId1"/>
     <sheet name="VEVE" sheetId="16" r:id="rId2"/>
     <sheet name="VFEM" sheetId="17" r:id="rId3"/>
-    <sheet name="VWCG" sheetId="19" r:id="rId4"/>
-    <sheet name="VGEK" sheetId="20" r:id="rId5"/>
-    <sheet name="VJPA" sheetId="21" r:id="rId6"/>
-    <sheet name="GTD" sheetId="14" r:id="rId7"/>
-    <sheet name="LeakgePerFund" sheetId="15" r:id="rId8"/>
-    <sheet name="Lending" sheetId="18" r:id="rId9"/>
+    <sheet name="GTD" sheetId="14" r:id="rId4"/>
+    <sheet name="LeakgePerFund" sheetId="15" r:id="rId5"/>
+    <sheet name="Lending" sheetId="18" r:id="rId6"/>
+    <sheet name="arch-VWCG" sheetId="19" r:id="rId7"/>
+    <sheet name="arch-VGEK" sheetId="20" r:id="rId8"/>
+    <sheet name="arch-VJPA" sheetId="21" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191028" concurrentCalc="0"/>
   <extLst>
@@ -43,8 +43,80 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Gerben van Loon</author>
+  </authors>
+  <commentList>
+    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{BB6CECE5-43A2-43A9-9859-AD3A91778DBD}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Not taking alog deferred tax</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{941A112A-10CC-4EE0-B330-754D1369EA3B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Not taking alog deferred tax</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Gerben van Loon</author>
+  </authors>
+  <commentList>
+    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{D92005C8-4DCD-493A-A50F-C7CAD30D3444}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Not taking alog deferred tax</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{561A8048-76DB-460F-9472-297A8F469676}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Not taking alog deferred tax</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="101">
   <si>
     <t>Dividend income</t>
   </si>
@@ -298,9 +370,6 @@
     <t>FTSE Japan Index USD gross</t>
   </si>
   <si>
-    <t>2021: capital gains tax reservation high, taking on only real paid taxes as specifiek on page 637</t>
-  </si>
-  <si>
     <t>2015-2021</t>
   </si>
   <si>
@@ -341,6 +410,15 @@
   </si>
   <si>
     <t>2023: index diff because of Russian stocks</t>
+  </si>
+  <si>
+    <t>2021-2024: capital gains tax reservation high, taking on only real paid taxes as specifiek on page 637</t>
+  </si>
+  <si>
+    <t>2014-2025</t>
+  </si>
+  <si>
+    <t>2015-2025</t>
   </si>
 </sst>
 </file>
@@ -356,7 +434,7 @@
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -428,6 +506,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -459,7 +543,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -501,6 +585,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -788,8 +873,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD89FDB9-F393-4A65-BDCD-E968CF6BDA63}">
-  <dimension ref="A1:Q36"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD89FDB9-F393-4A65-BDCD-E968CF6BDA63}">
+  <dimension ref="A1:R36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" customWidth="1"/>
@@ -798,11 +883,11 @@
     <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="16.28515625" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" customWidth="1"/>
+    <col min="9" max="14" width="16.28515625" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>2</v>
       </c>
@@ -819,16 +904,17 @@
       <c r="L1" s="10"/>
       <c r="M1" s="10"/>
       <c r="N1" s="10"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O1" s="10"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>2013</v>
       </c>
@@ -865,14 +951,17 @@
       <c r="M3" s="1">
         <v>2024</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" s="30" t="s">
+      <c r="R3" s="30" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -912,12 +1001,15 @@
       <c r="M4" s="20">
         <v>27231939274</v>
       </c>
-      <c r="N4" s="1"/>
-      <c r="Q4" t="s">
+      <c r="N4" s="20">
+        <v>42324686694</v>
+      </c>
+      <c r="O4" s="1"/>
+      <c r="R4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -955,11 +1047,14 @@
       <c r="M5" s="20">
         <v>47677363</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="N5" s="20">
+        <v>73788802</v>
+      </c>
+      <c r="R5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -997,12 +1092,15 @@
       <c r="M6" s="14">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="N6" s="3">
-        <f>AVERAGE(C6:M6)</f>
-        <v>2.3721311475409842E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N6" s="14">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="O6" s="3">
+        <f>AVERAGE(C6:N6)</f>
+        <v>2.3577868852459019E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1012,7 +1110,7 @@
         <v>294940960.5</v>
       </c>
       <c r="D7" s="19">
-        <f t="shared" ref="D7:M7" si="0">(C4+D4)/2</f>
+        <f t="shared" ref="D7:N7" si="0">(C4+D4)/2</f>
         <v>675934486</v>
       </c>
       <c r="E7" s="19">
@@ -1051,12 +1149,16 @@
         <f t="shared" si="0"/>
         <v>22727651379</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="Q7" t="s">
+      <c r="N7" s="19">
+        <f t="shared" si="0"/>
+        <v>34778312984</v>
+      </c>
+      <c r="O7" s="3"/>
+      <c r="R7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1105,9 +1207,13 @@
         <f t="shared" si="1"/>
         <v>21671528636.363636</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N8" s="20">
+        <f t="shared" ref="N8" si="2">N5/N6</f>
+        <v>33540364545.454544</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B9" s="5"/>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
@@ -1120,12 +1226,13 @@
       <c r="K9" s="20"/>
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
-      <c r="N9" s="3"/>
-      <c r="Q9" t="s">
+      <c r="N9" s="20"/>
+      <c r="O9" s="3"/>
+      <c r="R9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -1163,9 +1270,12 @@
       <c r="M10" s="5">
         <v>465915642</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N10" s="5">
+        <v>681582910</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -1207,12 +1317,16 @@
         <f>55892990+1229091</f>
         <v>57122081</v>
       </c>
-      <c r="N11" s="3"/>
-      <c r="Q11" t="s">
+      <c r="N11" s="5">
+        <f>78871274+1562514</f>
+        <v>80433788</v>
+      </c>
+      <c r="O11" s="3"/>
+      <c r="R11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -1221,107 +1335,115 @@
         <v>9.7922058588519476E-2</v>
       </c>
       <c r="D12" s="16">
-        <f t="shared" ref="D12:I12" si="2">D11/D10</f>
+        <f t="shared" ref="D12:I12" si="3">D11/D10</f>
         <v>0.11047702125834585</v>
       </c>
       <c r="E12" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.12061500541151199</v>
       </c>
       <c r="F12" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.11782380307559541</v>
       </c>
       <c r="G12" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.12240510161750223</v>
       </c>
       <c r="H12" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.11610549719046288</v>
       </c>
       <c r="I12" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.12381152795958808</v>
       </c>
       <c r="J12" s="16">
-        <f t="shared" ref="J12:M12" si="3">J11/J10</f>
+        <f t="shared" ref="J12:M12" si="4">J11/J10</f>
         <v>0.11939435881277437</v>
       </c>
       <c r="K12" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.10888380847533533</v>
       </c>
       <c r="L12" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.11660711770243906</v>
       </c>
       <c r="M12" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.12260176703833438</v>
       </c>
-      <c r="N12" s="3">
-        <f>AVERAGE(C12:M12)</f>
-        <v>0.11605882428458264</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N12" s="16">
+        <f t="shared" ref="N12" si="5">N11/N10</f>
+        <v>0.11801027698889927</v>
+      </c>
+      <c r="O12" s="3">
+        <f>AVERAGE(C12:N12)</f>
+        <v>0.11622144534327571</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>33</v>
       </c>
       <c r="C13" s="15">
-        <f t="shared" ref="C13:M13" si="4">C11/C8</f>
+        <f t="shared" ref="C13:M13" si="6">C11/C8</f>
         <v>2.9793239033275593E-3</v>
       </c>
       <c r="D13" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.9008998452562927E-3</v>
       </c>
       <c r="E13" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3.3069112179469032E-3</v>
       </c>
       <c r="F13" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3.0780053070631006E-3</v>
       </c>
       <c r="G13" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3.1605818758204548E-3</v>
       </c>
       <c r="H13" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3.2255323865140995E-3</v>
       </c>
       <c r="I13" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.9719738836664353E-3</v>
       </c>
       <c r="J13" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.4575280393107383E-3</v>
       </c>
       <c r="K13" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.4391148993882679E-3</v>
       </c>
       <c r="L13" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.8252972401138408E-3</v>
       </c>
       <c r="M13" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.6358122658755269E-3</v>
       </c>
-      <c r="N13" s="3">
-        <f>AVERAGE(C13:M13)</f>
-        <v>2.9073618967530193E-3</v>
-      </c>
-      <c r="Q13" t="s">
+      <c r="N13" s="15">
+        <f t="shared" ref="N13" si="7">N11/N8</f>
+        <v>2.3981190750325503E-3</v>
+      </c>
+      <c r="O13" s="3">
+        <f>AVERAGE(C13:N13)</f>
+        <v>2.86492499494298E-3</v>
+      </c>
+      <c r="R13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
@@ -1333,9 +1455,10 @@
       <c r="K14" s="15"/>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N14" s="15"/>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1367,50 +1490,57 @@
       <c r="M15" s="20">
         <v>186032405</v>
       </c>
-      <c r="N15" s="3"/>
-      <c r="Q15" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N15" s="20">
+        <v>180407095</v>
+      </c>
+      <c r="O15" s="3"/>
+      <c r="R15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="F16" s="15">
-        <f t="shared" ref="F16:M16" si="5">F15/F4</f>
+        <f t="shared" ref="F16:N16" si="8">F15/F4</f>
         <v>7.5996950544667203E-4</v>
       </c>
       <c r="G16" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1.5227354256797665E-3</v>
       </c>
       <c r="H16" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2.8483776181205903E-3</v>
       </c>
       <c r="I16" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>8.3582065130645752E-3</v>
       </c>
       <c r="J16" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>4.8079554966156089E-3</v>
       </c>
       <c r="K16" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>9.6335825798747644E-3</v>
       </c>
       <c r="L16" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>7.9415016951763055E-3</v>
       </c>
       <c r="M16" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>6.8314049590150394E-3</v>
       </c>
-      <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N16" s="15">
+        <f t="shared" si="8"/>
+        <v>4.2624555334410718E-3</v>
+      </c>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
@@ -1422,9 +1552,10 @@
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N17" s="13"/>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1454,62 +1585,69 @@
       <c r="M18" s="20">
         <v>3848294</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N18" s="20">
+        <v>5427750</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
       <c r="C19" s="17">
-        <f t="shared" ref="C19:M19" si="6">C18/C8</f>
+        <f t="shared" ref="C19:N19" si="9">C18/C8</f>
         <v>0</v>
       </c>
       <c r="D19" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E19" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F19" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>4.0793344703854958E-5</v>
       </c>
       <c r="G19" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>7.2936029555201135E-5</v>
       </c>
       <c r="H19" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.1410591162373468E-4</v>
       </c>
       <c r="I19" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.294620261114799E-4</v>
       </c>
       <c r="J19" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.2380232376531009E-4</v>
       </c>
       <c r="K19" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.3669414458174718E-4</v>
       </c>
       <c r="L19" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.1056429480869639E-4</v>
       </c>
       <c r="M19" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.7757372193592168E-4</v>
       </c>
-      <c r="N19" s="2">
-        <f>AVERAGE(C19:M19)</f>
-        <v>9.1448345189631473E-5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N19" s="17">
+        <f t="shared" si="9"/>
+        <v>1.6182740031475237E-4</v>
+      </c>
+      <c r="O19" s="3">
+        <f>AVERAGE(C19:N19)</f>
+        <v>9.7313266450058206E-5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
       <c r="E20" s="13"/>
@@ -1521,9 +1659,10 @@
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N20" s="13"/>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -1561,62 +1700,69 @@
       <c r="M21" s="20">
         <v>2914559</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N21" s="20">
+        <v>5752698</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>34</v>
       </c>
       <c r="C22" s="15">
-        <f t="shared" ref="C22:M22" si="7">C21/C8</f>
+        <f t="shared" ref="C22:N22" si="10">C21/C8</f>
         <v>1.1474210887744186E-3</v>
       </c>
       <c r="D22" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>4.8929012207559125E-4</v>
       </c>
       <c r="E22" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>2.7223928217264459E-4</v>
       </c>
       <c r="F22" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1.979525684001794E-4</v>
       </c>
       <c r="G22" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>3.335391643126273E-4</v>
       </c>
       <c r="H22" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1.7092815043736145E-4</v>
       </c>
       <c r="I22" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>3.7372429923953455E-4</v>
       </c>
       <c r="J22" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>2.7158849079707569E-4</v>
       </c>
       <c r="K22" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1.7244390304391297E-4</v>
       </c>
       <c r="L22" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1.4193666812890526E-4</v>
       </c>
       <c r="M22" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1.3448792878918242E-4</v>
       </c>
-      <c r="N22" s="2">
-        <f>AVERAGE(C22:M22)</f>
-        <v>3.3686833328831208E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N22" s="18">
+        <f t="shared" si="10"/>
+        <v>1.7151566710623653E-4</v>
+      </c>
+      <c r="O22" s="3">
+        <f>AVERAGE(C22:N22)</f>
+        <v>3.2308894443980579E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
@@ -1628,11 +1774,12 @@
       <c r="K23" s="18"/>
       <c r="L23" s="18"/>
       <c r="M23" s="18"/>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N23" s="18"/>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -1646,21 +1793,24 @@
       <c r="M24" s="18">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="N25" s="18"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N24" s="18">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O25" s="18"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>41</v>
       </c>
       <c r="B26" s="3">
-        <f>N6+N13-N19+N22</f>
-        <v>5.5249130323926851E-3</v>
+        <f>O6+O13-O19+O22</f>
+        <v>5.4484875581786293E-3</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
@@ -1672,8 +1822,9 @@
       <c r="L26" s="18"/>
       <c r="M26" s="18"/>
       <c r="N26" s="18"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O26" s="18"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -1682,44 +1833,44 @@
         <v>5.5272727272727253E-3</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H27" s="2"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
       <c r="B28" s="3">
         <f>B27-B26</f>
-        <v>2.3596948800401821E-6</v>
+        <v>7.8785169094095983E-5</v>
       </c>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B29" s="3"/>
       <c r="H29" s="3"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B32" s="3">
         <v>1.9E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B33" s="2">
-        <f>AVERAGE(K22:M22)</f>
-        <v>1.4962283332066686E-4</v>
+        <f>AVERAGE(L22:N22)</f>
+        <v>1.493134213414414E-4</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -1732,14 +1883,15 @@
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O33" s="7"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <f>N13</f>
-        <v>2.9073618967530193E-3</v>
+        <f>O13</f>
+        <v>2.86492499494298E-3</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -1752,48 +1904,50 @@
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
       <c r="N34" s="7"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O34" s="7"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="2">
+        <f>-AVERAGE(L19:N19)</f>
+        <v>-1.8332180568645683E-4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>95</v>
-      </c>
-      <c r="B35" s="2">
-        <f>-AVERAGE(K19:M19)</f>
-        <v>-1.749440537754551E-4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>96</v>
       </c>
       <c r="B36" s="3">
         <f>SUM(B32:B35)</f>
-        <v>4.7820406762982314E-3</v>
+        <v>4.7309166105979645E-3</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="Q3" r:id="rId1" display="https://www.ie.vanguard/product-documentation/mifid-priips" xr:uid="{5F97709C-78A2-4F08-A418-EFDAFE8E468D}"/>
+    <hyperlink ref="R3" r:id="rId1" display="https://www.ie.vanguard/product-documentation/mifid-priips" xr:uid="{5F97709C-78A2-4F08-A418-EFDAFE8E468D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF345284-CA73-4DF5-92DD-8F9EBDED894B}">
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="16.28515625" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" customWidth="1"/>
+    <col min="7" max="12" width="16.28515625" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>43</v>
       </c>
@@ -1808,16 +1962,17 @@
       <c r="J1" s="10"/>
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M1" s="10"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>44</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>2015</v>
       </c>
@@ -1848,14 +2003,17 @@
       <c r="K3" s="1">
         <v>2024</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="30" t="s">
+      <c r="P3" s="30" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1889,12 +2047,15 @@
       <c r="K4" s="20">
         <v>5631475076</v>
       </c>
-      <c r="L4" s="1"/>
-      <c r="O4" t="s">
+      <c r="L4" s="20">
+        <v>8260348153</v>
+      </c>
+      <c r="M4" s="1"/>
+      <c r="P4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1928,11 +2089,14 @@
       <c r="K5" s="20">
         <v>4899038</v>
       </c>
-      <c r="O5" t="s">
+      <c r="L5" s="20">
+        <v>8274816</v>
+      </c>
+      <c r="P5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -1967,12 +2131,15 @@
       <c r="K6" s="14">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="L6" s="3">
-        <f>AVERAGE(B6:K6)</f>
-        <v>1.5186885245901637E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L6" s="14">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="M6" s="3">
+        <f>AVERAGE(B6:L6)</f>
+        <v>1.4897168405365124E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -2010,15 +2177,19 @@
         <v>2543846482</v>
       </c>
       <c r="K7" s="19">
-        <f t="shared" ref="K7" si="3">(J4+K4)/2</f>
+        <f t="shared" ref="K7:L7" si="3">(J4+K4)/2</f>
         <v>4376407580</v>
       </c>
-      <c r="L7" s="3"/>
-      <c r="O7" t="s">
+      <c r="L7" s="19">
+        <f t="shared" si="3"/>
+        <v>6945911614.5</v>
+      </c>
+      <c r="M7" s="3"/>
+      <c r="P7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -2062,9 +2233,13 @@
         <f t="shared" si="5"/>
         <v>4082531666.666667</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L8" s="20">
+        <f t="shared" ref="L8" si="6">L5/L6</f>
+        <v>6895680000.000001</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
@@ -2075,9 +2250,10 @@
       <c r="I9" s="20"/>
       <c r="J9" s="20"/>
       <c r="K9" s="20"/>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L9" s="20"/>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -2111,9 +2287,12 @@
       <c r="K10" s="5">
         <v>85525055</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L10" s="5">
+        <v>130712101</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -2147,107 +2326,118 @@
       <c r="K11" s="5">
         <v>10185280</v>
       </c>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L11" s="5">
+        <v>15434175</v>
+      </c>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="16">
-        <f t="shared" ref="B12:G12" si="6">B11/B10</f>
+        <f t="shared" ref="B12:G12" si="7">B11/B10</f>
         <v>0.11546544711899318</v>
       </c>
       <c r="C12" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.11915828563527434</v>
       </c>
       <c r="D12" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.1197856723939338</v>
       </c>
       <c r="E12" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.12412608808823429</v>
       </c>
       <c r="F12" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.11781412495821668</v>
       </c>
       <c r="G12" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.12865310864149149</v>
       </c>
       <c r="H12" s="16">
-        <f t="shared" ref="H12:K12" si="7">H11/H10</f>
+        <f t="shared" ref="H12:K12" si="8">H11/H10</f>
         <v>0.1182266668844406</v>
       </c>
       <c r="I12" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.11060395756275417</v>
       </c>
       <c r="J12" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.11832251260500587</v>
       </c>
       <c r="K12" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.11909118327956644</v>
       </c>
-      <c r="L12" s="3">
-        <f>AVERAGE(B12:K12)</f>
-        <v>0.11912470471679108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L12" s="16">
+        <f t="shared" ref="L12" si="9">L11/L10</f>
+        <v>0.11807762924719571</v>
+      </c>
+      <c r="M12" s="3">
+        <f>AVERAGE(B12:L12)</f>
+        <v>0.11902951603773695</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="15">
-        <f t="shared" ref="B13:G13" si="8">B11/B8</f>
+        <f t="shared" ref="B13:G13" si="10">B11/B8</f>
         <v>2.9202707674196157E-3</v>
       </c>
       <c r="C13" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>3.3125170131881542E-3</v>
       </c>
       <c r="D13" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>3.1485621031555559E-3</v>
       </c>
       <c r="E13" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>3.1760336228067953E-3</v>
       </c>
       <c r="F13" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>3.2565227523484465E-3</v>
       </c>
       <c r="G13" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>3.0366289876346997E-3</v>
       </c>
       <c r="H13" s="15">
-        <f t="shared" ref="H13:K13" si="9">H11/H8</f>
+        <f t="shared" ref="H13:K13" si="11">H11/H8</f>
         <v>2.3973609458538287E-3</v>
       </c>
       <c r="I13" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2.3898514048883812E-3</v>
       </c>
       <c r="J13" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2.7224817107772215E-3</v>
       </c>
       <c r="K13" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2.4948440897988541E-3</v>
       </c>
-      <c r="L13" s="3">
-        <f>AVERAGE(B13:K13)</f>
-        <v>2.8855073397871548E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L13" s="15">
+        <f t="shared" ref="L13" si="12">L11/L8</f>
+        <v>2.2382382883196434E-3</v>
+      </c>
+      <c r="M13" s="3">
+        <f>AVERAGE(B13:L13)</f>
+        <v>2.8266646987446537E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -2258,9 +2448,10 @@
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L14" s="15"/>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -2290,46 +2481,53 @@
       <c r="K15" s="20">
         <v>29429298</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L15" s="20">
+        <v>30751596</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
       <c r="D16" s="15">
-        <f t="shared" ref="D16:I16" si="10">D15/D4</f>
+        <f t="shared" ref="D16:I16" si="13">D15/D4</f>
         <v>2.728501994432894E-4</v>
       </c>
       <c r="E16" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>3.5309480724861185E-4</v>
       </c>
       <c r="F16" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2.3218508527542681E-3</v>
       </c>
       <c r="G16" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>6.7841504304116647E-3</v>
       </c>
       <c r="H16" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>3.394570123073678E-3</v>
       </c>
       <c r="I16" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7.7715104727285773E-3</v>
       </c>
       <c r="J16" s="15">
-        <f t="shared" ref="J16:K16" si="11">J15/J4</f>
+        <f t="shared" ref="J16:L16" si="14">J15/J4</f>
         <v>7.3542431719208975E-3</v>
       </c>
       <c r="K16" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>5.2258595843601673E-3</v>
       </c>
-      <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L16" s="15">
+        <f t="shared" si="14"/>
+        <v>3.7227965977235005E-3</v>
+      </c>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
@@ -2340,9 +2538,10 @@
       <c r="I17" s="13"/>
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L17" s="13"/>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2371,58 +2570,65 @@
       <c r="K18" s="20">
         <v>687170</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L18" s="20">
+        <v>891696</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
       <c r="B19" s="17">
-        <f t="shared" ref="B19:K19" si="12">B18/B8</f>
+        <f t="shared" ref="B19:L19" si="15">B18/B8</f>
         <v>0</v>
       </c>
       <c r="C19" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D19" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>3.1177059476953876E-5</v>
       </c>
       <c r="E19" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>5.0462422100774383E-5</v>
       </c>
       <c r="F19" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>9.7829839449777785E-5</v>
       </c>
       <c r="G19" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1.1986648624712558E-4</v>
       </c>
       <c r="H19" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1.0685330468808869E-4</v>
       </c>
       <c r="I19" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1.2111406376445236E-4</v>
       </c>
       <c r="J19" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2.0520001840424934E-4</v>
       </c>
       <c r="K19" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1.6831957621067645E-4</v>
       </c>
-      <c r="L19" s="2">
-        <f>AVERAGE(B19:K19)</f>
-        <v>9.0082277034209845E-5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L19" s="17">
+        <f t="shared" si="15"/>
+        <v>1.2931226507030487E-4</v>
+      </c>
+      <c r="M19" s="3">
+        <f>AVERAGE(B19:L19)</f>
+        <v>9.364863958294575E-5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B20" s="12"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -2433,9 +2639,10 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L20" s="13"/>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -2469,58 +2676,65 @@
       <c r="K21" s="20">
         <v>699386</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L21" s="20">
+        <v>754676</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>34</v>
       </c>
       <c r="B22" s="15">
-        <f t="shared" ref="B22:K22" si="13">B21/B8</f>
+        <f t="shared" ref="B22:L22" si="16">B21/B8</f>
         <v>1.5350746817747037E-3</v>
       </c>
       <c r="C22" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>3.533768245177641E-4</v>
       </c>
       <c r="D22" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2.684485525034627E-4</v>
       </c>
       <c r="E22" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2.8466899836877304E-4</v>
       </c>
       <c r="F22" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>3.0036069664566558E-4</v>
       </c>
       <c r="G22" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2.8598401916859041E-4</v>
       </c>
       <c r="H22" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2.472509852644048E-4</v>
       </c>
       <c r="I22" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2.4111648875731054E-4</v>
       </c>
       <c r="J22" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1.3716359843972864E-4</v>
       </c>
       <c r="K22" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1.7131183714027119E-4</v>
       </c>
-      <c r="L22" s="2">
-        <f>AVERAGE(B22:K22)</f>
-        <v>3.8247566825806749E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L22" s="18">
+        <f t="shared" si="16"/>
+        <v>1.0944185345027611E-4</v>
+      </c>
+      <c r="M22" s="3">
+        <f>AVERAGE(B22:L22)</f>
+        <v>3.5765441236645012E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -2531,11 +2745,12 @@
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
       <c r="K23" s="18"/>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L23" s="18"/>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -2549,21 +2764,24 @@
       <c r="K24" s="18">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L25" s="18"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L24" s="18">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M25" s="18"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>41</v>
       </c>
       <c r="B26" s="3">
-        <f>L6+L13-L19+L22</f>
-        <v>4.6965892556011758E-3</v>
+        <f>M6+M13-M19+M22</f>
+        <v>4.5803873120646701E-3</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="18"/>
@@ -2574,8 +2792,9 @@
       <c r="J26" s="18"/>
       <c r="K26" s="18"/>
       <c r="L26" s="18"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M26" s="18"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -2584,41 +2803,41 @@
         <v>4.5699999999999951E-3</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
       <c r="B28" s="3">
         <f>B27-B26</f>
-        <v>-1.2658925560118071E-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+        <v>-1.0387312064675039E-5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B29" s="3"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B32" s="3">
         <v>1.1999999999999999E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
       <c r="B33" s="3">
-        <f>L13</f>
-        <v>2.8855073397871548E-3</v>
+        <f>M13</f>
+        <v>2.8266646987446537E-3</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -2631,28 +2850,29 @@
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O33" s="7"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B34" s="2">
-        <f>AVERAGE(I22:K22)</f>
-        <v>1.8319730811243678E-4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+        <f>AVERAGE(J22:L22)</f>
+        <v>1.3930576301009198E-4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B35" s="2">
-        <f>-AVERAGE(I19:K19)</f>
-        <v>-1.6487788612645936E-4</v>
+        <f>-AVERAGE(J19:L19)</f>
+        <v>-1.6761061989507687E-4</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="O3" r:id="rId1" display="https://www.ie.vanguard/product-documentation/mifid-priips" xr:uid="{800CBD80-C22D-47C1-B2D9-A56B04DD2856}"/>
+    <hyperlink ref="P3" r:id="rId1" display="https://www.ie.vanguard/product-documentation/mifid-priips" xr:uid="{800CBD80-C22D-47C1-B2D9-A56B04DD2856}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
@@ -2660,8 +2880,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D805E6BE-6294-49D0-8387-463ECD6DFB0D}">
-  <dimension ref="A1:Q35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D805E6BE-6294-49D0-8387-463ECD6DFB0D}">
+  <dimension ref="A1:R35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" customWidth="1"/>
@@ -2670,11 +2890,11 @@
     <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="16.28515625" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" customWidth="1"/>
+    <col min="9" max="14" width="16.28515625" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>45</v>
       </c>
@@ -2691,16 +2911,17 @@
       <c r="L1" s="10"/>
       <c r="M1" s="10"/>
       <c r="N1" s="10"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O1" s="10"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>2013</v>
       </c>
@@ -2737,14 +2958,17 @@
       <c r="M3" s="1">
         <v>2024</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" s="30" t="s">
+      <c r="R3" s="30" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -2784,12 +3008,15 @@
       <c r="M4" s="20">
         <v>2887900203</v>
       </c>
-      <c r="N4" s="1"/>
-      <c r="Q4" t="s">
+      <c r="N4" s="20">
+        <v>3784111440</v>
+      </c>
+      <c r="O4" s="1"/>
+      <c r="R4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2827,11 +3054,14 @@
       <c r="M5" s="20">
         <v>5835147</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="N5" s="20">
+        <v>7044863</v>
+      </c>
+      <c r="R5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -2870,12 +3100,15 @@
       <c r="M6" s="14">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="N6" s="3">
-        <f>AVERAGE(C6:M6)</f>
-        <v>2.4145553899652264E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N6" s="14">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="O6" s="3">
+        <f>AVERAGE(C6:N6)</f>
+        <v>2.396675774134791E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -2921,15 +3154,19 @@
         <v>2374871062</v>
       </c>
       <c r="M7" s="19">
-        <f t="shared" ref="M7" si="3">(L4+M4)/2</f>
+        <f t="shared" ref="M7:N7" si="3">(L4+M4)/2</f>
         <v>2708933922.5</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="Q7" s="31" t="s">
+      <c r="N7" s="19">
+        <f t="shared" si="3"/>
+        <v>3336005821.5</v>
+      </c>
+      <c r="O7" s="3"/>
+      <c r="R7" s="31" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -2978,12 +3215,16 @@
         <f t="shared" si="5"/>
         <v>2652339545.4545455</v>
       </c>
-      <c r="N8" s="3"/>
-      <c r="Q8" s="31" t="s">
+      <c r="N8" s="20">
+        <f t="shared" ref="N8" si="6">N5/N6</f>
+        <v>3202210454.5454545</v>
+      </c>
+      <c r="O8" s="3"/>
+      <c r="R8" s="31" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B9" s="5"/>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
@@ -2996,9 +3237,10 @@
       <c r="K9" s="20"/>
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N9" s="20"/>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -3036,12 +3278,15 @@
       <c r="M10" s="5">
         <v>81019956</v>
       </c>
-      <c r="N10" s="3"/>
-      <c r="Q10" t="s">
+      <c r="N10" s="5">
+        <v>101567857</v>
+      </c>
+      <c r="O10" s="3"/>
+      <c r="R10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -3082,12 +3327,16 @@
         <f>9985172+2197734</f>
         <v>12182906</v>
       </c>
-      <c r="N11" s="3"/>
-      <c r="Q11" t="s">
+      <c r="N11" s="5">
+        <f>10797610+1638955</f>
+        <v>12436565</v>
+      </c>
+      <c r="O11" s="3"/>
+      <c r="R11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -3096,107 +3345,115 @@
         <v>8.9776513350898604E-2</v>
       </c>
       <c r="D12" s="16">
-        <f t="shared" ref="D12:M12" si="6">D11/D10</f>
+        <f t="shared" ref="D12:N12" si="7">D11/D10</f>
         <v>9.5180405280383379E-2</v>
       </c>
       <c r="E12" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.8063171778057942E-2</v>
       </c>
       <c r="F12" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.10383667528572453</v>
       </c>
       <c r="G12" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.10857957357802306</v>
       </c>
       <c r="H12" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.10012884998079227</v>
       </c>
       <c r="I12" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.10509924506420849</v>
       </c>
       <c r="J12" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.11615113824614835</v>
       </c>
       <c r="K12" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.10267005412283477</v>
       </c>
       <c r="L12" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.11126303627157551</v>
       </c>
       <c r="M12" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.1503692003979859</v>
       </c>
-      <c r="N12" s="3">
-        <f>AVERAGE(C12:M12)</f>
-        <v>0.10737435121423934</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N12" s="16">
+        <f t="shared" si="7"/>
+        <v>0.12244587379647087</v>
+      </c>
+      <c r="O12" s="3">
+        <f>AVERAGE(C12:N12)</f>
+        <v>0.10863031142942531</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>33</v>
       </c>
       <c r="C13" s="15">
-        <f t="shared" ref="C13:M13" si="7">C11/C8</f>
+        <f t="shared" ref="C13:N13" si="8">C11/C8</f>
         <v>2.1989037579430207E-3</v>
       </c>
       <c r="D13" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.0079082555531439E-3</v>
       </c>
       <c r="E13" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3401265279795599E-3</v>
       </c>
       <c r="F13" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.0212432671102925E-3</v>
       </c>
       <c r="G13" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.0467114832694385E-3</v>
       </c>
       <c r="H13" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3494928807731019E-3</v>
       </c>
       <c r="I13" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.0002646748835955E-3</v>
       </c>
       <c r="J13" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.7135004853683442E-3</v>
       </c>
       <c r="K13" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.387151374355041E-3</v>
       </c>
       <c r="L13" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.0598784215336945E-3</v>
       </c>
       <c r="M13" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.5932678645456571E-3</v>
       </c>
-      <c r="N13" s="3">
-        <f>AVERAGE(C13:M13)</f>
-        <v>3.2471317266649898E-3</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N13" s="15">
+        <f t="shared" si="8"/>
+        <v>3.8837438002697852E-3</v>
+      </c>
+      <c r="O13" s="3">
+        <f>AVERAGE(C13:N13)</f>
+        <v>3.3001827327987228E-3</v>
+      </c>
+      <c r="R13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
@@ -3208,9 +3465,13 @@
       <c r="K14" s="15"/>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N14" s="15"/>
+      <c r="O14" s="3"/>
+      <c r="R14" s="37" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -3242,12 +3503,15 @@
       <c r="M15" s="20">
         <v>42404847</v>
       </c>
-      <c r="N15" s="3"/>
-      <c r="Q15" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N15" s="20">
+        <v>24415146</v>
+      </c>
+      <c r="O15" s="3"/>
+      <c r="R15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
@@ -3272,20 +3536,24 @@
         <v>3.9756729034141217E-3</v>
       </c>
       <c r="K16" s="15">
-        <f t="shared" ref="K16:M16" si="8">K15/K4</f>
+        <f t="shared" ref="K16:N16" si="9">K15/K4</f>
         <v>6.2885766609150524E-3</v>
       </c>
       <c r="L16" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8.9249987332446681E-3</v>
       </c>
       <c r="M16" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.4683626170997572E-2</v>
       </c>
-      <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N16" s="15">
+        <f t="shared" si="9"/>
+        <v>6.4520155886318188E-3</v>
+      </c>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
@@ -3297,9 +3565,10 @@
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N17" s="13"/>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -3329,62 +3598,69 @@
       <c r="M18" s="20">
         <v>589129</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N18" s="20">
+        <v>1327030</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
       <c r="C19" s="17">
-        <f t="shared" ref="C19:M19" si="9">C18/C8</f>
+        <f t="shared" ref="C19:N19" si="10">C18/C8</f>
         <v>0</v>
       </c>
       <c r="D19" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E19" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F19" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.6350714625735352E-5</v>
       </c>
       <c r="G19" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0118807413586624E-4</v>
       </c>
       <c r="H19" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.2952185214987173E-4</v>
       </c>
       <c r="I19" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0290647695934121E-4</v>
       </c>
       <c r="J19" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9.8133642273549616E-5</v>
       </c>
       <c r="K19" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.4568629187539013E-4</v>
       </c>
       <c r="L19" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.6173448920046873E-4</v>
       </c>
       <c r="M19" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.2211673501970044E-4</v>
       </c>
-      <c r="N19" s="2">
-        <f>AVERAGE(C19:M19)</f>
-        <v>1.0069438874908396E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N19" s="17">
+        <f t="shared" si="10"/>
+        <v>4.144106138046971E-4</v>
+      </c>
+      <c r="O19" s="3">
+        <f>AVERAGE(C19:N19)</f>
+        <v>1.2683740750371838E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
       <c r="E20" s="13"/>
@@ -3396,9 +3672,10 @@
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N20" s="13"/>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -3436,62 +3713,69 @@
       <c r="M21" s="20">
         <v>733911</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N21" s="20">
+        <v>1039973</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>34</v>
       </c>
       <c r="C22" s="15">
-        <f t="shared" ref="C22:M22" si="10">C21/C8</f>
+        <f t="shared" ref="C22:N22" si="11">C21/C8</f>
         <v>1.8274071034802002E-3</v>
       </c>
       <c r="D22" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.0323658483344553E-3</v>
       </c>
       <c r="E22" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.0226249780822603E-3</v>
       </c>
       <c r="F22" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>9.155266221597141E-4</v>
       </c>
       <c r="G22" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.6949416816992265E-4</v>
       </c>
       <c r="H22" s="18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.9369371598872568E-4</v>
       </c>
       <c r="I22" s="18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.3301124574795845E-4</v>
       </c>
       <c r="J22" s="18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.414081670524723E-4</v>
       </c>
       <c r="K22" s="18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.8362068570085742E-4</v>
       </c>
       <c r="L22" s="18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.3661067213969925E-4</v>
       </c>
       <c r="M22" s="18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.7670326043199942E-4</v>
       </c>
-      <c r="N22" s="2">
-        <f>AVERAGE(C22:M22)</f>
-        <v>6.756787697534786E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N22" s="18">
+        <f t="shared" si="11"/>
+        <v>3.2476722400421416E-4</v>
+      </c>
+      <c r="O22" s="3">
+        <f>AVERAGE(C22:N22)</f>
+        <v>6.4643614094103989E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
@@ -3503,11 +3787,12 @@
       <c r="K23" s="18"/>
       <c r="L23" s="18"/>
       <c r="M23" s="18"/>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N23" s="18"/>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -3522,21 +3807,24 @@
       <c r="M24" s="18">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="N25" s="18"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N24" s="18">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O25" s="18"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>41</v>
       </c>
       <c r="B26" s="3">
-        <f>N6+N13-N19+N22</f>
-        <v>6.2366714976346107E-3</v>
+        <f>O6+O13-O19+O22</f>
+        <v>6.2164572403708342E-3</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
@@ -3548,8 +3836,9 @@
       <c r="L26" s="18"/>
       <c r="M26" s="18"/>
       <c r="N26" s="18"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O26" s="18"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -3558,38 +3847,38 @@
         <v>7.0818181818181839E-3</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
       <c r="B28" s="3">
         <f>B27-B26</f>
-        <v>8.4514668418357326E-4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+        <v>8.6536094144734968E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B32" s="3">
-        <v>2.2000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1.6999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
       <c r="B33" s="3">
-        <f>N13</f>
-        <v>3.2471317266649898E-3</v>
+        <f>O13</f>
+        <v>3.3001827327987228E-3</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -3602,23 +3891,24 @@
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O33" s="7"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B34" s="2">
-        <f>AVERAGE(K22:M22)</f>
-        <v>2.9897820609085199E-4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+        <f>AVERAGE(L22:N22)</f>
+        <v>3.1269371885863761E-4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B35" s="2">
-        <f>-AVERAGE(K19:M19)</f>
-        <v>-2.0984583869851977E-4</v>
+        <f>-AVERAGE(L19:N19)</f>
+        <v>-2.6608727934162207E-4</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
@@ -3631,2002 +3921,19 @@
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
       <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="Q3" r:id="rId1" display="https://www.ie.vanguard/product-documentation/mifid-priips" xr:uid="{ED597E86-B6BB-480D-8B9C-8BC707A084BF}"/>
+    <hyperlink ref="R3" r:id="rId1" display="https://www.ie.vanguard/product-documentation/mifid-priips" xr:uid="{ED597E86-B6BB-480D-8B9C-8BC707A084BF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BEA51A6-CEA5-4113-9E88-4EE6B698AC9B}">
-  <dimension ref="B2:M36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="38.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="16.28515625" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C4" s="1">
-        <v>2015</v>
-      </c>
-      <c r="D4" s="1">
-        <v>2016</v>
-      </c>
-      <c r="E4" s="1">
-        <v>2017</v>
-      </c>
-      <c r="F4" s="1">
-        <v>2018</v>
-      </c>
-      <c r="G4" s="1">
-        <v>2019</v>
-      </c>
-      <c r="H4" s="1">
-        <v>2020</v>
-      </c>
-      <c r="I4" s="1">
-        <v>2021</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="36">
-        <v>44377</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="19">
-        <v>286237679</v>
-      </c>
-      <c r="D5" s="20">
-        <v>502327318</v>
-      </c>
-      <c r="E5" s="20">
-        <v>1113048696</v>
-      </c>
-      <c r="F5" s="20">
-        <v>1679694691</v>
-      </c>
-      <c r="G5" s="20">
-        <v>1694765475</v>
-      </c>
-      <c r="H5" s="20">
-        <v>2009226586</v>
-      </c>
-      <c r="I5" s="20">
-        <v>2645377063</v>
-      </c>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="19">
-        <v>197844</v>
-      </c>
-      <c r="D6" s="20">
-        <v>500281</v>
-      </c>
-      <c r="E6" s="20">
-        <v>868002</v>
-      </c>
-      <c r="F6" s="20">
-        <v>1747960</v>
-      </c>
-      <c r="G6" s="20">
-        <v>1927300</v>
-      </c>
-      <c r="H6" s="20">
-        <v>2030488</v>
-      </c>
-      <c r="I6" s="20">
-        <v>2223741</v>
-      </c>
-      <c r="M6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="14">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="D7" s="14">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="E7" s="14">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="F7" s="14">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="G7" s="14">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="H7" s="14">
-        <f>((114/366)*0.12%)+((252/366)*0.1%)</f>
-        <v>1.0622950819672132E-3</v>
-      </c>
-      <c r="I7" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="J7" s="3">
-        <f>AVERAGE(D7:I7)</f>
-        <v>1.1437158469945355E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19">
-        <f t="shared" ref="D8" si="0">(C5+D5)/2</f>
-        <v>394282498.5</v>
-      </c>
-      <c r="E8" s="19">
-        <f t="shared" ref="E8" si="1">(D5+E5)/2</f>
-        <v>807688007</v>
-      </c>
-      <c r="F8" s="19">
-        <f t="shared" ref="F8" si="2">(E5+F5)/2</f>
-        <v>1396371693.5</v>
-      </c>
-      <c r="G8" s="19">
-        <f t="shared" ref="G8" si="3">(F5+G5)/2</f>
-        <v>1687230083</v>
-      </c>
-      <c r="H8" s="19">
-        <f t="shared" ref="H8:I8" si="4">(G5+H5)/2</f>
-        <v>1851996030.5</v>
-      </c>
-      <c r="I8" s="19">
-        <f t="shared" si="4"/>
-        <v>2327301824.5</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="M8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="20">
-        <f t="shared" ref="C9:H9" si="5">C6/C7</f>
-        <v>164870000</v>
-      </c>
-      <c r="D9" s="20">
-        <f t="shared" si="5"/>
-        <v>416900833.33333337</v>
-      </c>
-      <c r="E9" s="20">
-        <f t="shared" si="5"/>
-        <v>723335000.00000012</v>
-      </c>
-      <c r="F9" s="20">
-        <f t="shared" si="5"/>
-        <v>1456633333.3333335</v>
-      </c>
-      <c r="G9" s="20">
-        <f t="shared" si="5"/>
-        <v>1606083333.3333335</v>
-      </c>
-      <c r="H9" s="20">
-        <f t="shared" si="5"/>
-        <v>1911416172.8395061</v>
-      </c>
-      <c r="I9" s="20">
-        <f t="shared" ref="I9" si="6">I6/I7</f>
-        <v>2223741000</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="M9" s="30" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="3"/>
-      <c r="M10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="5">
-        <v>6453840</v>
-      </c>
-      <c r="D11" s="5">
-        <v>16699948</v>
-      </c>
-      <c r="E11" s="5">
-        <v>28612288</v>
-      </c>
-      <c r="F11" s="5">
-        <v>55451908</v>
-      </c>
-      <c r="G11" s="5">
-        <v>63355725</v>
-      </c>
-      <c r="H11" s="5">
-        <v>53087528</v>
-      </c>
-      <c r="I11" s="5">
-        <v>70651678</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="M11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5">
-        <v>449779</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1214196</v>
-      </c>
-      <c r="E12" s="5">
-        <v>2137859</v>
-      </c>
-      <c r="F12" s="5">
-        <v>4211322</v>
-      </c>
-      <c r="G12" s="5">
-        <v>4497447</v>
-      </c>
-      <c r="H12" s="5">
-        <v>5016404</v>
-      </c>
-      <c r="I12" s="5">
-        <v>5281336</v>
-      </c>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="16">
-        <f t="shared" ref="C13:H13" si="7">C12/C11</f>
-        <v>6.9691687429499341E-2</v>
-      </c>
-      <c r="D13" s="16">
-        <f t="shared" si="7"/>
-        <v>7.2706573697115709E-2</v>
-      </c>
-      <c r="E13" s="16">
-        <f t="shared" si="7"/>
-        <v>7.4718211979412488E-2</v>
-      </c>
-      <c r="F13" s="16">
-        <f t="shared" si="7"/>
-        <v>7.5945484148173939E-2</v>
-      </c>
-      <c r="G13" s="16">
-        <f t="shared" si="7"/>
-        <v>7.0987223333013716E-2</v>
-      </c>
-      <c r="H13" s="16">
-        <f t="shared" si="7"/>
-        <v>9.4493079429126936E-2</v>
-      </c>
-      <c r="I13" s="16">
-        <f t="shared" ref="I13" si="8">I12/I11</f>
-        <v>7.475174191899589E-2</v>
-      </c>
-      <c r="J13" s="3">
-        <f>AVERAGE(D13:I13)</f>
-        <v>7.7267052417639773E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="15">
-        <f t="shared" ref="C14:H14" si="9">C12/C9</f>
-        <v>2.7280827318493356E-3</v>
-      </c>
-      <c r="D14" s="15">
-        <f t="shared" si="9"/>
-        <v>2.9124336123098815E-3</v>
-      </c>
-      <c r="E14" s="15">
-        <f t="shared" si="9"/>
-        <v>2.9555586277450968E-3</v>
-      </c>
-      <c r="F14" s="15">
-        <f t="shared" si="9"/>
-        <v>2.8911338932241007E-3</v>
-      </c>
-      <c r="G14" s="15">
-        <f t="shared" si="9"/>
-        <v>2.8002575623929846E-3</v>
-      </c>
-      <c r="H14" s="15">
-        <f t="shared" si="9"/>
-        <v>2.6244436304773315E-3</v>
-      </c>
-      <c r="I14" s="15">
-        <f t="shared" ref="I14" si="10">I12/I9</f>
-        <v>2.3749780212713621E-3</v>
-      </c>
-      <c r="J14" s="3">
-        <f>AVERAGE(D14:I14)</f>
-        <v>2.7598008912367929E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20">
-        <v>4326489</v>
-      </c>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20">
-        <v>22002115</v>
-      </c>
-      <c r="I16" s="20">
-        <v>12654321</v>
-      </c>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="15">
-        <f>E16/E5</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="15">
-        <f>F16/F5</f>
-        <v>2.5757591681284894E-3</v>
-      </c>
-      <c r="G17" s="15">
-        <f>G16/G5</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="15">
-        <f>H16/H5</f>
-        <v>1.0950539452995274E-2</v>
-      </c>
-      <c r="I17" s="15">
-        <f>I16/I5</f>
-        <v>4.7835604145026189E-3</v>
-      </c>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20">
-        <v>89435</v>
-      </c>
-      <c r="F19" s="20">
-        <v>193993</v>
-      </c>
-      <c r="G19" s="20">
-        <v>209291</v>
-      </c>
-      <c r="H19" s="20">
-        <v>480474</v>
-      </c>
-      <c r="I19" s="20">
-        <v>607727</v>
-      </c>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="17">
-        <f t="shared" ref="C20:I20" si="11">C19/C9</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="17">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="E20" s="17">
-        <f t="shared" si="11"/>
-        <v>1.2364257225213764E-4</v>
-      </c>
-      <c r="F20" s="17">
-        <f t="shared" si="11"/>
-        <v>1.3317902011487676E-4</v>
-      </c>
-      <c r="G20" s="17">
-        <f t="shared" si="11"/>
-        <v>1.3031142012141336E-4</v>
-      </c>
-      <c r="H20" s="17">
-        <f t="shared" si="11"/>
-        <v>2.5137068882609241E-4</v>
-      </c>
-      <c r="I20" s="17">
-        <f t="shared" si="11"/>
-        <v>2.7329036969683069E-4</v>
-      </c>
-      <c r="J20" s="3">
-        <f>AVERAGE(D20:I20)</f>
-        <v>1.519656785018918E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="3"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="19">
-        <v>422303</v>
-      </c>
-      <c r="D22" s="20">
-        <v>602163</v>
-      </c>
-      <c r="E22" s="20">
-        <v>1099868</v>
-      </c>
-      <c r="F22" s="20">
-        <v>1252501</v>
-      </c>
-      <c r="G22" s="20">
-        <v>481133</v>
-      </c>
-      <c r="H22" s="20">
-        <v>891525</v>
-      </c>
-      <c r="I22" s="20">
-        <v>325824</v>
-      </c>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="15">
-        <f t="shared" ref="C23:I23" si="12">C22/C9</f>
-        <v>2.5614302177473162E-3</v>
-      </c>
-      <c r="D23" s="15">
-        <f t="shared" si="12"/>
-        <v>1.4443794587441856E-3</v>
-      </c>
-      <c r="E23" s="15">
-        <f t="shared" si="12"/>
-        <v>1.5205513351351722E-3</v>
-      </c>
-      <c r="F23" s="15">
-        <f t="shared" si="12"/>
-        <v>8.5986017986681605E-4</v>
-      </c>
-      <c r="G23" s="18">
-        <f t="shared" si="12"/>
-        <v>2.9956913817257301E-4</v>
-      </c>
-      <c r="H23" s="18">
-        <f t="shared" si="12"/>
-        <v>4.6642118690227161E-4</v>
-      </c>
-      <c r="I23" s="18">
-        <f t="shared" si="12"/>
-        <v>1.4652066045461231E-4</v>
-      </c>
-      <c r="J23" s="3">
-        <f>AVERAGE(D23:I23)</f>
-        <v>7.8955032654593838E-4</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J26" s="18"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="3">
-        <f>J7+J14-J20+J23</f>
-        <v>4.541101386275375E-3</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="3">
-        <f>AVERAGE(GTD!F26:J26)/100</f>
-        <v>3.7799999999999995E-3</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="3">
-        <f>C28-C27</f>
-        <v>-7.6110138627537554E-4</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="1"/>
-      <c r="C31" s="11"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B32" s="1"/>
-      <c r="C32" s="11"/>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" s="1"/>
-      <c r="C33" s="11"/>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C34" s="11"/>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="1"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="M9" r:id="rId1" display="https://www.ie.vanguard/product-documentation/mifid-priips" xr:uid="{B1E0BFAB-C50F-4C2F-9682-FD621075CC24}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6F59AA-9D8B-4A10-A65A-228471C4BA4F}">
-  <dimension ref="B2:M36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="38.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="16.28515625" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C4" s="1">
-        <v>2015</v>
-      </c>
-      <c r="D4" s="1">
-        <v>2016</v>
-      </c>
-      <c r="E4" s="1">
-        <v>2017</v>
-      </c>
-      <c r="F4" s="1">
-        <v>2018</v>
-      </c>
-      <c r="G4" s="1">
-        <v>2019</v>
-      </c>
-      <c r="H4" s="1">
-        <v>2020</v>
-      </c>
-      <c r="I4" s="1">
-        <v>2021</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="30"/>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="19">
-        <v>95809998</v>
-      </c>
-      <c r="D5" s="20">
-        <v>123443681</v>
-      </c>
-      <c r="E5" s="20">
-        <v>256132398</v>
-      </c>
-      <c r="F5" s="20">
-        <v>353569464</v>
-      </c>
-      <c r="G5" s="20">
-        <v>391574855</v>
-      </c>
-      <c r="H5" s="20">
-        <v>578659274</v>
-      </c>
-      <c r="I5" s="20">
-        <v>1090229427</v>
-      </c>
-      <c r="J5" s="1"/>
-      <c r="M5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="19">
-        <v>176697</v>
-      </c>
-      <c r="D6" s="20">
-        <v>222968</v>
-      </c>
-      <c r="E6" s="20">
-        <v>394440</v>
-      </c>
-      <c r="F6" s="20">
-        <v>734028</v>
-      </c>
-      <c r="G6" s="20">
-        <v>772839</v>
-      </c>
-      <c r="H6" s="20">
-        <v>756995</v>
-      </c>
-      <c r="I6" s="20">
-        <v>1281554</v>
-      </c>
-      <c r="M6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="14">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="D7" s="14">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="E7" s="14">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="F7" s="14">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="G7" s="14">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="H7" s="14">
-        <f>((114/366)*0.22%)+((252/366)*0.15%)</f>
-        <v>1.7180327868852462E-3</v>
-      </c>
-      <c r="I7" s="14">
-        <v>1.5E-3</v>
-      </c>
-      <c r="J7" s="3">
-        <f>AVERAGE(C7:I7)</f>
-        <v>2.0311475409836065E-3</v>
-      </c>
-      <c r="M7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19">
-        <f t="shared" ref="D8:I8" si="0">(C5+D5)/2</f>
-        <v>109626839.5</v>
-      </c>
-      <c r="E8" s="19">
-        <f t="shared" si="0"/>
-        <v>189788039.5</v>
-      </c>
-      <c r="F8" s="19">
-        <f t="shared" si="0"/>
-        <v>304850931</v>
-      </c>
-      <c r="G8" s="19">
-        <f t="shared" si="0"/>
-        <v>372572159.5</v>
-      </c>
-      <c r="H8" s="19">
-        <f t="shared" si="0"/>
-        <v>485117064.5</v>
-      </c>
-      <c r="I8" s="19">
-        <f t="shared" si="0"/>
-        <v>834444350.5</v>
-      </c>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="20">
-        <f t="shared" ref="C9:H9" si="1">C6/C7</f>
-        <v>80316818.181818172</v>
-      </c>
-      <c r="D9" s="20">
-        <f t="shared" si="1"/>
-        <v>101349090.90909091</v>
-      </c>
-      <c r="E9" s="20">
-        <f t="shared" si="1"/>
-        <v>179290909.09090909</v>
-      </c>
-      <c r="F9" s="20">
-        <f t="shared" si="1"/>
-        <v>333649090.90909088</v>
-      </c>
-      <c r="G9" s="20">
-        <f t="shared" si="1"/>
-        <v>351290454.5454545</v>
-      </c>
-      <c r="H9" s="20">
-        <f t="shared" si="1"/>
-        <v>440617318.70229</v>
-      </c>
-      <c r="I9" s="20">
-        <f t="shared" ref="I9" si="2">I6/I7</f>
-        <v>854369333.33333337</v>
-      </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="5">
-        <v>2910412</v>
-      </c>
-      <c r="D11" s="5">
-        <v>3697627</v>
-      </c>
-      <c r="E11" s="5">
-        <v>6020134</v>
-      </c>
-      <c r="F11" s="5">
-        <v>12310610</v>
-      </c>
-      <c r="G11" s="5">
-        <v>14080736</v>
-      </c>
-      <c r="H11" s="5">
-        <v>14853415</v>
-      </c>
-      <c r="I11" s="5">
-        <v>27718490</v>
-      </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5">
-        <v>95674</v>
-      </c>
-      <c r="D12" s="5">
-        <v>135521</v>
-      </c>
-      <c r="E12" s="5">
-        <v>217184</v>
-      </c>
-      <c r="F12" s="5">
-        <v>396984</v>
-      </c>
-      <c r="G12" s="5">
-        <v>725905</v>
-      </c>
-      <c r="H12" s="5">
-        <v>642854</v>
-      </c>
-      <c r="I12" s="5">
-        <v>1842818</v>
-      </c>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="16">
-        <f t="shared" ref="C13:H13" si="3">C12/C11</f>
-        <v>3.2873009044767545E-2</v>
-      </c>
-      <c r="D13" s="16">
-        <f t="shared" si="3"/>
-        <v>3.6650803339547226E-2</v>
-      </c>
-      <c r="E13" s="16">
-        <f t="shared" si="3"/>
-        <v>3.6076273385276809E-2</v>
-      </c>
-      <c r="F13" s="16">
-        <f t="shared" si="3"/>
-        <v>3.2247305373169971E-2</v>
-      </c>
-      <c r="G13" s="16">
-        <f t="shared" si="3"/>
-        <v>5.1553058021967031E-2</v>
-      </c>
-      <c r="H13" s="16">
-        <f t="shared" si="3"/>
-        <v>4.3279878734957582E-2</v>
-      </c>
-      <c r="I13" s="16">
-        <f t="shared" ref="I13" si="4">I12/I11</f>
-        <v>6.6483347397351011E-2</v>
-      </c>
-      <c r="J13" s="3">
-        <f>AVERAGE(C13:I13)</f>
-        <v>4.2737667899576733E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="15">
-        <f t="shared" ref="C14:H14" si="5">C12/C9</f>
-        <v>1.191207547383374E-3</v>
-      </c>
-      <c r="D14" s="15">
-        <f t="shared" si="5"/>
-        <v>1.3371703562843099E-3</v>
-      </c>
-      <c r="E14" s="15">
-        <f t="shared" si="5"/>
-        <v>1.2113497616874555E-3</v>
-      </c>
-      <c r="F14" s="15">
-        <f t="shared" si="5"/>
-        <v>1.1898249113112852E-3</v>
-      </c>
-      <c r="G14" s="15">
-        <f t="shared" si="5"/>
-        <v>2.0663954588213073E-3</v>
-      </c>
-      <c r="H14" s="15">
-        <f t="shared" si="5"/>
-        <v>1.4589848667168582E-3</v>
-      </c>
-      <c r="I14" s="15">
-        <f t="shared" ref="I14" si="6">I12/I9</f>
-        <v>2.1569336914402356E-3</v>
-      </c>
-      <c r="J14" s="3">
-        <f>AVERAGE(C14:I14)</f>
-        <v>1.5159809419492607E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20">
-        <v>2168054</v>
-      </c>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20">
-        <v>5733068</v>
-      </c>
-      <c r="I16" s="20">
-        <v>2494078</v>
-      </c>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="15">
-        <f>E16/E5</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="15">
-        <f>F16/F5</f>
-        <v>6.1319039700781404E-3</v>
-      </c>
-      <c r="G17" s="15">
-        <f>G16/G5</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="15">
-        <f>H16/H5</f>
-        <v>9.9075021478010564E-3</v>
-      </c>
-      <c r="I17" s="15">
-        <f>I16/I5</f>
-        <v>2.2876634387525114E-3</v>
-      </c>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20">
-        <v>4070</v>
-      </c>
-      <c r="F19" s="20">
-        <v>43784</v>
-      </c>
-      <c r="G19" s="20">
-        <v>81269</v>
-      </c>
-      <c r="H19" s="20">
-        <v>147489</v>
-      </c>
-      <c r="I19" s="20">
-        <v>85284</v>
-      </c>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="17">
-        <f t="shared" ref="C20:I20" si="7">C19/C9</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="17">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="E20" s="17">
-        <f t="shared" si="7"/>
-        <v>2.2700537470844743E-5</v>
-      </c>
-      <c r="F20" s="17">
-        <f t="shared" si="7"/>
-        <v>1.3122769158669699E-4</v>
-      </c>
-      <c r="G20" s="17">
-        <f t="shared" si="7"/>
-        <v>2.3134417388356439E-4</v>
-      </c>
-      <c r="H20" s="17">
-        <f t="shared" si="7"/>
-        <v>3.3473264381524061E-4</v>
-      </c>
-      <c r="I20" s="17">
-        <f t="shared" si="7"/>
-        <v>9.9820998568924912E-5</v>
-      </c>
-      <c r="J20" s="3">
-        <f>AVERAGE(C20:I20)</f>
-        <v>1.1711800647503882E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="3"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="19">
-        <v>57821</v>
-      </c>
-      <c r="D22" s="20">
-        <v>32497</v>
-      </c>
-      <c r="E22" s="20">
-        <v>59576</v>
-      </c>
-      <c r="F22" s="20">
-        <v>92342</v>
-      </c>
-      <c r="G22" s="20">
-        <v>59886</v>
-      </c>
-      <c r="H22" s="20">
-        <v>127784</v>
-      </c>
-      <c r="I22" s="20">
-        <v>211398</v>
-      </c>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="15">
-        <f t="shared" ref="C23:I23" si="8">C22/C9</f>
-        <v>7.1991148689564625E-4</v>
-      </c>
-      <c r="D23" s="15">
-        <f t="shared" si="8"/>
-        <v>3.2064421800437733E-4</v>
-      </c>
-      <c r="E23" s="15">
-        <f t="shared" si="8"/>
-        <v>3.322867863299868E-4</v>
-      </c>
-      <c r="F23" s="15">
-        <f t="shared" si="8"/>
-        <v>2.7676382917272914E-4</v>
-      </c>
-      <c r="G23" s="18">
-        <f t="shared" si="8"/>
-        <v>1.7047431612535083E-4</v>
-      </c>
-      <c r="H23" s="18">
-        <f t="shared" si="8"/>
-        <v>2.9001129682407981E-4</v>
-      </c>
-      <c r="I23" s="18">
-        <f t="shared" si="8"/>
-        <v>2.4743163378211137E-4</v>
-      </c>
-      <c r="J23" s="3">
-        <f>AVERAGE(C23:I23)</f>
-        <v>3.3678908101918311E-4</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J26" s="18"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="3">
-        <f>J7+J14-J20+J23</f>
-        <v>3.766799557477012E-3</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="3">
-        <f>AVERAGE(GTD!E33:J33)/100</f>
-        <v>3.5500000000000015E-3</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="3">
-        <f>C28-C27</f>
-        <v>-2.1679955747701046E-4</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="1"/>
-      <c r="C31" s="11"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B32" s="1"/>
-      <c r="C32" s="11"/>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" s="1"/>
-      <c r="C33" s="11"/>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C34" s="11"/>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="1"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17C62D4-0311-4C15-9CAB-0AC451E6E3A5}">
-  <dimension ref="B2:M36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="38.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="16.28515625" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C4" s="1">
-        <v>2015</v>
-      </c>
-      <c r="D4" s="1">
-        <v>2016</v>
-      </c>
-      <c r="E4" s="1">
-        <v>2017</v>
-      </c>
-      <c r="F4" s="1">
-        <v>2018</v>
-      </c>
-      <c r="G4" s="1">
-        <v>2019</v>
-      </c>
-      <c r="H4" s="1">
-        <v>2020</v>
-      </c>
-      <c r="I4" s="1">
-        <v>2021</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="30"/>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="19">
-        <v>590786984</v>
-      </c>
-      <c r="D5" s="20">
-        <v>722285064</v>
-      </c>
-      <c r="E5" s="20">
-        <v>1085744450</v>
-      </c>
-      <c r="F5" s="20">
-        <v>2020467317</v>
-      </c>
-      <c r="G5" s="20">
-        <v>1829551730</v>
-      </c>
-      <c r="H5" s="20">
-        <v>1685328502</v>
-      </c>
-      <c r="I5" s="20">
-        <v>2170757534</v>
-      </c>
-      <c r="J5" s="1"/>
-      <c r="M5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="19">
-        <v>1049432</v>
-      </c>
-      <c r="D6" s="20">
-        <v>1383165</v>
-      </c>
-      <c r="E6" s="20">
-        <v>1596845</v>
-      </c>
-      <c r="F6" s="20">
-        <v>3363704</v>
-      </c>
-      <c r="G6" s="20">
-        <v>3719157</v>
-      </c>
-      <c r="H6" s="20">
-        <v>2951847</v>
-      </c>
-      <c r="I6" s="20">
-        <v>3098267</v>
-      </c>
-      <c r="M6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="14">
-        <v>1.9E-3</v>
-      </c>
-      <c r="D7" s="14">
-        <v>1.9E-3</v>
-      </c>
-      <c r="E7" s="14">
-        <v>1.9E-3</v>
-      </c>
-      <c r="F7" s="14">
-        <v>1.9E-3</v>
-      </c>
-      <c r="G7" s="14">
-        <v>1.9E-3</v>
-      </c>
-      <c r="H7" s="14">
-        <f>((114/366)*0.19%)+((252/366)*0.15%)</f>
-        <v>1.6245901639344263E-3</v>
-      </c>
-      <c r="I7" s="14">
-        <v>1.5E-3</v>
-      </c>
-      <c r="J7" s="3">
-        <f>AVERAGE(C7:I7)</f>
-        <v>1.8035128805620607E-3</v>
-      </c>
-      <c r="M7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19">
-        <f t="shared" ref="D8:I8" si="0">(C5+D5)/2</f>
-        <v>656536024</v>
-      </c>
-      <c r="E8" s="19">
-        <f t="shared" si="0"/>
-        <v>904014757</v>
-      </c>
-      <c r="F8" s="19">
-        <f t="shared" si="0"/>
-        <v>1553105883.5</v>
-      </c>
-      <c r="G8" s="19">
-        <f t="shared" si="0"/>
-        <v>1925009523.5</v>
-      </c>
-      <c r="H8" s="19">
-        <f t="shared" si="0"/>
-        <v>1757440116</v>
-      </c>
-      <c r="I8" s="19">
-        <f t="shared" si="0"/>
-        <v>1928043018</v>
-      </c>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="20">
-        <f t="shared" ref="C9:H9" si="1">C6/C7</f>
-        <v>552332631.57894742</v>
-      </c>
-      <c r="D9" s="20">
-        <f t="shared" si="1"/>
-        <v>727981578.94736838</v>
-      </c>
-      <c r="E9" s="20">
-        <f t="shared" si="1"/>
-        <v>840444736.84210527</v>
-      </c>
-      <c r="F9" s="20">
-        <f t="shared" si="1"/>
-        <v>1770370526.3157895</v>
-      </c>
-      <c r="G9" s="20">
-        <f t="shared" si="1"/>
-        <v>1957451052.6315789</v>
-      </c>
-      <c r="H9" s="20">
-        <f t="shared" si="1"/>
-        <v>1816979485.3683147</v>
-      </c>
-      <c r="I9" s="20">
-        <f t="shared" ref="I9" si="2">I6/I7</f>
-        <v>2065511333.3333333</v>
-      </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="5">
-        <v>10217727</v>
-      </c>
-      <c r="D11" s="5">
-        <v>16266986</v>
-      </c>
-      <c r="E11" s="5">
-        <v>17759481</v>
-      </c>
-      <c r="F11" s="5">
-        <v>39527484</v>
-      </c>
-      <c r="G11" s="5">
-        <v>46429139</v>
-      </c>
-      <c r="H11" s="5">
-        <v>44479054</v>
-      </c>
-      <c r="I11" s="5">
-        <v>44662717</v>
-      </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5">
-        <v>1532098</v>
-      </c>
-      <c r="D12" s="5">
-        <v>2439137</v>
-      </c>
-      <c r="E12" s="5">
-        <v>2650584</v>
-      </c>
-      <c r="F12" s="5">
-        <v>5929674</v>
-      </c>
-      <c r="G12" s="5">
-        <v>6964518</v>
-      </c>
-      <c r="H12" s="5">
-        <v>6671858</v>
-      </c>
-      <c r="I12" s="5">
-        <v>6670470</v>
-      </c>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="16">
-        <f t="shared" ref="C13:H13" si="3">C12/C11</f>
-        <v>0.14994509052747251</v>
-      </c>
-      <c r="D13" s="16">
-        <f t="shared" si="3"/>
-        <v>0.14994400314846279</v>
-      </c>
-      <c r="E13" s="16">
-        <f>E12/E11</f>
-        <v>0.14924895609280475</v>
-      </c>
-      <c r="F13" s="16">
-        <f t="shared" si="3"/>
-        <v>0.15001394978744409</v>
-      </c>
-      <c r="G13" s="16">
-        <f t="shared" si="3"/>
-        <v>0.15000316934587135</v>
-      </c>
-      <c r="H13" s="16">
-        <f t="shared" si="3"/>
-        <v>0.14999999775175074</v>
-      </c>
-      <c r="I13" s="16">
-        <f t="shared" ref="I13" si="4">I12/I11</f>
-        <v>0.14935208711104611</v>
-      </c>
-      <c r="J13" s="3">
-        <f>AVERAGE(C13:I13)</f>
-        <v>0.14978675053783605</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="15">
-        <f t="shared" ref="C14:H14" si="5">C12/C9</f>
-        <v>2.7738683402068927E-3</v>
-      </c>
-      <c r="D14" s="15">
-        <f t="shared" si="5"/>
-        <v>3.3505476931530226E-3</v>
-      </c>
-      <c r="E14" s="15">
-        <f t="shared" si="5"/>
-        <v>3.153787374479051E-3</v>
-      </c>
-      <c r="F14" s="15">
-        <f t="shared" si="5"/>
-        <v>3.3493971526626599E-3</v>
-      </c>
-      <c r="G14" s="15">
-        <f t="shared" si="5"/>
-        <v>3.557952568283619E-3</v>
-      </c>
-      <c r="H14" s="15">
-        <f t="shared" si="5"/>
-        <v>3.6719500983510372E-3</v>
-      </c>
-      <c r="I14" s="15">
-        <f t="shared" ref="I14" si="6">I12/I9</f>
-        <v>3.2294521421168676E-3</v>
-      </c>
-      <c r="J14" s="3">
-        <f>AVERAGE(C14:I14)</f>
-        <v>3.2981364813218783E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20">
-        <v>4191238</v>
-      </c>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20">
-        <v>109586469</v>
-      </c>
-      <c r="I16" s="20">
-        <v>132363890</v>
-      </c>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="15">
-        <f>E16/E5</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="15">
-        <f>F16/F5</f>
-        <v>2.0743903970805977E-3</v>
-      </c>
-      <c r="G17" s="15">
-        <f>G16/G5</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="15">
-        <f>H16/H5</f>
-        <v>6.5023803294106994E-2</v>
-      </c>
-      <c r="I17" s="15">
-        <f>I16/I5</f>
-        <v>6.0975898011094959E-2</v>
-      </c>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20">
-        <v>23585</v>
-      </c>
-      <c r="F19" s="20">
-        <v>204352</v>
-      </c>
-      <c r="G19" s="20">
-        <v>191141</v>
-      </c>
-      <c r="H19" s="20">
-        <v>287610</v>
-      </c>
-      <c r="I19" s="20">
-        <v>254177</v>
-      </c>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="17">
-        <f t="shared" ref="C20:I20" si="7">C19/C9</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="17">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="E20" s="17">
-        <f t="shared" si="7"/>
-        <v>2.806252328810874E-5</v>
-      </c>
-      <c r="F20" s="17">
-        <f t="shared" si="7"/>
-        <v>1.1542894380718398E-4</v>
-      </c>
-      <c r="G20" s="17">
-        <f t="shared" si="7"/>
-        <v>9.764790784578334E-5</v>
-      </c>
-      <c r="H20" s="17">
-        <f t="shared" si="7"/>
-        <v>1.5829017460904321E-4</v>
-      </c>
-      <c r="I20" s="17">
-        <f t="shared" si="7"/>
-        <v>1.2305766417161594E-4</v>
-      </c>
-      <c r="J20" s="3">
-        <f>AVERAGE(C20:I20)</f>
-        <v>7.464103053167645E-5</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="3"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="19">
-        <v>85794</v>
-      </c>
-      <c r="D22" s="20">
-        <v>109651</v>
-      </c>
-      <c r="E22" s="20">
-        <v>103589</v>
-      </c>
-      <c r="F22" s="20">
-        <v>128797</v>
-      </c>
-      <c r="G22" s="20">
-        <v>90461</v>
-      </c>
-      <c r="H22" s="20">
-        <v>37218</v>
-      </c>
-      <c r="I22" s="20">
-        <v>85891</v>
-      </c>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="15">
-        <f t="shared" ref="C23:I23" si="8">C22/C9</f>
-        <v>1.5533031201640505E-4</v>
-      </c>
-      <c r="D23" s="15">
-        <f t="shared" si="8"/>
-        <v>1.5062331681325078E-4</v>
-      </c>
-      <c r="E23" s="15">
-        <f t="shared" si="8"/>
-        <v>1.2325498091549274E-4</v>
-      </c>
-      <c r="F23" s="15">
-        <f t="shared" si="8"/>
-        <v>7.2751437106237648E-5</v>
-      </c>
-      <c r="G23" s="18">
-        <f t="shared" si="8"/>
-        <v>4.6213671539007365E-5</v>
-      </c>
-      <c r="H23" s="18">
-        <f t="shared" si="8"/>
-        <v>2.0483445355166266E-5</v>
-      </c>
-      <c r="I23" s="18">
-        <f t="shared" si="8"/>
-        <v>4.1583407756658806E-5</v>
-      </c>
-      <c r="J23" s="3">
-        <f>AVERAGE(C23:I23)</f>
-        <v>8.7177224500316946E-5</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J26" s="18"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="3">
-        <f>J7+J14-J20+J23</f>
-        <v>5.1141855558525795E-3</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="3">
-        <f>AVERAGE(GTD!E40:J40)/100</f>
-        <v>5.416666666666666E-3</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="3">
-        <f>C28-C27</f>
-        <v>3.0248111081408648E-4</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="1"/>
-      <c r="C31" s="11"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B32" s="1"/>
-      <c r="C32" s="11"/>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" s="1"/>
-      <c r="C33" s="11"/>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C34" s="11"/>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="1"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D55271D4-8CAB-4791-86A4-56A1D92A09CA}">
   <dimension ref="B1:T41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6427,7 +4734,7 @@
         <v>-0.29583333333333323</v>
       </c>
       <c r="T20" s="31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
@@ -6975,7 +5282,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756669C5-6D31-44B8-AA06-7A631D93EE50}">
   <dimension ref="B1:J13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7069,8 +5376,8 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="J4" s="29">
-        <f>VWRL!N12</f>
-        <v>0.11605882428458264</v>
+        <f>VWRL!O12</f>
+        <v>0.11622144534327571</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -7387,15 +5694,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B41DF3-38FC-48D2-A2F4-45E9F93EAE67}">
-  <dimension ref="B1:J13"/>
+  <dimension ref="B1:K13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C1" s="1">
         <v>2017</v>
       </c>
@@ -7420,8 +5727,11 @@
       <c r="J1" s="1">
         <v>2024</v>
       </c>
-    </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>51</v>
       </c>
@@ -7430,7 +5740,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>49</v>
       </c>
@@ -7458,8 +5768,11 @@
       <c r="J3" s="6">
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="6">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>50</v>
       </c>
@@ -7493,13 +5806,16 @@
       <c r="J4" s="6">
         <v>0.93</v>
       </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="6">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>49</v>
       </c>
@@ -7527,8 +5843,11 @@
       <c r="J7" s="6">
         <v>0.06</v>
       </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>50</v>
       </c>
@@ -7561,24 +5880,2012 @@
       <c r="J8" s="6">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="6">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="31" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="31" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BEA51A6-CEA5-4113-9E88-4EE6B698AC9B}">
+  <dimension ref="B2:M36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="38.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="16.28515625" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C4" s="1">
+        <v>2015</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2016</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2017</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2018</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2019</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2020</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="36">
+        <v>44377</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="19">
+        <v>286237679</v>
+      </c>
+      <c r="D5" s="20">
+        <v>502327318</v>
+      </c>
+      <c r="E5" s="20">
+        <v>1113048696</v>
+      </c>
+      <c r="F5" s="20">
+        <v>1679694691</v>
+      </c>
+      <c r="G5" s="20">
+        <v>1694765475</v>
+      </c>
+      <c r="H5" s="20">
+        <v>2009226586</v>
+      </c>
+      <c r="I5" s="20">
+        <v>2645377063</v>
+      </c>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="19">
+        <v>197844</v>
+      </c>
+      <c r="D6" s="20">
+        <v>500281</v>
+      </c>
+      <c r="E6" s="20">
+        <v>868002</v>
+      </c>
+      <c r="F6" s="20">
+        <v>1747960</v>
+      </c>
+      <c r="G6" s="20">
+        <v>1927300</v>
+      </c>
+      <c r="H6" s="20">
+        <v>2030488</v>
+      </c>
+      <c r="I6" s="20">
+        <v>2223741</v>
+      </c>
+      <c r="M6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="14">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="D7" s="14">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="E7" s="14">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="F7" s="14">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="G7" s="14">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="H7" s="14">
+        <f>((114/366)*0.12%)+((252/366)*0.1%)</f>
+        <v>1.0622950819672132E-3</v>
+      </c>
+      <c r="I7" s="14">
+        <v>1E-3</v>
+      </c>
+      <c r="J7" s="3">
+        <f>AVERAGE(D7:I7)</f>
+        <v>1.1437158469945355E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19">
+        <f t="shared" ref="D8" si="0">(C5+D5)/2</f>
+        <v>394282498.5</v>
+      </c>
+      <c r="E8" s="19">
+        <f t="shared" ref="E8" si="1">(D5+E5)/2</f>
+        <v>807688007</v>
+      </c>
+      <c r="F8" s="19">
+        <f t="shared" ref="F8" si="2">(E5+F5)/2</f>
+        <v>1396371693.5</v>
+      </c>
+      <c r="G8" s="19">
+        <f t="shared" ref="G8" si="3">(F5+G5)/2</f>
+        <v>1687230083</v>
+      </c>
+      <c r="H8" s="19">
+        <f t="shared" ref="H8:I8" si="4">(G5+H5)/2</f>
+        <v>1851996030.5</v>
+      </c>
+      <c r="I8" s="19">
+        <f t="shared" si="4"/>
+        <v>2327301824.5</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="M8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="20">
+        <f t="shared" ref="C9:H9" si="5">C6/C7</f>
+        <v>164870000</v>
+      </c>
+      <c r="D9" s="20">
+        <f t="shared" si="5"/>
+        <v>416900833.33333337</v>
+      </c>
+      <c r="E9" s="20">
+        <f t="shared" si="5"/>
+        <v>723335000.00000012</v>
+      </c>
+      <c r="F9" s="20">
+        <f t="shared" si="5"/>
+        <v>1456633333.3333335</v>
+      </c>
+      <c r="G9" s="20">
+        <f t="shared" si="5"/>
+        <v>1606083333.3333335</v>
+      </c>
+      <c r="H9" s="20">
+        <f t="shared" si="5"/>
+        <v>1911416172.8395061</v>
+      </c>
+      <c r="I9" s="20">
+        <f t="shared" ref="I9" si="6">I6/I7</f>
+        <v>2223741000</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="M9" s="30" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="3"/>
+      <c r="M10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>6453840</v>
+      </c>
+      <c r="D11" s="5">
+        <v>16699948</v>
+      </c>
+      <c r="E11" s="5">
+        <v>28612288</v>
+      </c>
+      <c r="F11" s="5">
+        <v>55451908</v>
+      </c>
+      <c r="G11" s="5">
+        <v>63355725</v>
+      </c>
+      <c r="H11" s="5">
+        <v>53087528</v>
+      </c>
+      <c r="I11" s="5">
+        <v>70651678</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="M11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5">
+        <v>449779</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1214196</v>
+      </c>
+      <c r="E12" s="5">
+        <v>2137859</v>
+      </c>
+      <c r="F12" s="5">
+        <v>4211322</v>
+      </c>
+      <c r="G12" s="5">
+        <v>4497447</v>
+      </c>
+      <c r="H12" s="5">
+        <v>5016404</v>
+      </c>
+      <c r="I12" s="5">
+        <v>5281336</v>
+      </c>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="16">
+        <f t="shared" ref="C13:H13" si="7">C12/C11</f>
+        <v>6.9691687429499341E-2</v>
+      </c>
+      <c r="D13" s="16">
+        <f t="shared" si="7"/>
+        <v>7.2706573697115709E-2</v>
+      </c>
+      <c r="E13" s="16">
+        <f t="shared" si="7"/>
+        <v>7.4718211979412488E-2</v>
+      </c>
+      <c r="F13" s="16">
+        <f t="shared" si="7"/>
+        <v>7.5945484148173939E-2</v>
+      </c>
+      <c r="G13" s="16">
+        <f t="shared" si="7"/>
+        <v>7.0987223333013716E-2</v>
+      </c>
+      <c r="H13" s="16">
+        <f t="shared" si="7"/>
+        <v>9.4493079429126936E-2</v>
+      </c>
+      <c r="I13" s="16">
+        <f t="shared" ref="I13" si="8">I12/I11</f>
+        <v>7.475174191899589E-2</v>
+      </c>
+      <c r="J13" s="3">
+        <f>AVERAGE(D13:I13)</f>
+        <v>7.7267052417639773E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="15">
+        <f t="shared" ref="C14:H14" si="9">C12/C9</f>
+        <v>2.7280827318493356E-3</v>
+      </c>
+      <c r="D14" s="15">
+        <f t="shared" si="9"/>
+        <v>2.9124336123098815E-3</v>
+      </c>
+      <c r="E14" s="15">
+        <f t="shared" si="9"/>
+        <v>2.9555586277450968E-3</v>
+      </c>
+      <c r="F14" s="15">
+        <f t="shared" si="9"/>
+        <v>2.8911338932241007E-3</v>
+      </c>
+      <c r="G14" s="15">
+        <f t="shared" si="9"/>
+        <v>2.8002575623929846E-3</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="9"/>
+        <v>2.6244436304773315E-3</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" ref="I14" si="10">I12/I9</f>
+        <v>2.3749780212713621E-3</v>
+      </c>
+      <c r="J14" s="3">
+        <f>AVERAGE(D14:I14)</f>
+        <v>2.7598008912367929E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20">
+        <v>4326489</v>
+      </c>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20">
+        <v>22002115</v>
+      </c>
+      <c r="I16" s="20">
+        <v>12654321</v>
+      </c>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="15">
+        <f>E16/E5</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="15">
+        <f>F16/F5</f>
+        <v>2.5757591681284894E-3</v>
+      </c>
+      <c r="G17" s="15">
+        <f>G16/G5</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="15">
+        <f>H16/H5</f>
+        <v>1.0950539452995274E-2</v>
+      </c>
+      <c r="I17" s="15">
+        <f>I16/I5</f>
+        <v>4.7835604145026189E-3</v>
+      </c>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20">
+        <v>89435</v>
+      </c>
+      <c r="F19" s="20">
+        <v>193993</v>
+      </c>
+      <c r="G19" s="20">
+        <v>209291</v>
+      </c>
+      <c r="H19" s="20">
+        <v>480474</v>
+      </c>
+      <c r="I19" s="20">
+        <v>607727</v>
+      </c>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="17">
+        <f t="shared" ref="C20:I20" si="11">C19/C9</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="17">
+        <f t="shared" si="11"/>
+        <v>1.2364257225213764E-4</v>
+      </c>
+      <c r="F20" s="17">
+        <f t="shared" si="11"/>
+        <v>1.3317902011487676E-4</v>
+      </c>
+      <c r="G20" s="17">
+        <f t="shared" si="11"/>
+        <v>1.3031142012141336E-4</v>
+      </c>
+      <c r="H20" s="17">
+        <f t="shared" si="11"/>
+        <v>2.5137068882609241E-4</v>
+      </c>
+      <c r="I20" s="17">
+        <f t="shared" si="11"/>
+        <v>2.7329036969683069E-4</v>
+      </c>
+      <c r="J20" s="3">
+        <f>AVERAGE(D20:I20)</f>
+        <v>1.519656785018918E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C21" s="12"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="19">
+        <v>422303</v>
+      </c>
+      <c r="D22" s="20">
+        <v>602163</v>
+      </c>
+      <c r="E22" s="20">
+        <v>1099868</v>
+      </c>
+      <c r="F22" s="20">
+        <v>1252501</v>
+      </c>
+      <c r="G22" s="20">
+        <v>481133</v>
+      </c>
+      <c r="H22" s="20">
+        <v>891525</v>
+      </c>
+      <c r="I22" s="20">
+        <v>325824</v>
+      </c>
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="15">
+        <f t="shared" ref="C23:I23" si="12">C22/C9</f>
+        <v>2.5614302177473162E-3</v>
+      </c>
+      <c r="D23" s="15">
+        <f t="shared" si="12"/>
+        <v>1.4443794587441856E-3</v>
+      </c>
+      <c r="E23" s="15">
+        <f t="shared" si="12"/>
+        <v>1.5205513351351722E-3</v>
+      </c>
+      <c r="F23" s="15">
+        <f t="shared" si="12"/>
+        <v>8.5986017986681605E-4</v>
+      </c>
+      <c r="G23" s="18">
+        <f t="shared" si="12"/>
+        <v>2.9956913817257301E-4</v>
+      </c>
+      <c r="H23" s="18">
+        <f t="shared" si="12"/>
+        <v>4.6642118690227161E-4</v>
+      </c>
+      <c r="I23" s="18">
+        <f t="shared" si="12"/>
+        <v>1.4652066045461231E-4</v>
+      </c>
+      <c r="J23" s="3">
+        <f>AVERAGE(D23:I23)</f>
+        <v>7.8955032654593838E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="3">
+        <f>J7+J14-J20+J23</f>
+        <v>4.541101386275375E-3</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E27" s="8"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="3">
+        <f>AVERAGE(GTD!F26:J26)/100</f>
+        <v>3.7799999999999995E-3</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="3">
+        <f>C28-C27</f>
+        <v>-7.6110138627537554E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="1"/>
+      <c r="C31" s="11"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="1"/>
+      <c r="C32" s="11"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="1"/>
+      <c r="C33" s="11"/>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C34" s="11"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="1"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M9" r:id="rId1" display="https://www.ie.vanguard/product-documentation/mifid-priips" xr:uid="{B1E0BFAB-C50F-4C2F-9682-FD621075CC24}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6F59AA-9D8B-4A10-A65A-228471C4BA4F}">
+  <dimension ref="B2:M36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="38.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="16.28515625" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C4" s="1">
+        <v>2015</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2016</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2017</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2018</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2019</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2020</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="30"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="19">
+        <v>95809998</v>
+      </c>
+      <c r="D5" s="20">
+        <v>123443681</v>
+      </c>
+      <c r="E5" s="20">
+        <v>256132398</v>
+      </c>
+      <c r="F5" s="20">
+        <v>353569464</v>
+      </c>
+      <c r="G5" s="20">
+        <v>391574855</v>
+      </c>
+      <c r="H5" s="20">
+        <v>578659274</v>
+      </c>
+      <c r="I5" s="20">
+        <v>1090229427</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="M5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="19">
+        <v>176697</v>
+      </c>
+      <c r="D6" s="20">
+        <v>222968</v>
+      </c>
+      <c r="E6" s="20">
+        <v>394440</v>
+      </c>
+      <c r="F6" s="20">
+        <v>734028</v>
+      </c>
+      <c r="G6" s="20">
+        <v>772839</v>
+      </c>
+      <c r="H6" s="20">
+        <v>756995</v>
+      </c>
+      <c r="I6" s="20">
+        <v>1281554</v>
+      </c>
+      <c r="M6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="14">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="D7" s="14">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="E7" s="14">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="F7" s="14">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="G7" s="14">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="H7" s="14">
+        <f>((114/366)*0.22%)+((252/366)*0.15%)</f>
+        <v>1.7180327868852462E-3</v>
+      </c>
+      <c r="I7" s="14">
+        <v>1.5E-3</v>
+      </c>
+      <c r="J7" s="3">
+        <f>AVERAGE(C7:I7)</f>
+        <v>2.0311475409836065E-3</v>
+      </c>
+      <c r="M7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19">
+        <f t="shared" ref="D8:I8" si="0">(C5+D5)/2</f>
+        <v>109626839.5</v>
+      </c>
+      <c r="E8" s="19">
+        <f t="shared" si="0"/>
+        <v>189788039.5</v>
+      </c>
+      <c r="F8" s="19">
+        <f t="shared" si="0"/>
+        <v>304850931</v>
+      </c>
+      <c r="G8" s="19">
+        <f t="shared" si="0"/>
+        <v>372572159.5</v>
+      </c>
+      <c r="H8" s="19">
+        <f t="shared" si="0"/>
+        <v>485117064.5</v>
+      </c>
+      <c r="I8" s="19">
+        <f t="shared" si="0"/>
+        <v>834444350.5</v>
+      </c>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="20">
+        <f t="shared" ref="C9:H9" si="1">C6/C7</f>
+        <v>80316818.181818172</v>
+      </c>
+      <c r="D9" s="20">
+        <f t="shared" si="1"/>
+        <v>101349090.90909091</v>
+      </c>
+      <c r="E9" s="20">
+        <f t="shared" si="1"/>
+        <v>179290909.09090909</v>
+      </c>
+      <c r="F9" s="20">
+        <f t="shared" si="1"/>
+        <v>333649090.90909088</v>
+      </c>
+      <c r="G9" s="20">
+        <f t="shared" si="1"/>
+        <v>351290454.5454545</v>
+      </c>
+      <c r="H9" s="20">
+        <f t="shared" si="1"/>
+        <v>440617318.70229</v>
+      </c>
+      <c r="I9" s="20">
+        <f t="shared" ref="I9" si="2">I6/I7</f>
+        <v>854369333.33333337</v>
+      </c>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2910412</v>
+      </c>
+      <c r="D11" s="5">
+        <v>3697627</v>
+      </c>
+      <c r="E11" s="5">
+        <v>6020134</v>
+      </c>
+      <c r="F11" s="5">
+        <v>12310610</v>
+      </c>
+      <c r="G11" s="5">
+        <v>14080736</v>
+      </c>
+      <c r="H11" s="5">
+        <v>14853415</v>
+      </c>
+      <c r="I11" s="5">
+        <v>27718490</v>
+      </c>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5">
+        <v>95674</v>
+      </c>
+      <c r="D12" s="5">
+        <v>135521</v>
+      </c>
+      <c r="E12" s="5">
+        <v>217184</v>
+      </c>
+      <c r="F12" s="5">
+        <v>396984</v>
+      </c>
+      <c r="G12" s="5">
+        <v>725905</v>
+      </c>
+      <c r="H12" s="5">
+        <v>642854</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1842818</v>
+      </c>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="16">
+        <f t="shared" ref="C13:H13" si="3">C12/C11</f>
+        <v>3.2873009044767545E-2</v>
+      </c>
+      <c r="D13" s="16">
+        <f t="shared" si="3"/>
+        <v>3.6650803339547226E-2</v>
+      </c>
+      <c r="E13" s="16">
+        <f t="shared" si="3"/>
+        <v>3.6076273385276809E-2</v>
+      </c>
+      <c r="F13" s="16">
+        <f t="shared" si="3"/>
+        <v>3.2247305373169971E-2</v>
+      </c>
+      <c r="G13" s="16">
+        <f t="shared" si="3"/>
+        <v>5.1553058021967031E-2</v>
+      </c>
+      <c r="H13" s="16">
+        <f t="shared" si="3"/>
+        <v>4.3279878734957582E-2</v>
+      </c>
+      <c r="I13" s="16">
+        <f t="shared" ref="I13" si="4">I12/I11</f>
+        <v>6.6483347397351011E-2</v>
+      </c>
+      <c r="J13" s="3">
+        <f>AVERAGE(C13:I13)</f>
+        <v>4.2737667899576733E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="15">
+        <f t="shared" ref="C14:H14" si="5">C12/C9</f>
+        <v>1.191207547383374E-3</v>
+      </c>
+      <c r="D14" s="15">
+        <f t="shared" si="5"/>
+        <v>1.3371703562843099E-3</v>
+      </c>
+      <c r="E14" s="15">
+        <f t="shared" si="5"/>
+        <v>1.2113497616874555E-3</v>
+      </c>
+      <c r="F14" s="15">
+        <f t="shared" si="5"/>
+        <v>1.1898249113112852E-3</v>
+      </c>
+      <c r="G14" s="15">
+        <f t="shared" si="5"/>
+        <v>2.0663954588213073E-3</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="5"/>
+        <v>1.4589848667168582E-3</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" ref="I14" si="6">I12/I9</f>
+        <v>2.1569336914402356E-3</v>
+      </c>
+      <c r="J14" s="3">
+        <f>AVERAGE(C14:I14)</f>
+        <v>1.5159809419492607E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20">
+        <v>2168054</v>
+      </c>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20">
+        <v>5733068</v>
+      </c>
+      <c r="I16" s="20">
+        <v>2494078</v>
+      </c>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="15">
+        <f>E16/E5</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="15">
+        <f>F16/F5</f>
+        <v>6.1319039700781404E-3</v>
+      </c>
+      <c r="G17" s="15">
+        <f>G16/G5</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="15">
+        <f>H16/H5</f>
+        <v>9.9075021478010564E-3</v>
+      </c>
+      <c r="I17" s="15">
+        <f>I16/I5</f>
+        <v>2.2876634387525114E-3</v>
+      </c>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20">
+        <v>4070</v>
+      </c>
+      <c r="F19" s="20">
+        <v>43784</v>
+      </c>
+      <c r="G19" s="20">
+        <v>81269</v>
+      </c>
+      <c r="H19" s="20">
+        <v>147489</v>
+      </c>
+      <c r="I19" s="20">
+        <v>85284</v>
+      </c>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="17">
+        <f t="shared" ref="C20:I20" si="7">C19/C9</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="17">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="17">
+        <f t="shared" si="7"/>
+        <v>2.2700537470844743E-5</v>
+      </c>
+      <c r="F20" s="17">
+        <f t="shared" si="7"/>
+        <v>1.3122769158669699E-4</v>
+      </c>
+      <c r="G20" s="17">
+        <f t="shared" si="7"/>
+        <v>2.3134417388356439E-4</v>
+      </c>
+      <c r="H20" s="17">
+        <f t="shared" si="7"/>
+        <v>3.3473264381524061E-4</v>
+      </c>
+      <c r="I20" s="17">
+        <f t="shared" si="7"/>
+        <v>9.9820998568924912E-5</v>
+      </c>
+      <c r="J20" s="3">
+        <f>AVERAGE(C20:I20)</f>
+        <v>1.1711800647503882E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C21" s="12"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="19">
+        <v>57821</v>
+      </c>
+      <c r="D22" s="20">
+        <v>32497</v>
+      </c>
+      <c r="E22" s="20">
+        <v>59576</v>
+      </c>
+      <c r="F22" s="20">
+        <v>92342</v>
+      </c>
+      <c r="G22" s="20">
+        <v>59886</v>
+      </c>
+      <c r="H22" s="20">
+        <v>127784</v>
+      </c>
+      <c r="I22" s="20">
+        <v>211398</v>
+      </c>
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="15">
+        <f t="shared" ref="C23:I23" si="8">C22/C9</f>
+        <v>7.1991148689564625E-4</v>
+      </c>
+      <c r="D23" s="15">
+        <f t="shared" si="8"/>
+        <v>3.2064421800437733E-4</v>
+      </c>
+      <c r="E23" s="15">
+        <f t="shared" si="8"/>
+        <v>3.322867863299868E-4</v>
+      </c>
+      <c r="F23" s="15">
+        <f t="shared" si="8"/>
+        <v>2.7676382917272914E-4</v>
+      </c>
+      <c r="G23" s="18">
+        <f t="shared" si="8"/>
+        <v>1.7047431612535083E-4</v>
+      </c>
+      <c r="H23" s="18">
+        <f t="shared" si="8"/>
+        <v>2.9001129682407981E-4</v>
+      </c>
+      <c r="I23" s="18">
+        <f t="shared" si="8"/>
+        <v>2.4743163378211137E-4</v>
+      </c>
+      <c r="J23" s="3">
+        <f>AVERAGE(C23:I23)</f>
+        <v>3.3678908101918311E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="3">
+        <f>J7+J14-J20+J23</f>
+        <v>3.766799557477012E-3</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E27" s="8"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="3">
+        <f>AVERAGE(GTD!E33:J33)/100</f>
+        <v>3.5500000000000015E-3</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="3">
+        <f>C28-C27</f>
+        <v>-2.1679955747701046E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="1"/>
+      <c r="C31" s="11"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="1"/>
+      <c r="C32" s="11"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="1"/>
+      <c r="C33" s="11"/>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C34" s="11"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="1"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17C62D4-0311-4C15-9CAB-0AC451E6E3A5}">
+  <dimension ref="B2:M36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="38.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="16.28515625" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C4" s="1">
+        <v>2015</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2016</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2017</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2018</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2019</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2020</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="30"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="19">
+        <v>590786984</v>
+      </c>
+      <c r="D5" s="20">
+        <v>722285064</v>
+      </c>
+      <c r="E5" s="20">
+        <v>1085744450</v>
+      </c>
+      <c r="F5" s="20">
+        <v>2020467317</v>
+      </c>
+      <c r="G5" s="20">
+        <v>1829551730</v>
+      </c>
+      <c r="H5" s="20">
+        <v>1685328502</v>
+      </c>
+      <c r="I5" s="20">
+        <v>2170757534</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="M5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="19">
+        <v>1049432</v>
+      </c>
+      <c r="D6" s="20">
+        <v>1383165</v>
+      </c>
+      <c r="E6" s="20">
+        <v>1596845</v>
+      </c>
+      <c r="F6" s="20">
+        <v>3363704</v>
+      </c>
+      <c r="G6" s="20">
+        <v>3719157</v>
+      </c>
+      <c r="H6" s="20">
+        <v>2951847</v>
+      </c>
+      <c r="I6" s="20">
+        <v>3098267</v>
+      </c>
+      <c r="M6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="14">
+        <v>1.9E-3</v>
+      </c>
+      <c r="D7" s="14">
+        <v>1.9E-3</v>
+      </c>
+      <c r="E7" s="14">
+        <v>1.9E-3</v>
+      </c>
+      <c r="F7" s="14">
+        <v>1.9E-3</v>
+      </c>
+      <c r="G7" s="14">
+        <v>1.9E-3</v>
+      </c>
+      <c r="H7" s="14">
+        <f>((114/366)*0.19%)+((252/366)*0.15%)</f>
+        <v>1.6245901639344263E-3</v>
+      </c>
+      <c r="I7" s="14">
+        <v>1.5E-3</v>
+      </c>
+      <c r="J7" s="3">
+        <f>AVERAGE(C7:I7)</f>
+        <v>1.8035128805620607E-3</v>
+      </c>
+      <c r="M7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19">
+        <f t="shared" ref="D8:I8" si="0">(C5+D5)/2</f>
+        <v>656536024</v>
+      </c>
+      <c r="E8" s="19">
+        <f t="shared" si="0"/>
+        <v>904014757</v>
+      </c>
+      <c r="F8" s="19">
+        <f t="shared" si="0"/>
+        <v>1553105883.5</v>
+      </c>
+      <c r="G8" s="19">
+        <f t="shared" si="0"/>
+        <v>1925009523.5</v>
+      </c>
+      <c r="H8" s="19">
+        <f t="shared" si="0"/>
+        <v>1757440116</v>
+      </c>
+      <c r="I8" s="19">
+        <f t="shared" si="0"/>
+        <v>1928043018</v>
+      </c>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="20">
+        <f t="shared" ref="C9:H9" si="1">C6/C7</f>
+        <v>552332631.57894742</v>
+      </c>
+      <c r="D9" s="20">
+        <f t="shared" si="1"/>
+        <v>727981578.94736838</v>
+      </c>
+      <c r="E9" s="20">
+        <f t="shared" si="1"/>
+        <v>840444736.84210527</v>
+      </c>
+      <c r="F9" s="20">
+        <f t="shared" si="1"/>
+        <v>1770370526.3157895</v>
+      </c>
+      <c r="G9" s="20">
+        <f t="shared" si="1"/>
+        <v>1957451052.6315789</v>
+      </c>
+      <c r="H9" s="20">
+        <f t="shared" si="1"/>
+        <v>1816979485.3683147</v>
+      </c>
+      <c r="I9" s="20">
+        <f t="shared" ref="I9" si="2">I6/I7</f>
+        <v>2065511333.3333333</v>
+      </c>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>10217727</v>
+      </c>
+      <c r="D11" s="5">
+        <v>16266986</v>
+      </c>
+      <c r="E11" s="5">
+        <v>17759481</v>
+      </c>
+      <c r="F11" s="5">
+        <v>39527484</v>
+      </c>
+      <c r="G11" s="5">
+        <v>46429139</v>
+      </c>
+      <c r="H11" s="5">
+        <v>44479054</v>
+      </c>
+      <c r="I11" s="5">
+        <v>44662717</v>
+      </c>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1532098</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2439137</v>
+      </c>
+      <c r="E12" s="5">
+        <v>2650584</v>
+      </c>
+      <c r="F12" s="5">
+        <v>5929674</v>
+      </c>
+      <c r="G12" s="5">
+        <v>6964518</v>
+      </c>
+      <c r="H12" s="5">
+        <v>6671858</v>
+      </c>
+      <c r="I12" s="5">
+        <v>6670470</v>
+      </c>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="16">
+        <f t="shared" ref="C13:H13" si="3">C12/C11</f>
+        <v>0.14994509052747251</v>
+      </c>
+      <c r="D13" s="16">
+        <f t="shared" si="3"/>
+        <v>0.14994400314846279</v>
+      </c>
+      <c r="E13" s="16">
+        <f>E12/E11</f>
+        <v>0.14924895609280475</v>
+      </c>
+      <c r="F13" s="16">
+        <f t="shared" si="3"/>
+        <v>0.15001394978744409</v>
+      </c>
+      <c r="G13" s="16">
+        <f t="shared" si="3"/>
+        <v>0.15000316934587135</v>
+      </c>
+      <c r="H13" s="16">
+        <f t="shared" si="3"/>
+        <v>0.14999999775175074</v>
+      </c>
+      <c r="I13" s="16">
+        <f t="shared" ref="I13" si="4">I12/I11</f>
+        <v>0.14935208711104611</v>
+      </c>
+      <c r="J13" s="3">
+        <f>AVERAGE(C13:I13)</f>
+        <v>0.14978675053783605</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="15">
+        <f t="shared" ref="C14:H14" si="5">C12/C9</f>
+        <v>2.7738683402068927E-3</v>
+      </c>
+      <c r="D14" s="15">
+        <f t="shared" si="5"/>
+        <v>3.3505476931530226E-3</v>
+      </c>
+      <c r="E14" s="15">
+        <f t="shared" si="5"/>
+        <v>3.153787374479051E-3</v>
+      </c>
+      <c r="F14" s="15">
+        <f t="shared" si="5"/>
+        <v>3.3493971526626599E-3</v>
+      </c>
+      <c r="G14" s="15">
+        <f t="shared" si="5"/>
+        <v>3.557952568283619E-3</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="5"/>
+        <v>3.6719500983510372E-3</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" ref="I14" si="6">I12/I9</f>
+        <v>3.2294521421168676E-3</v>
+      </c>
+      <c r="J14" s="3">
+        <f>AVERAGE(C14:I14)</f>
+        <v>3.2981364813218783E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20">
+        <v>4191238</v>
+      </c>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20">
+        <v>109586469</v>
+      </c>
+      <c r="I16" s="20">
+        <v>132363890</v>
+      </c>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="15">
+        <f>E16/E5</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="15">
+        <f>F16/F5</f>
+        <v>2.0743903970805977E-3</v>
+      </c>
+      <c r="G17" s="15">
+        <f>G16/G5</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="15">
+        <f>H16/H5</f>
+        <v>6.5023803294106994E-2</v>
+      </c>
+      <c r="I17" s="15">
+        <f>I16/I5</f>
+        <v>6.0975898011094959E-2</v>
+      </c>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20">
+        <v>23585</v>
+      </c>
+      <c r="F19" s="20">
+        <v>204352</v>
+      </c>
+      <c r="G19" s="20">
+        <v>191141</v>
+      </c>
+      <c r="H19" s="20">
+        <v>287610</v>
+      </c>
+      <c r="I19" s="20">
+        <v>254177</v>
+      </c>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="17">
+        <f t="shared" ref="C20:I20" si="7">C19/C9</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="17">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="17">
+        <f t="shared" si="7"/>
+        <v>2.806252328810874E-5</v>
+      </c>
+      <c r="F20" s="17">
+        <f t="shared" si="7"/>
+        <v>1.1542894380718398E-4</v>
+      </c>
+      <c r="G20" s="17">
+        <f t="shared" si="7"/>
+        <v>9.764790784578334E-5</v>
+      </c>
+      <c r="H20" s="17">
+        <f t="shared" si="7"/>
+        <v>1.5829017460904321E-4</v>
+      </c>
+      <c r="I20" s="17">
+        <f t="shared" si="7"/>
+        <v>1.2305766417161594E-4</v>
+      </c>
+      <c r="J20" s="3">
+        <f>AVERAGE(C20:I20)</f>
+        <v>7.464103053167645E-5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C21" s="12"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="19">
+        <v>85794</v>
+      </c>
+      <c r="D22" s="20">
+        <v>109651</v>
+      </c>
+      <c r="E22" s="20">
+        <v>103589</v>
+      </c>
+      <c r="F22" s="20">
+        <v>128797</v>
+      </c>
+      <c r="G22" s="20">
+        <v>90461</v>
+      </c>
+      <c r="H22" s="20">
+        <v>37218</v>
+      </c>
+      <c r="I22" s="20">
+        <v>85891</v>
+      </c>
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="15">
+        <f t="shared" ref="C23:I23" si="8">C22/C9</f>
+        <v>1.5533031201640505E-4</v>
+      </c>
+      <c r="D23" s="15">
+        <f t="shared" si="8"/>
+        <v>1.5062331681325078E-4</v>
+      </c>
+      <c r="E23" s="15">
+        <f t="shared" si="8"/>
+        <v>1.2325498091549274E-4</v>
+      </c>
+      <c r="F23" s="15">
+        <f t="shared" si="8"/>
+        <v>7.2751437106237648E-5</v>
+      </c>
+      <c r="G23" s="18">
+        <f t="shared" si="8"/>
+        <v>4.6213671539007365E-5</v>
+      </c>
+      <c r="H23" s="18">
+        <f t="shared" si="8"/>
+        <v>2.0483445355166266E-5</v>
+      </c>
+      <c r="I23" s="18">
+        <f t="shared" si="8"/>
+        <v>4.1583407756658806E-5</v>
+      </c>
+      <c r="J23" s="3">
+        <f>AVERAGE(C23:I23)</f>
+        <v>8.7177224500316946E-5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="3">
+        <f>J7+J14-J20+J23</f>
+        <v>5.1141855558525795E-3</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E27" s="8"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="3">
+        <f>AVERAGE(GTD!E40:J40)/100</f>
+        <v>5.416666666666666E-3</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="3">
+        <f>C28-C27</f>
+        <v>3.0248111081408648E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="1"/>
+      <c r="C31" s="11"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="1"/>
+      <c r="C32" s="11"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="1"/>
+      <c r="C33" s="11"/>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C34" s="11"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="1"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Vanguard EU/Vanguard-ETFs-KostenBepaling.xlsx
+++ b/Vanguard EU/Vanguard-ETFs-KostenBepaling.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1186" documentId="13_ncr:1_{383DE9F1-B669-4070-96E2-664D98CFDC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84BF6C09-70EC-4502-98DB-2A0E0EFD36F1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10350" yWindow="4830" windowWidth="38700" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VWRL" sheetId="13" r:id="rId1"/>
@@ -543,7 +543,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -585,7 +585,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -605,10 +604,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3467,7 +3462,7 @@
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
       <c r="O14" s="3"/>
-      <c r="R14" s="37" t="s">
+      <c r="R14" t="s">
         <v>97</v>
       </c>
     </row>
